--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1268,16 +1268,20 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>14</v>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Evilkyatt</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>130</v>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -1294,11 +1298,15 @@
           <t>Bilgewater|Demacia|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>16</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
@@ -1316,16 +1324,20 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>19</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Im Bard Out</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>101</v>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -1342,11 +1354,15 @@
           <t>Bandle City|F18|Freljord|Mount Targon|Shurima</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>17</v>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1364,16 +1380,20 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>29</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Carrot Spirit</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>100</v>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1390,11 +1410,15 @@
           <t>Bandle City|Noxus</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>14</v>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
@@ -1406,6 +1430,592 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>mbrookz</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>iMQDykjthqoztGrFSrHwtphL2pV9BIrGgAz1EIFDSRHTboYbSYy9SPFPyLCvPzq3i5PdNMVJIeWEiA</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>CIEQCAIADUAQEAAGAECAAAYBAUAAYAIGAYOQCBQEBAAQOAAFAEEAABQEAYAAMCQVDQBACAIABIAQMABAAA</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01DE029","n":3},{"c":"02DE006","n":3},{"c":"04DE003","n":3},{"c":"05DE012","n":3},{"c":"06BW029","n":3},{"c":"06PZ008","n":3},{"c":"07DE005","n":3},{"c":"08DE006","n":3},{"c":"06DE006","n":3},{"c":"06DE010","n":3},{"c":"06DE021","n":3},{"c":"06DE028","n":3},{"c":"01DE010","n":2},{"c":"06DE032","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>NotreDammit</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Ik2qUvSnwi86IeXEu5fiNj4mTgE6LR2fHlKi_J1gS05olorTm2il2QpyaTh-gdM17lDLdfXLjcZ3lw</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>CQDACBQKDIAQQCQFAEEAIGACA4FASFADAECAQGJUAMCQIAQGBYBQCAIEGUAQEBAKAECQURQBAEDAIKY</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BC026","n":3},{"c":"08BC005","n":3},{"c":"08PZ024","n":3},{"c":"07BC009","n":3},{"c":"07BC020","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"05PZ002","n":3},{"c":"05PZ006","n":3},{"c":"05PZ014","n":3},{"c":"01PZ053","n":2},{"c":"02PZ010","n":2},{"c":"05BC070","n":2},{"c":"01BW004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Scilla</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>vwIBeem3KeMHt2DXT689hGEUoZwydZ1S7q2GcWLHvl4GxNDmaxHhI4X25Rx9afLQ0Z4io5Xm3dC2-A</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>CEAAAAICAAAAMJY</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Demacia</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02DE000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>netinho99</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>pv-ejnBJpvr2-uknjMz4mPMiw3R4DenY9PoZl1KIB13JDHHA0bveLZ52rxlSXCMHyWvTBN-0c4ubjw</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>CMCQCBADB4AQOBZHAIDAOBAFAMAQGEY2EYBQIBYFCQ3QIAIBAMFQCAYDAMAQIAYKAECAOOYCAECAGFQBBADQE</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04NX015","n":3},{"c":"07SH039","n":3},{"c":"06SH004","n":3},{"c":"06SH005","n":3},{"c":"01NX019","n":3},{"c":"01NX026","n":3},{"c":"01NX038","n":3},{"c":"04SH005","n":3},{"c":"04SH020","n":3},{"c":"04SH055","n":3},{"c":"01NX011","n":2},{"c":"03NX003","n":2},{"c":"04NX010","n":2},{"c":"04SH059","n":2},{"c":"01PZ003","n":1},{"c":"22FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ANG3L</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>64T_QJuxrjgymcgVU_WRi83XMzxl5n3CFbhCLnEpra1r8axDA_rRCCP2Lvk2rIRx-TL7jn-FAfdNqQ</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>CIDQCBAAAIAQKBQBAECQADABA4AA4AQBAAOSGAQCAYLCQAQCAADAUBIBAIDD4AICAAEQCBAAAMAQMBQ5AEDAAMAA</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04DE002","n":3},{"c":"05BW001","n":3},{"c":"05DE012","n":3},{"c":"07DE014","n":3},{"c":"01DE029","n":3},{"c":"01DE035","n":3},{"c":"02BW022","n":3},{"c":"02BW040","n":3},{"c":"02DE006","n":3},{"c":"02DE010","n":3},{"c":"02BW062","n":2},{"c":"02DE009","n":2},{"c":"04DE003","n":2},{"c":"06BW029","n":2},{"c":"06DE048","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Keldog</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1CKHt5W262OqVUahdjh11tOI_iLOClJy8SS9v3HT9RIEWsSJ40CQAUPI_xtuajXdOFC7cdvA3xsd3A</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCBACBYAQMAQJAEDAKDYBBECQ2AQBAUKROBIBAEBASAIHAUBACCAFFEBACBIEFIBAMBIMFYBQCCIKCQBQMBIHBYIAIAIFAEBQ6HI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Mount Targon|Noxus|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04IO014","n":3},{"c":"06IO009","n":3},{"c":"06SI015","n":3},{"c":"09SI013","n":3},{"c":"01SI021","n":3},{"c":"01SI023","n":3},{"c":"01IO009","n":2},{"c":"07SI002","n":2},{"c":"08SI041","n":2},{"c":"01SI004","n":2},{"c":"01SI042","n":2},{"c":"06SI012","n":2},{"c":"06SI046","n":2},{"c":"01MT010","n":1},{"c":"20NX006","n":1},{"c":"05SH014","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Borden</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>qK9glayGZ5epQctvwehXPI9r5oRK7o06vZ6d6XJXNy_B35V-NIfKnsbD6sbg9oW4vlzESUqjtMEecA</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>CECACBIEAYAQQAITAEEAIGADAECAQGJ2AYAQCBBUAEBQCAQBAQAQUAIIAEMAEAIBAEPAIBIEAIFA4GIBAIAQCFRK</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05PZ006","n":3},{"c":"08FR019","n":3},{"c":"08PZ024","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ058","n":3},{"c":"01PZ052","n":2},{"c":"03FR002","n":2},{"c":"04FR010","n":2},{"c":"08FR024","n":2},{"c":"01FR001","n":2},{"c":"01FR030","n":2},{"c":"05PZ002","n":2},{"c":"05PZ010","n":2},{"c":"05PZ014","n":2},{"c":"05PZ025","n":2},{"c":"02FR001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>mbrookz</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>iMQDykjthqoztGrFSrHwtphL2pV9BIrGgAz1EIFDSRHTboYbSYy9SPFPyLCvPzq3i5PdNMVJIeWEiA</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>CIEQCAIADUAQEAAGAECAAAYBAUAAYAIGAYOQCBQEBAAQOAAFAEEAABQEAYAAMCQVDQBACAIABIAQMABAAA</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01DE029","n":3},{"c":"02DE006","n":3},{"c":"04DE003","n":3},{"c":"05DE012","n":3},{"c":"06BW029","n":3},{"c":"06PZ008","n":3},{"c":"07DE005","n":3},{"c":"08DE006","n":3},{"c":"06DE006","n":3},{"c":"06DE010","n":3},{"c":"06DE021","n":3},{"c":"06DE028","n":3},{"c":"01DE010","n":2},{"c":"06DE032","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Mzhkm</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>wKRwXzXitOo8tiys3ThWEcY6NOqbxCgRL6LZa2_S69LCgiqhZdeCqkDtBim83OCOSHJ0lI82rvz5uA</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>CQDQCAICFEAQCBBUAEBQEFABAMCAWAIGAQJACBYCBMAQSAR2A4AQCARRAEBAEBIBAUCBSAIGAQVACCAKAYAQQAQKAIDQEEIUAMAQKBBGAEDAEIABA4BAS</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F32|Freljord|Ionia|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO041","n":3},{"c":"01PZ052","n":3},{"c":"03IO020","n":3},{"c":"03PZ011","n":3},{"c":"06PZ018","n":3},{"c":"07IO011","n":3},{"c":"09IO058","n":3},{"c":"01IO049","n":2},{"c":"02IO005","n":2},{"c":"05PZ025","n":2},{"c":"06PZ042","n":2},{"c":"08BC006","n":2},{"c":"08IO010","n":2},{"c":"07IO017","n":2},{"c":"07IO020","n":2},{"c":"01SI004","n":1},{"c":"38FR006","n":1},{"c":"02F32001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>hungrylouna129</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>4DksskDtcvxtt8JMYwyNMjIIbmau_tz4KwUT-zwcbizxUo3ZMm990UGyxvJ8PHKAEDre0lfPtNGyMw</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAIFGEAQQAY4AMCAKBBWG4BQQBIHFEVAKBQFCQNSAJZOAAAQCBQFFU</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Noxus|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI049","n":3},{"c":"08NX028","n":3},{"c":"04SI004","n":3},{"c":"04SI054","n":3},{"c":"04SI055","n":3},{"c":"08SI007","n":3},{"c":"08SI041","n":3},{"c":"08SI042","n":3},{"c":"06SI020","n":3},{"c":"06SI027","n":3},{"c":"06SI032","n":3},{"c":"06SI039","n":3},{"c":"06SI046","n":3},{"c":"01BW005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>NotreDammit</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Ik2qUvSnwi86IeXEu5fiNj4mTgE6LR2fHlKi_J1gS05olorTm2il2QpyaTh-gdM17lDLdfXLjcZ3lw</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>CQBQCBAFGYAQMBIUAIEAKBZJAYAQSCQUAEEQKDICAECQCMICAYCSKLQCBACSKKQEAQCQIBJVG4CACBAFHAAQKCT7AEDAKJYBA4CQU</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F127|Freljord|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04SI054","n":3},{"c":"06SI020","n":3},{"c":"08SI007","n":3},{"c":"08SI041","n":3},{"c":"09BC020","n":2},{"c":"09SI013","n":2},{"c":"01SI001","n":2},{"c":"01SI049","n":2},{"c":"06SI037","n":2},{"c":"06SI046","n":2},{"c":"08SI037","n":2},{"c":"08SI042","n":2},{"c":"04SI004","n":2},{"c":"04SI005","n":2},{"c":"04SI053","n":2},{"c":"04SI055","n":2},{"c":"01PZ005","n":1},{"c":"56FR005","n":1},{"c":"10F127001","n":1},{"c":"06SI039","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1772,16 +1772,20 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>2</v>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Borden</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>317</v>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>317.0</t>
+        </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1798,20 +1802,30 @@
           <t>Freljord|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>5.1</v>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>43.6</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1830,16 +1844,20 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>5</v>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>mbrookz</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>237</v>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1856,11 +1874,15 @@
           <t>Bilgewater|Demacia|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>14</v>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
@@ -1878,16 +1900,20 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
-        <v>8</v>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Mzhkm</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>198</v>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1904,11 +1930,15 @@
           <t>Bandle City|F32|Freljord|Ionia|Piltover &amp; Zaun|Shadow Isles</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>18</v>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
@@ -1926,16 +1956,20 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>12</v>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>hungrylouna129</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>160</v>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1952,11 +1986,15 @@
           <t>Bilgewater|Noxus|Shadow Isles</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>14</v>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
@@ -1974,16 +2012,20 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
-        <v>14</v>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>NotreDammit</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
-        <v>146</v>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -2000,11 +2042,15 @@
           <t>Bandle City|F127|Freljord|Piltover &amp; Zaun|Shadow Isles</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>20</v>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
@@ -2016,6 +2062,198 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Evilkyatt</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>VIhWFnBFEMr4EV5Wso7qWAXeLXjX7AsH9jGXBsQMzElxqWDkmhYduySwqjiw2LKgm8Vl4x7vCePEVA</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>CIEACAIEFUAQKAAMAEDAMHIBA4AAKAIIAAFACCAJAMBAMAAVDQBAMBAIEYBQCAQAAIAQIAADAIDAABQKAIAQKBBGAEDAAGA</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ045","n":3},{"c":"05DE012","n":3},{"c":"06BW029","n":3},{"c":"07DE005","n":3},{"c":"08DE010","n":3},{"c":"08MT003","n":3},{"c":"06DE021","n":3},{"c":"06DE028","n":3},{"c":"06PZ008","n":3},{"c":"06PZ038","n":3},{"c":"02DE002","n":2},{"c":"04DE003","n":2},{"c":"06DE006","n":2},{"c":"06DE010","n":2},{"c":"01SI004","n":1},{"c":"38FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Im Bard Out</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Yz3vZckMMsL-Dws1t-3XJfGXMMs6-aF_NVmV38P_BTavVKVSeopCEa87wrihIzczQX0FLehUySyTFw</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>CUCQCAYECMAQMCRLAEDQYDYBBEAQUAQBAEEBABQBAEBSEAIBAQKACAQBAMAQQBAZAEEQODACAQDTCOYIAEAQAMIBAEASWAIBAICQCAIFEUAQEBQKAEBQSJYBAQAQ6AIGAEKQ</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F43|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shurima</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03PZ019","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"09FR010","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01NX034","n":2},{"c":"01PZ020","n":2},{"c":"02FR003","n":2},{"c":"08PZ025","n":2},{"c":"09SH012","n":2},{"c":"04SH049","n":2},{"c":"04SH059","n":2},{"c":"01FR000","n":1},{"c":"49FR001","n":1},{"c":"01F43001","n":1},{"c":"01IO005","n":1},{"c":"01FR005","n":1},{"c":"37FR002","n":1},{"c":"06BC001","n":1},{"c":"03MT039","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>waitimplaying</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>_azDPaOzvLiVWYOIu_tqeRsKBR8jGB0PqWIwKWT4Q7tkGYQL315DorDP9xtQYmJXyLKmpxH_bxvxjA</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>CECQCBAABAAQMARDAEDQABICAEBCAKYDAEAASGQ5AUAQEAABAEBQADQBAQAAEAIGAAYACCAAAYCQCAYAAYAQGAQJAEDAEJQBBAAAUAQBAISTC</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|F08|Freljord|Ionia|Mount Targon|Noxus</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04DE008","n":3},{"c":"06IO035","n":3},{"c":"07DE005","n":3},{"c":"01IO032","n":3},{"c":"01IO043","n":3},{"c":"01DE009","n":3},{"c":"01DE026","n":3},{"c":"01DE029","n":3},{"c":"02DE001","n":2},{"c":"03DE014","n":2},{"c":"04DE002","n":2},{"c":"06DE048","n":2},{"c":"08DE006","n":2},{"c":"01NX000","n":1},{"c":"06FR003","n":1},{"c":"02MT001","n":1},{"c":"06IO038","n":1},{"c":"01F08000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>iNilesD</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>wyBqeP-e5g-DWGj1HtegH7itQvt6v4ICyf548MkkPS2eOQAg1oZuz0NOBM3NpzMY4X3b_j_0lyxQ8g</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>CMDQCAIEGQAQGBADAECQOFQBAYDTAAIIAQEQEBAEAIDQIBAHE4WU63IDAEDQICIBBABQYAIIAQEACAIIAQBA</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>F08|Noxus|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ052","n":3},{"c":"03PZ003","n":3},{"c":"05SH022","n":3},{"c":"06SH048","n":3},{"c":"08PZ009","n":3},{"c":"04PZ002","n":3},{"c":"04PZ007","n":3},{"c":"04SH039","n":3},{"c":"04SH045","n":3},{"c":"04SH079","n":3},{"c":"04SH109","n":3},{"c":"07PZ009","n":2},{"c":"08NX012","n":2},{"c":"08PZ008","n":2},{"c":"01F08004","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2068,16 +2068,20 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
-        <v>16</v>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Evilkyatt</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
-        <v>141</v>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -2094,11 +2098,15 @@
           <t>Bilgewater|Demacia|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>16</v>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
@@ -2116,16 +2124,20 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
-        <v>18</v>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Im Bard Out</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
-        <v>135</v>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -2142,11 +2154,15 @@
           <t>Bandle City|F43|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shurima</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>21</v>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
@@ -2164,16 +2180,20 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
-        <v>24</v>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>waitimplaying</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
-        <v>124</v>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2190,11 +2210,15 @@
           <t>Demacia|F08|Freljord|Ionia|Mount Targon|Noxus</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>18</v>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
@@ -2212,16 +2236,20 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
-        <v>29</v>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>iNilesD</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
-        <v>100</v>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -2238,11 +2266,15 @@
           <t>F08|Noxus|Piltover &amp; Zaun|Shurima</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>15</v>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
@@ -2254,6 +2286,256 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>DrChekhov42</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1c4nwBwSyv5F1x83lL5dfhKFmmilYJSGA5t0If7XkaoDeMUcqouHaokbFO8-2k5ClT0A1DDCqeWjkw</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>CQDACBQFEAAQOBICAEEAABQBBECQ4AQJBIARIAYBAEFREJQCAIAQKAIDAQAQCAIHDYVACAIBAUOQ</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06SI032","n":3},{"c":"07SI002","n":3},{"c":"08DE006","n":3},{"c":"09SI014","n":3},{"c":"09BC001","n":3},{"c":"09BC020","n":3},{"c":"01FR011","n":3},{"c":"01FR018","n":3},{"c":"01FR038","n":3},{"c":"01SI001","n":2},{"c":"01SI003","n":2},{"c":"01FR001","n":2},{"c":"01FR007","n":2},{"c":"01FR030","n":2},{"c":"01FR042","n":2},{"c":"01FR005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Carrot Spirit</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>NF9ZwowvSyBz45YcetDzIlsyVLSXCW7enL4zTVyKjr2XKr2XBFWy1fc_CdtXAjFtiOBxXQRJAYTRUA</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAQDAMAQMCQ2AEDAGKIBBEFAWBABAMBAYKBXAQCQUBZJUMA2MAICAEAQGGIBAUFHIAA</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Noxus</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02NX003","n":3},{"c":"06BC026","n":3},{"c":"06NX041","n":3},{"c":"09BC011","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01NX055","n":3},{"c":"05BC007","n":3},{"c":"05BC041","n":3},{"c":"05BC163","n":3},{"c":"05BC166","n":3},{"c":"01NX025","n":2},{"c":"05BC116","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Davebo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>VLKpCAmlUM3NEPhfXqQhNpavrwVpFqBTl0XhrDvMARySiqz6PJyEtbCAExJgF-KsxVkqbVZgpxDFSQ</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>CEDACBYECEAQQAITAEEAIGACAEAQIHQDAUCAEBQOAQAQICAZGQ5ACAIBAEVAEAIBAEAQCBABBI</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>midrange</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"07PZ017","n":3},{"c":"08FR019","n":3},{"c":"08PZ024","n":3},{"c":"01FR004","n":3},{"c":"01FR030","n":3},{"c":"05PZ002","n":3},{"c":"05PZ006","n":3},{"c":"05PZ014","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"01PZ058","n":3},{"c":"01FR042","n":2},{"c":"01FR001","n":1},{"c":"01FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Scilla</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>vwIBeem3KeMHt2DXT689hGEUoZwydZ1S7q2GcWLHvl4GxNDmaxHhI4X25Rx9afLQ0Z4io5Xm3dC2-A</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>CEAAAAICAAAAMJY</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Demacia</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02DE000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Keldog</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1CKHt5W262OqVUahdjh11tOI_iLOClJy8SS9v3HT9RIEWsSJ40CQAUPI_xtuajXdOFC7cdvA3xsd3A</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCBACBYAQMAQJAEDAKDYBBECQ2AQBAUKROBIBAEBASAIHAUBACCAFFEBAMBIMFYBQCBIBAQVAGAIJBIKAEAIFAMOQGBQFA4HBA</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Mount Targon|Noxus|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04IO014","n":3},{"c":"06IO009","n":3},{"c":"06SI015","n":3},{"c":"09SI013","n":3},{"c":"01SI021","n":3},{"c":"01SI023","n":3},{"c":"01IO009","n":2},{"c":"07SI002","n":2},{"c":"08SI041","n":2},{"c":"06SI012","n":2},{"c":"06SI046","n":2},{"c":"01SI001","n":2},{"c":"01SI004","n":2},{"c":"01SI042","n":2},{"c":"01MT010","n":1},{"c":"20IO001","n":1},{"c":"05NX029","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2292,16 +2292,20 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
-        <v>34</v>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>DrChekhov42</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
-        <v>100</v>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -2318,11 +2322,15 @@
           <t>Bandle City|Demacia|Freljord|Shadow Isles</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>16</v>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
@@ -2340,16 +2348,20 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
-        <v>37</v>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Carrot Spirit</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
-        <v>100</v>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -2366,11 +2378,15 @@
           <t>Bandle City|Noxus</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>14</v>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
@@ -2388,16 +2404,20 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n">
-        <v>39</v>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Davebo</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
-        <v>99</v>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -2414,20 +2434,30 @@
           <t>Freljord|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>12.5</v>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2446,16 +2476,20 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>42</v>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Scilla</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
-        <v>80</v>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -2472,11 +2506,15 @@
           <t>Demacia</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>1</v>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
@@ -2494,16 +2532,20 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
-        <v>44</v>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Keldog</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n">
-        <v>65</v>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -2520,11 +2562,15 @@
           <t>Ionia|Mount Targon|Noxus|Shadow Isles</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>17</v>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
@@ -2536,6 +2582,536 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>ANG3L</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>64T_QJuxrjgymcgVU_WRi83XMzxl5n3CFbhCLnEpra1r8axDA_rRCCP2Lvk2rIRx-TL7jn-FAfdNqQ</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>CIDACBYJBEAQQAI6AIDACJBJAIEASAY7AMAQCDBBFICAGCIOCVLWIAABAEBQCFQ</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Mount Targon|Noxus</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"07MT009","n":3},{"c":"08FR030","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"08MT003","n":3},{"c":"08MT031","n":3},{"c":"01FR012","n":3},{"c":"01FR033","n":3},{"c":"01FR042","n":3},{"c":"03MT014","n":3},{"c":"03MT021","n":3},{"c":"03MT087","n":3},{"c":"03MT100","n":3},{"c":"01NX001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Scilla</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>426.0</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>vwIBeem3KeMHt2DXT689hGEUoZwydZ1S7q2GcWLHvl4GxNDmaxHhI4X25Rx9afLQ0Z4io5Xm3dC2-A</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>CEAAAAICAAAAMJY</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Demacia</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02DE000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Borden</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>398.0</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>qK9glayGZ5epQctvwehXPI9r5oRK7o06vZ6d6XJXNy_B35V-NIfKnsbD6sbg9oW4vlzESUqjtMEecA</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAIBCYAQEAYFAEEACGABBABRGBABAMJRIGJGAMAQCAIFAEDACJYDAEBQ6JJHAUAQMAIYAEDAGGQBA4AQQAIIAEJQEBADBAHQ</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F08|F26|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"02NX005","n":3},{"c":"08FR024","n":3},{"c":"08NX019","n":3},{"c":"01NX019","n":3},{"c":"01NX020","n":3},{"c":"01NX025","n":3},{"c":"01NX038","n":3},{"c":"01FR005","n":2},{"c":"06FR039","n":2},{"c":"01NX015","n":2},{"c":"01NX037","n":2},{"c":"01NX039","n":2},{"c":"01BW001","n":1},{"c":"24FR006","n":1},{"c":"03F26001","n":1},{"c":"07FR008","n":1},{"c":"01F08001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>mbrookz</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>372.0</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>iMQDykjthqoztGrFSrHwtphL2pV9BIrGgAz1EIFDSRHTboYbSYy9SPFPyLCvPzq3i5PdNMVJIeWEiA</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>CUCQCAYECMAQMCRLAEDQYDYBBEDQYAQBAEEBABIBAEARSAIBAMRACAIECQAQEAIDAECAO3ILAEAQAMIBAEBAKAIBAUSQCAQGBIAQGCJHAECACDYBAUFIYAIBAYARKAIIAQMQCCIBBIBAIBZRHM</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F21|F39|Freljord|Ionia|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03PZ019","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"09SH012","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01FR025","n":2},{"c":"01NX034","n":2},{"c":"01PZ020","n":2},{"c":"02FR003","n":2},{"c":"04SH109","n":2},{"c":"01FR000","n":1},{"c":"49FR001","n":1},{"c":"02SI001","n":1},{"c":"01SI037","n":1},{"c":"01IO006","n":1},{"c":"10FR003","n":1},{"c":"09F39001","n":1},{"c":"04FR015","n":1},{"c":"01SI010","n":1},{"c":"140FR006","n":1},{"c":"01F21001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Barbaronte</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>9a2qB8uTMNBKODgBHYOYsiFBKF34wGbJqeLclag9IqdLeNQMkyJqQ0bKJX8uos1ZzoXkuPnf2YM41Q</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>CUCQCAIECQAQEAIDAEDAUKYBA4GA6AQBAEEBABIBAEARSAIEAEHQCBQJFMAQSAIKAMBQSDJTKUEACAIAGEAQCAQFAEAQGIQBAECSKAIDBETQCAYECMAQMAIVAEDASIY</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F39|Freljord|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ020","n":3},{"c":"02FR003","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01FR025","n":2},{"c":"04FR015","n":2},{"c":"06MT043","n":2},{"c":"09FR010","n":2},{"c":"03MT013","n":2},{"c":"03MT051","n":2},{"c":"03MT085","n":2},{"c":"01FR000","n":1},{"c":"49FR001","n":1},{"c":"02SI001","n":1},{"c":"01NX034","n":1},{"c":"01FR005","n":1},{"c":"37FR003","n":1},{"c":"09F39001","n":1},{"c":"03PZ019","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>hungrylouna129</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>4DksskDtcvxtt8JMYwyNMjIIbmau_tz4KwUT-zwcbizxUo3ZMm990UGyxvJ8PHKAEDre0lfPtNGyMw</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>CECACAIDEEBAQAITDABQCAIWEYUQGBADAQEA6BABAEBR6AIDAEBACBQBCIBQCAILDYVACAIBAMZQ</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX033","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01FR041","n":3},{"c":"04NX004","n":3},{"c":"04NX008","n":3},{"c":"04NX015","n":3},{"c":"01NX031","n":2},{"c":"03FR002","n":2},{"c":"06FR018","n":2},{"c":"01FR011","n":2},{"c":"01FR030","n":2},{"c":"01FR042","n":2},{"c":"01FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>cloite</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>S5FeQ_9nYTSQwyzmssTeHjZtfnkDOY3-IkDlNjCoY-lrZ1-TX6gxgYaqnpjF5OIyCnEyB_-uuFMDVg</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>CEDACBQAGAAQMARDAEEQENICAEAASIACAQAAGCADAEBBGIBRAQAQCAA2AEAQEJIBAQAAEAIIAADAEAIBAA2ACBACBU</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06DE048","n":3},{"c":"06IO035","n":3},{"c":"09IO053","n":3},{"c":"01DE009","n":3},{"c":"01DE032","n":3},{"c":"04DE003","n":3},{"c":"04DE008","n":3},{"c":"01IO019","n":3},{"c":"01IO032","n":3},{"c":"01IO049","n":3},{"c":"01DE026","n":2},{"c":"01IO037","n":2},{"c":"04DE002","n":2},{"c":"08DE006","n":2},{"c":"01FR000","n":1},{"c":"52FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Mzhkm</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>wKRwXzXitOo8tiys3ThWEcY6NOqbxCgRL6LZa2_S69LCgiqhZdeCqkDtBim83OCOSHJ0lI82rvz5uA</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>CEBQCCABCMBQKBACAYHAIAIEBAMTIOQGAEBQCAQBAMCAWAIEAEFACBIEBIAQQBAYAIAQCBBKAIAQCAI6AEEACGA</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08FR019","n":3},{"c":"05PZ002","n":3},{"c":"05PZ006","n":3},{"c":"05PZ014","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"01PZ058","n":3},{"c":"03FR002","n":2},{"c":"03PZ011","n":2},{"c":"04FR010","n":2},{"c":"05PZ010","n":2},{"c":"08PZ024","n":2},{"c":"01FR004","n":2},{"c":"01FR042","n":2},{"c":"01FR001","n":1},{"c":"30FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>ZequiSlo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>sDHVIztIwYIUMUMQMbtW8_F0xNYe4ZkpSBHW9D2r8pxioi2rKuddbjA33gjylSaOO6jIvO4FCZQXRg</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>CEBAEBIEAYHAIAIEBAMTIOQFAECACCQBBACBQAQFAQBAUAQIAEJRQBABAECBMHRKAIAQCAIBAECACDA</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05PZ006","n":3},{"c":"05PZ014","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"01PZ058","n":3},{"c":"04FR010","n":2},{"c":"08PZ024","n":2},{"c":"05PZ002","n":2},{"c":"05PZ010","n":2},{"c":"08FR019","n":2},{"c":"08FR024","n":2},{"c":"01FR004","n":2},{"c":"01FR022","n":2},{"c":"01FR030","n":2},{"c":"01FR042","n":2},{"c":"01FR001","n":1},{"c":"01FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Thir</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>PSn5jNtfV5cPKB1w5tU3K4_C3dNJ9MQC0F7qfI93H6EPCuf1SM32zjIn7YY3xzuflYfagd4d7Fr5gg</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>CIDACBAGBUAQKBQBAEDAMHQCAMESGWACAYEQQIYDAIDBQKBXAQAQEBQJAEBQSDIBAQEQKAIGBEIQCAQGBEDCW</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04BW013","n":3},{"c":"05BW001","n":3},{"c":"06BW030","n":3},{"c":"03MT035","n":3},{"c":"03MT088","n":3},{"c":"06MT008","n":3},{"c":"06MT035","n":3},{"c":"02BW024","n":3},{"c":"02BW040","n":3},{"c":"02BW055","n":3},{"c":"02BW009","n":2},{"c":"03MT013","n":2},{"c":"04MT005","n":2},{"c":"06MT017","n":2},{"c":"02BW009","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2868,16 +2868,20 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
-        <v>16</v>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>hungrylouna129</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
-        <v>266</v>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>266.0</t>
+        </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -2894,11 +2898,15 @@
           <t>Freljord|Noxus</t>
         </is>
       </c>
-      <c r="H43" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>16</v>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
@@ -2916,16 +2924,20 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
-        <v>23</v>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>cloite</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
-        <v>184</v>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>184.0</t>
+        </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -2942,11 +2954,15 @@
           <t>Demacia|Freljord|Ionia</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>16</v>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
@@ -2964,16 +2980,20 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
-        <v>26</v>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Mzhkm</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
-        <v>173</v>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>173.0</t>
+        </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -2990,11 +3010,15 @@
           <t>Freljord|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>17</v>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
@@ -3012,16 +3036,20 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
-        <v>28</v>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>ZequiSlo</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
-        <v>158</v>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -3038,20 +3066,30 @@
           <t>Freljord|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>12.5</v>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3070,16 +3108,20 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
-        <v>31</v>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Thir</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
-        <v>154</v>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -3096,11 +3138,15 @@
           <t>Bilgewater|Mount Targon</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>15</v>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
@@ -3112,6 +3158,246 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>waitimplaying</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>_azDPaOzvLiVWYOIu_tqeRsKBR8jGB0PqWIwKWT4Q7tkGYQL315DorDP9xtQYmJXyLKmpxH_bxvxjA</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAYBAIAQQAIYAIAQCFRGAIAQGHZBAMCAGAQEB4CACBADBAAQMAI4AEEACEYDAEAQCCY6AEAQQAAG</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>F08|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03FR002","n":3},{"c":"08FR024","n":3},{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"04NX002","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"04NX008","n":2},{"c":"06FR028","n":2},{"c":"08FR019","n":2},{"c":"01FR001","n":2},{"c":"01FR011","n":2},{"c":"01FR030","n":2},{"c":"01F08000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>PirataDoDavila</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Xb_TdoxL4oP0ryHVyoAfdih7QCTf2cN13JQwZgkYuFuqm_Qv5D45sI2qRBrRPzWspxrHy4EzSpFnYQ</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCAYFBYAQIAQOAECQEGQBAYCRAAIIAILQCCIFBUCACAQGCENTSAQBAECTCAYGAUOCKJQBAIDAKAYP</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Ionia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03SI014","n":3},{"c":"04IO014","n":3},{"c":"05IO026","n":3},{"c":"06SI016","n":3},{"c":"08IO023","n":3},{"c":"09SI013","n":3},{"c":"01IO006","n":3},{"c":"01IO017","n":3},{"c":"01IO027","n":3},{"c":"01IO057","n":3},{"c":"01SI049","n":2},{"c":"06SI028","n":2},{"c":"06SI037","n":2},{"c":"06SI038","n":2},{"c":"02BW005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>MarioBat</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>LfF_0N00I--nj6QsgNhJxuiuZ920FYOhYtM2t9oHdiPMyKLXruSjpjn7QMj2ydxhN_cXaPVOKLKfvA</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAYFBUAQOBICAEEQUFABBECQ2AYGAUUC2LQGAECQCAYOCAPDKAABAEAQKDY</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03SI013","n":3},{"c":"07SI002","n":3},{"c":"09BC020","n":3},{"c":"09SI013","n":3},{"c":"06SI040","n":3},{"c":"06SI045","n":3},{"c":"06SI046","n":3},{"c":"01SI001","n":3},{"c":"01SI003","n":3},{"c":"01SI014","n":3},{"c":"01SI016","n":3},{"c":"01SI030","n":3},{"c":"01SI053","n":3},{"c":"01FR005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Evilkyatt</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>VIhWFnBFEMr4EV5Wso7qWAXeLXjX7AsH9jGXBsQMzElxqWDkmhYduySwqjiw2LKgm8Vl4x7vCePEVA</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>CIEACAIEFUAQKAAMAEDAMHIBA4AAKAIIAAFACCAJAMBAMAAVDQBAMBAIEYBQCAQAAIAQIAADAIDAABQKAIAQKBBGAEDAAGA</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ045","n":3},{"c":"05DE012","n":3},{"c":"06BW029","n":3},{"c":"07DE005","n":3},{"c":"08DE010","n":3},{"c":"08MT003","n":3},{"c":"06DE021","n":3},{"c":"06DE028","n":3},{"c":"06PZ008","n":3},{"c":"06PZ038","n":3},{"c":"02DE002","n":2},{"c":"04DE003","n":2},{"c":"06DE006","n":2},{"c":"06DE010","n":2},{"c":"01SI004","n":1},{"c":"38FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>SrdasParanga</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>A6p0IhoXbKSbKc-2OXF6DXbe0qG3fpxRZCpsYFt1DN6_mDyJLL-Lt1WMvuIRkpGW91CVR0Ta7bAc1Q</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCAIBBQAQCARJAEBQCFQBAMBBGAIGAIWAEBQBEQUQGBYCBMIRIBABAEASUAIFAIDACBQBEYBAOAQTFEAA</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR012","n":3},{"c":"01IO041","n":3},{"c":"03FR022","n":3},{"c":"03IO019","n":3},{"c":"06IO044","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"07IO011","n":3},{"c":"07IO017","n":3},{"c":"07IO020","n":3},{"c":"01FR042","n":2},{"c":"05IO006","n":2},{"c":"06FR038","n":2},{"c":"07IO019","n":2},{"c":"07IO041","n":2}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,12 +443,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -3164,16 +3164,20 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
-        <v>32</v>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>waitimplaying</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
-        <v>149</v>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -3190,11 +3194,15 @@
           <t>F08|Freljord|Noxus</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>16</v>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
@@ -3212,16 +3220,20 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
-        <v>33</v>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>PirataDoDavila</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
-        <v>149</v>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -3238,11 +3250,15 @@
           <t>Bilgewater|Ionia|Shadow Isles</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>15</v>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
@@ -3260,16 +3276,20 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
-        <v>35</v>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>MarioBat</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
-        <v>146</v>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -3286,11 +3306,15 @@
           <t>Bandle City|Freljord|Shadow Isles</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>14</v>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
@@ -3308,16 +3332,20 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>37</v>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Evilkyatt</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
-        <v>141</v>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -3334,11 +3362,15 @@
           <t>Bilgewater|Demacia|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
         </is>
       </c>
-      <c r="H51" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>16</v>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
@@ -3356,16 +3388,20 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>38</v>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>SrdasParanga</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
-        <v>141</v>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -3382,11 +3418,15 @@
           <t>Freljord|Ionia</t>
         </is>
       </c>
-      <c r="H52" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>15</v>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
@@ -3398,6 +3438,934 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Davebo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>VLKpCAmlUM3NEPhfXqQhNpavrwVpFqBTl0XhrDvMARySiqz6PJyEtbCAExJgF-KsxVkqbVZgpxDFSQ</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>CICQCAYEDEBAEBQJDIBQCBBHFU2AGCAGBALRSAYIAQCQQEQAAQAQEBADAECAMEABBADAEAIIAQKA</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F16|Freljord|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03PZ025","n":3},{"c":"02BW009","n":3},{"c":"02BW026","n":3},{"c":"01PZ039","n":3},{"c":"01PZ045","n":3},{"c":"01PZ052","n":3},{"c":"08BW008","n":3},{"c":"08BW023","n":3},{"c":"08BW025","n":3},{"c":"08PZ005","n":3},{"c":"08PZ008","n":3},{"c":"08PZ018","n":3},{"c":"01IO004","n":1},{"c":"03FR004","n":1},{"c":"06F16001","n":1},{"c":"08BW002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Worst Jangle NA</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Jsv9vweO73ILxpP8Pe_6VWshG6-jpMFZxZkQkgI1HIGXjlG7ftk3XiHUN1J0NIXGivYj_x7JyDDa8g</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCAIBCYAQEBROAEEAUAQCAUFAKHICBAARGGAGAECACCQBAYFCQAIGAEMACBYKBEBACAIFFIBAKCVGAHJACAQBAYFBOAQFBIJ5KAI</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"02BW046","n":3},{"c":"08BC002","n":3},{"c":"05BC005","n":3},{"c":"05BC029","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"04FR010","n":2},{"c":"06BC040","n":2},{"c":"06FR024","n":2},{"c":"07BC009","n":2},{"c":"01FR005","n":2},{"c":"01FR042","n":2},{"c":"05BC166","n":2},{"c":"05BC210","n":2},{"c":"01BW010","n":1},{"c":"23IO005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Jøsst</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>XHgsBjE5uwO_L_s6vYm5QzqxMmbjlkVTwRtUnzCdk3V-FSoUuUKB2BdR96DUg93RoTQLjljQ35bjTg</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>CIBQCAYABMAQGCKXAECAADQIAEBQABQBAUAAYAIGAAYACBQJFMAQOAAFAEDQSAYCAEAASGQEAMEQGDRTMQBQCCAJDABQGAAHBAHAGAYJENKFK</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|F08|Mount Targon|Noxus|Shurima</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03DE011","n":3},{"c":"03MT087","n":3},{"c":"04DE014","n":3},{"c":"03DE006","n":2},{"c":"05DE012","n":2},{"c":"06DE048","n":2},{"c":"06MT043","n":2},{"c":"07DE005","n":2},{"c":"07MT003","n":2},{"c":"01DE009","n":2},{"c":"01DE026","n":2},{"c":"03MT003","n":2},{"c":"03MT014","n":2},{"c":"03MT051","n":2},{"c":"03MT100","n":2},{"c":"01F08009","n":1},{"c":"24NX003","n":1},{"c":"00SH008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>superguh</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>TqicWWZomh_rA1Qn7vOBlPdqU3-JB79cAEZHeRK39ZUlLFDVD-yOPZvOAkDOE2V9wqqW_wNtl_RwHA</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBIKGEAQMBBOAIAQINBYAMCQIFQYDEDACAIECAAQGBALAEDQUCIBBEFBIAQFBIA5CAICAUCBWHYCAECAIDYCAUCBKGQ</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC049","n":3},{"c":"06PZ046","n":3},{"c":"01PZ052","n":3},{"c":"01PZ056","n":3},{"c":"05PZ022","n":3},{"c":"05PZ024","n":3},{"c":"05PZ025","n":3},{"c":"01PZ016","n":2},{"c":"03PZ011","n":2},{"c":"07BC009","n":2},{"c":"09BC020","n":2},{"c":"05BC001","n":2},{"c":"05BC209","n":2},{"c":"05PZ027","n":2},{"c":"05PZ031","n":2},{"c":"01PZ004","n":1},{"c":"15IO005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Edgy Dank Memer</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>F74AKcKMmPGOnYg66v1j86wCa8V6a1aGJrZDLcyWZ85FJLfiGjvMJR1wC_Nzsz-vWuaUikoWp-d0eg</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAIFAEAQGAIWAEEACAICAYASIKIDAQCTKNZYAQAQCDAXFI2AEAIBAUOQCBYFAEAA</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI001","n":3},{"c":"03FR022","n":3},{"c":"08FR001","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"04SI053","n":3},{"c":"04SI055","n":3},{"c":"04SI056","n":3},{"c":"01FR012","n":3},{"c":"01FR023","n":3},{"c":"01FR042","n":3},{"c":"01FR052","n":3},{"c":"01SI029","n":2},{"c":"07SI001","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>BGA Clid</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>4-9P1VbSk7i2bErv7Z6CwNg1mTZhRy3kIVpZ75hfxgd8nFwHQn_4kNsnECo-RwsLfvtgVXE4Ozy-TA</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAIEGQAQKAAMAEDAILQCAEACQKQDAUCBMGI2AQAQGBALAEDQABIBBAAAMBAFAQKRQGY7AEBACAA2FE</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ052","n":3},{"c":"05DE012","n":3},{"c":"06PZ046","n":3},{"c":"01DE040","n":3},{"c":"01DE042","n":3},{"c":"05PZ022","n":3},{"c":"05PZ025","n":3},{"c":"05PZ026","n":3},{"c":"03PZ011","n":2},{"c":"07DE005","n":2},{"c":"08DE006","n":2},{"c":"05PZ021","n":2},{"c":"05PZ024","n":2},{"c":"05PZ027","n":2},{"c":"05PZ031","n":2},{"c":"02FR000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Estudante de Mat</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>rUh-MxR_6Nd3cz6xcl8hbvAwoxH_jZHnM-5moWJhC4Xr8z4WEinjVmQNf21wGbqwDytgVuZX_XN4Wg</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>CUFACAIEGYAQEBR4AEBQKBQBAQEQ2AIFAEDACBQCAMAQMAYMAEDAYAQCAIBQGBADAEBQEDBIAAAQCAIDFY</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ054","n":3},{"c":"02BW060","n":3},{"c":"03SI006","n":3},{"c":"04MT013","n":3},{"c":"05FR006","n":3},{"c":"06IO003","n":3},{"c":"06NX012","n":3},{"c":"06RU002","n":3},{"c":"02NX003","n":3},{"c":"02NX004","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Voulge</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>5Ekucr8sZhwq2CAYxc3g9EEZkMPtR8iDm3cOdX2MuZNrTn8fhTXOsvOZnOdVudi0Vu-ev4UavO7kMw</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCAICFMAQEAQJAEBQGAYBBABQWAQGAMGCIAYBAMGA6KAEAYBAGCAODUAACAIGAIHQ</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Ionia|Noxus</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO043","n":3},{"c":"02IO009","n":3},{"c":"03NX003","n":3},{"c":"08NX011","n":3},{"c":"06NX012","n":3},{"c":"06NX036","n":3},{"c":"01NX012","n":3},{"c":"01NX015","n":3},{"c":"01NX040","n":3},{"c":"06IO003","n":3},{"c":"06IO008","n":3},{"c":"06IO014","n":3},{"c":"06IO029","n":3},{"c":"01BW002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Carrot Spirit</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>NF9ZwowvSyBz45YcetDzIlsyVLSXCW7enL4zTVyKjr2XKr2XBFWy1fc_CdtXAjFtiOBxXQRJAYTRUA</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAQDAMAQMCQ2AEDAGKIBBEFAWBABAMBAYKBXAQCQUBZJUMA2MAICAEAQGGIBAUFHIAA</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Noxus</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02NX003","n":3},{"c":"06BC026","n":3},{"c":"06NX041","n":3},{"c":"09BC011","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01NX055","n":3},{"c":"05BC007","n":3},{"c":"05BC041","n":3},{"c":"05BC163","n":3},{"c":"05BC166","n":3},{"c":"01NX025","n":2},{"c":"05BC116","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>ThePeterJ</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>bPnRARyfsq_ASQlcALbXWm_d6QwD_ouVJq3On-6b5BOF7uKYmJ5bnffsS30CviSjGqa7PZgAWQKb1A</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>CECACAIDD4AQQAIYAICAGBAPAMAQCFQ6EYDACAIDEEAQIAYIAEDACEQBBAAAMAIIAEJQGAIBAEFSSAYBAMAQEAIEAMBACBQAAY</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Ionia|Noxus</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX031","n":3},{"c":"08FR024","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"01FR022","n":3},{"c":"01FR030","n":3},{"c":"01FR038","n":3},{"c":"01NX033","n":2},{"c":"04NX008","n":2},{"c":"06FR018","n":2},{"c":"08DE006","n":2},{"c":"08FR019","n":2},{"c":"01FR001","n":2},{"c":"01FR011","n":2},{"c":"01FR041","n":2},{"c":"01NX001","n":1},{"c":"02FR004","n":1},{"c":"03IO001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>DK catmonX</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>bpoOMszo_WlxKnKHIgrSIt2tLo8-wImxEaWLM6K5lD3h_8aVXxLxbNAmKFG-nWUpVs4vaGxe6iYz3w</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBIKXQAQCBQHAUAQOBZOAUCAOAI4J5JWIAQBAQDV2AIFBLDACBQBAECAQAIIBIDAEBAHHOBACAQHBICQ6AYFBINSRJABAMDAOMBRHA</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Ionia|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC188","n":3},{"c":"06SH005","n":3},{"c":"07SH046","n":3},{"c":"04SH001","n":3},{"c":"04SH028","n":3},{"c":"04SH079","n":3},{"c":"04SH083","n":3},{"c":"04SH100","n":3},{"c":"04SH093","n":2},{"c":"05BC198","n":2},{"c":"01FR004","n":1},{"c":"08FR008","n":1},{"c":"10BW002","n":1},{"c":"04SH059","n":1},{"c":"130IO007","n":1},{"c":"10SI015","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Kidrobot123</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>GGgM83nY2yjo8GRYdcY5-_C1fzPnQr8h6htZVFs3CSPZbiBv9fHW5AGWk06pyekwDQTitQueVleKdA</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>CUDACAQBAMAQGBATAEDAUKYBA4GA6AIIAIFAGAIBBAIBSAYBAEBAEAIBAQKACCIBBIEQCAIAGEAQCAZCAEBAMCQBAQAQ6AIEA4YQCBQBCUAQOAQUAEEAIGICAEBAKLQ</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|F34|F49|Freljord|Ionia|Piltover &amp; Zaun|Runeterra|Shurima</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02FR003","n":3},{"c":"03PZ019","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"08IO010","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01FR025","n":3},{"c":"01IO002","n":2},{"c":"01PZ020","n":2},{"c":"09FR010","n":2},{"c":"01FR000","n":1},{"c":"49FR001","n":1},{"c":"03F34001","n":1},{"c":"02BW010","n":1},{"c":"01PZ001","n":1},{"c":"15FR004","n":1},{"c":"07F49001","n":1},{"c":"06FR021","n":1},{"c":"01SH002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>netinho99</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>pv-ejnBJpvr2-uknjMz4mPMiw3R4DenY9PoZl1KIB13JDHHA0bveLZ52rxlSXCMHyWvTBN-0c4ubjw</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>CQDQCBQCEAAQQCQGAEEQOCQCAMBASFACAQDSOSICAYDQKMADBEBC2MZ2AEAQQAQKAIAQCARRAECAO3I</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Ionia|Shurima</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06IO032","n":3},{"c":"08BC006","n":3},{"c":"09SH010","n":3},{"c":"03IO009","n":3},{"c":"03IO020","n":3},{"c":"04SH039","n":3},{"c":"04SH073","n":3},{"c":"06SH005","n":3},{"c":"06SH048","n":3},{"c":"09IO045","n":3},{"c":"09IO051","n":3},{"c":"09IO058","n":3},{"c":"08IO010","n":2},{"c":"01FR002","n":1},{"c":"49FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Vstorm</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>JpFQzWqtPpJDo8r48y6HblRG0dMn8GhRylC5B7wzHUXJ31GaT8brYA4Uitv1OdWhB1kCmC7JEk8fCg</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>CUDACAIBCYAQMAAGAEDAYCABA4AQSAIIAEMAGBQBAQECOBIBAYABCAIGAEFQCBQFAMAQQAAGAICACCQMAQAQCAIEAEBQCFQBAYBBYAIIAEJQ</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|F22|Freljord|Ionia|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"06DE006","n":3},{"c":"06RU008","n":3},{"c":"07FR009","n":3},{"c":"08FR024","n":3},{"c":"06FR004","n":3},{"c":"06FR008","n":3},{"c":"06FR039","n":3},{"c":"06DE017","n":2},{"c":"06FR011","n":2},{"c":"06SI003","n":2},{"c":"08DE006","n":2},{"c":"04FR010","n":2},{"c":"04FR012","n":2},{"c":"01FR001","n":1},{"c":"04FR003","n":1},{"c":"01F22001","n":1},{"c":"06IO028","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>DrChekhov42</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>1c4nwBwSyv5F1x83lL5dfhKFmmilYJSGA5t0If7XkaoDeMUcqouHaokbFO8-2k5ClT0A1DDCqeWjkw</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>CIEACAIDCQAQCBBUAEBQIBIBAYDB2AIHAMHACBYEBEAQQAYMAMBAGAIHBEBACAYEBMBAKBAYDEBQCAIDFMAQKBBGAIBAGAYI</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F38|Freljord|Noxus|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX020","n":3},{"c":"01PZ052","n":3},{"c":"03PZ005","n":3},{"c":"06BW029","n":3},{"c":"07NX014","n":3},{"c":"07PZ009","n":3},{"c":"08NX012","n":3},{"c":"02NX001","n":3},{"c":"02NX007","n":3},{"c":"02NX009","n":3},{"c":"03PZ011","n":2},{"c":"05PZ024","n":2},{"c":"05PZ025","n":2},{"c":"01FR003","n":1},{"c":"43FR005","n":1},{"c":"04F38002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Sly Red Fox</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>qNGovuOe08n5NBGIEcT_dIfURM1u8IzaHv10QLvx21USMMmEfqS3Pf7tdM7_gh9Hxo-sVjCBaXMUCQ</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAIDFYAQEAYJAEEQUFACAECR2KACAYCQYLQDAYBQYDQ4AMAQCAZLAEAQKMIBAQCTQBABAECSCAIDAMGQCAYFAIAQMBJF</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F13|Freljord|Noxus|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX046","n":3},{"c":"02NX009","n":3},{"c":"09BC020","n":3},{"c":"01SI029","n":3},{"c":"01SI040","n":3},{"c":"06SI012","n":3},{"c":"06SI046","n":3},{"c":"06NX012","n":3},{"c":"06NX014","n":3},{"c":"06NX028","n":3},{"c":"01NX043","n":2},{"c":"01SI049","n":2},{"c":"04SI056","n":2},{"c":"01FR005","n":1},{"c":"33FR003","n":1},{"c":"03F13001","n":1},{"c":"03SI002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>NotreDammit</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Ik2qUvSnwi86IeXEu5fiNj4mTgE6LR2fHlKi_J1gS05olorTm2il2QpyaTh-gdM17lDLdfXLjcZ3lw</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCCAKAUAQQBAYAICQIAQGAIDQUCIUAMAQICAZGQBQCAQEBIAQKBAOAIAQINJ2AQAQKCSGAEDAUGQBAYCCWAQFAQFA2</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F26|Freljord|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08BC005","n":3},{"c":"08PZ024","n":3},{"c":"05PZ002","n":3},{"c":"05PZ006","n":3},{"c":"07BC009","n":3},{"c":"07BC020","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"02PZ010","n":2},{"c":"05PZ014","n":2},{"c":"01PZ053","n":2},{"c":"01PZ058","n":2},{"c":"01SI010","n":1},{"c":"70FR006","n":1},{"c":"10F26001","n":1},{"c":"06PZ043","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4132,16 +4132,20 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
-        <v>96</v>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>netinho99</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
-        <v>74</v>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -4158,11 +4162,15 @@
           <t>Bandle City|Freljord|Ionia|Shurima</t>
         </is>
       </c>
-      <c r="H65" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>15</v>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
@@ -4180,16 +4188,20 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
-        <v>98</v>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Vstorm</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
-        <v>72</v>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -4206,11 +4218,15 @@
           <t>Demacia|F22|Freljord|Ionia|Runeterra|Shadow Isles</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>18</v>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
@@ -4228,16 +4244,20 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>99</v>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>DrChekhov42</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
-        <v>70</v>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -4254,11 +4274,15 @@
           <t>Bilgewater|F38|Freljord|Noxus|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H67" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>16</v>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
@@ -4276,16 +4300,20 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n">
-        <v>103</v>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Sly Red Fox</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
-        <v>63</v>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -4302,11 +4330,15 @@
           <t>Bandle City|F13|Freljord|Noxus|Shadow Isles</t>
         </is>
       </c>
-      <c r="H68" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>17</v>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
@@ -4324,16 +4356,20 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n">
-        <v>110</v>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>NotreDammit</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
-        <v>53</v>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -4350,11 +4386,15 @@
           <t>Bandle City|F26|Freljord|Piltover &amp; Zaun|Shadow Isles</t>
         </is>
       </c>
-      <c r="H69" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>17</v>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
@@ -4366,6 +4406,334 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Im Bard Out</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Yz3vZckMMsL-Dws1t-3XJfGXMMs6-aF_NVmV38P_BTavVKVSeopCEa87wrihIzczQX0FLehUySyTFw</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCAICBEAQIAACAECQADABAYADAAQBAAOSWAQHAACQ4BADAIAQECQRAEBACAQGHEAA</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Ionia</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO009","n":3},{"c":"04DE002","n":3},{"c":"05DE012","n":3},{"c":"06DE048","n":3},{"c":"01DE029","n":3},{"c":"01DE043","n":3},{"c":"07DE005","n":3},{"c":"07DE014","n":3},{"c":"03IO001","n":3},{"c":"03IO002","n":3},{"c":"03IO010","n":3},{"c":"03IO017","n":3},{"c":"01IO006","n":2},{"c":"01IO057","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Kyo1035</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1nAUNIIOPo7lSaGbshYaN3Db-aMceqGvyCbbwClP5lRyYFPTp67mI3nHPjpiQoWcrlMIFTIclO1RLA</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>CECAEAIBCYTAEAIDD4QQECABCMMAGBADAQEA6BABAEBRUAIGAADACBQBCIBAIAYCBIBQCAIBDYAQCAYLAEBQCAQ</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|F11|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"04NX004","n":3},{"c":"04NX008","n":3},{"c":"04NX015","n":3},{"c":"01NX026","n":2},{"c":"06DE006","n":2},{"c":"06FR018","n":2},{"c":"04NX002","n":2},{"c":"04NX010","n":2},{"c":"01FR001","n":1},{"c":"30FR001","n":1},{"c":"03F11001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>gabriel1223</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1WsbtUX9V0m0CYHe8GUY_TGfwxFuO9kepcE4_H4riGZg8gFe-EmFi3WkCuzdZ-FoaTmX5AX3t8UVdQ</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>CUDACAQBAMAQIAIPAEDAUKYBA4GA6AIJAEFAEAIBBAIAMAIBAQKACAIFEUAQGCJHAECQVDABAEDACFIBBACASBYBAEADCAIBAICQCAIDEIAQEBQKAEBQIEYBAQDTCAIIAQMQ</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F19|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02FR003","n":3},{"c":"04FR015","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"09FR010","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01PZ020","n":2},{"c":"01SI037","n":2},{"c":"03MT039","n":2},{"c":"05BC140","n":2},{"c":"06FR021","n":2},{"c":"08PZ009","n":2},{"c":"01FR000","n":1},{"c":"49FR001","n":1},{"c":"02SI001","n":1},{"c":"01NX034","n":1},{"c":"01IO006","n":1},{"c":"10FR003","n":1},{"c":"04F19001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Keldog</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1CKHt5W262OqVUahdjh11tOI_iLOClJy8SS9v3HT9RIEWsSJ40CQAUPI_xtuajXdOFC7cdvA3xsd3A</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>CUDQCBIKDUAQMCJPAEDAYAIBA4FBIAIIAUKQCCIKCQBAMCQLCUCACBIKAEAQMCI5AIDAUHZPAIEAUAQGAIAQMCRLAMCQUEYUWEAQ</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Mount Targon|Noxus|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC029","n":3},{"c":"06MT047","n":3},{"c":"06RU001","n":3},{"c":"07BC020","n":3},{"c":"08SI021","n":3},{"c":"09BC020","n":3},{"c":"06BC011","n":3},{"c":"06BC021","n":3},{"c":"05BC001","n":2},{"c":"06MT029","n":2},{"c":"06BC031","n":2},{"c":"06BC047","n":2},{"c":"08BC002","n":2},{"c":"08BC006","n":2},{"c":"01BW010","n":1},{"c":"43NX005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>DOUBLE A BATTERY</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Zi0ooeaPDWtw0B9w-RjKJY0dQYd5HBm2tsJ7A8KZ8jzmtH8-2iKuFqgrLFsAhewrnQoFgRutqAx-zA</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>CUDQCBQKDIAQMCI5AEDAYAIBBAAAMAIIAEJQEAIBCYUQEBQBCUOAKAICAEBACBQKFQAQMCJPAEEACGACAYARQIABAECACCQ</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Mount Targon|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BC026","n":3},{"c":"06MT029","n":3},{"c":"06RU001","n":3},{"c":"08DE006","n":3},{"c":"08FR019","n":3},{"c":"01FR022","n":3},{"c":"01FR041","n":3},{"c":"06FR021","n":3},{"c":"06FR028","n":3},{"c":"02FR002","n":2},{"c":"06BC044","n":2},{"c":"06MT047","n":2},{"c":"08FR024","n":2},{"c":"06FR024","n":2},{"c":"06FR032","n":2},{"c":"01PZ001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>ANG3L</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>64T_QJuxrjgymcgVU_WRi83XMzxl5n3CFbhCLnEpra1r8axDA_rRCCP2Lvk2rIRx-TL7jn-FAfdNqQ</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>CIDACBYJBEAQQAI6AIDACJBJAIEASAY7AMAQCDBBFICAGCIOCVLWIAABAEBQCFQ</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Mount Targon|Noxus</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"07MT009","n":3},{"c":"08FR030","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"08MT003","n":3},{"c":"08MT031","n":3},{"c":"01FR012","n":3},{"c":"01FR033","n":3},{"c":"01FR042","n":3},{"c":"03MT014","n":3},{"c":"03MT021","n":3},{"c":"03MT087","n":3},{"c":"03MT100","n":3},{"c":"01NX001","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4692,16 +4692,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
-        <v>125</v>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>ANG3L</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
-        <v>3</v>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -4718,11 +4722,15 @@
           <t>Freljord|Mount Targon|Noxus</t>
         </is>
       </c>
-      <c r="H75" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>14</v>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
@@ -4734,6 +4742,246 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Mzhkm</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>511</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>wKRwXzXitOo8tiys3ThWEcY6NOqbxCgRL6LZa2_S69LCgiqhZdeCqkDtBim83OCOSHJ0lI82rvz5uA</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>CEBQCAICFEAQGAIWAIDQECYUBAAQCARRAEBAEBIBAUBAMAIGAIWACBYCCEAQQAITAMDACJBGFECACAIMCQLCUAQBAEAROAIDAIJQ</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO041","n":3},{"c":"03FR022","n":3},{"c":"07IO011","n":3},{"c":"07IO020","n":3},{"c":"01IO049","n":2},{"c":"02IO005","n":2},{"c":"05IO006","n":2},{"c":"06IO044","n":2},{"c":"07IO017","n":2},{"c":"08FR019","n":2},{"c":"06FR036","n":2},{"c":"06FR038","n":2},{"c":"06FR041","n":2},{"c":"01FR012","n":2},{"c":"01FR020","n":2},{"c":"01FR022","n":2},{"c":"01FR042","n":2},{"c":"01FR001","n":1},{"c":"23FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>armroselund</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>487</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>AvHH9Z3PuNMHXtDRIB6qNKFH7fPKoZYur2Tn_8Tcqn9kEVRsfHD85_OqRAdblbmzCO7CndVSWr9dwA</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCAIFGEAQKCT7AEDQUCIDBACQOJJKAYDAKDAQDMOCMLICAEDQKAQBBAFAEAA</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI049","n":3},{"c":"05BC127","n":3},{"c":"07BC009","n":3},{"c":"08SI007","n":3},{"c":"08SI037","n":3},{"c":"08SI042","n":3},{"c":"06SI012","n":3},{"c":"06SI016","n":3},{"c":"06SI027","n":3},{"c":"06SI028","n":3},{"c":"06SI038","n":3},{"c":"06SI045","n":3},{"c":"07SI002","n":2},{"c":"08BC002","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Barbaronte</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>9a2qB8uTMNBKODgBHYOYsiFBKF34wGbJqeLclag9IqdLeNQMkyJqQ0bKJX8uos1ZzoXkuPnf2YM41Q</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAIEGQAQKBAWAEDQUFABBAFAMAQFBIA2MAIEAYFA6EITEACQCAIEAEAQEBAGAECQVNQBAEDAILQBA4FASAA</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ052","n":3},{"c":"05PZ022","n":3},{"c":"07BC020","n":3},{"c":"08BC006","n":3},{"c":"05BC001","n":3},{"c":"05BC166","n":3},{"c":"06BC015","n":3},{"c":"06BC017","n":3},{"c":"06BC019","n":3},{"c":"06BC032","n":3},{"c":"01PZ001","n":2},{"c":"02PZ006","n":2},{"c":"05BC182","n":2},{"c":"06PZ046","n":2},{"c":"07BC009","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Scilla</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>vwIBeem3KeMHt2DXT689hGEUoZwydZ1S7q2GcWLHvl4GxNDmaxHhI4X25Rx9afLQ0Z4io5Xm3dC2-A</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>CEAAAAICAAAAMJY</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Demacia</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02DE000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Borden</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>qK9glayGZ5epQctvwehXPI9r5oRK7o06vZ6d6XJXNy_B35V-NIfKnsbD6sbg9oW4vlzESUqjtMEecA</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>CECAEAIBCYTAEAIDD4QQECABCMMAGBADAICA6AYBAMAQEAIEAMEAEAIBDYUQEAQGAEJBYAYBAEAREKQ</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F28|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"04NX002","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"03FR002","n":2},{"c":"04NX008","n":2},{"c":"01FR030","n":2},{"c":"01FR041","n":2},{"c":"02BW001","n":1},{"c":"18F28003","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4748,16 +4748,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
-        <v>7</v>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Mzhkm</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
-        <v>511</v>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>511.0</t>
+        </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -4774,11 +4778,15 @@
           <t>Freljord|Ionia</t>
         </is>
       </c>
-      <c r="H76" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>19</v>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
@@ -4796,16 +4804,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
-        <v>9</v>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>armroselund</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
-        <v>487</v>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>487.0</t>
+        </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -4822,11 +4834,15 @@
           <t>Bandle City|Shadow Isles</t>
         </is>
       </c>
-      <c r="H77" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>14</v>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
@@ -4844,16 +4860,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n">
-        <v>15</v>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Barbaronte</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
-        <v>410</v>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>410.0</t>
+        </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -4870,11 +4890,15 @@
           <t>Bandle City|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H78" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>15</v>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
@@ -4892,16 +4916,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n">
-        <v>19</v>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Scilla</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
-        <v>376</v>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>376.0</t>
+        </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -4918,11 +4946,15 @@
           <t>Demacia</t>
         </is>
       </c>
-      <c r="H79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>1</v>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
@@ -4940,16 +4972,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n">
-        <v>21</v>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Borden</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
-        <v>373</v>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>373.0</t>
+        </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -4966,11 +5002,15 @@
           <t>Bilgewater|F28|Freljord|Noxus</t>
         </is>
       </c>
-      <c r="H80" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>15</v>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
@@ -4982,6 +5022,246 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>TheDescendedOne</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>wqJCOLzA1vVNBe2YPW9IadtgQ7Zh-na8CkFIUpQYVvqOtpQJRdchMv2NMKd38jhUoG9EZrv8X1TxTw</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>CUEQCAIEAYAQGBQRAECQEBYBAYBRQAIHBIEQCCAKCQAQSCQUAICQUKBRAIDAUDYRAIAQKCUYAEAQOCQPAMAQMCQXAEEAUBQBBAGA4</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Ionia|Noxus|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ006","n":3},{"c":"03BW017","n":3},{"c":"05IO007","n":3},{"c":"06NX024","n":3},{"c":"07BC009","n":3},{"c":"08BC020","n":3},{"c":"09BC020","n":3},{"c":"05BC040","n":3},{"c":"05BC049","n":3},{"c":"06BC015","n":3},{"c":"06BC017","n":3},{"c":"05BC152","n":2},{"c":"07BC015","n":2},{"c":"01BW010","n":1},{"c":"23FR008","n":1},{"c":"10BW001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Vstorm</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>JpFQzWqtPpJDo8r48y6HblRG0dMn8GhRylC5B7wzHUXJ31GaT8brYA4Uitv1OdWhB1kCmC7JEk8fCg</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>CUDACAIBCYAQMAAGAEDAYCABA4AQSAIIAEMAGBQBAQECOBIBAYABCAIGAEFQCBQFAMAQQAAGAICACCQMAQAQCAIEAEBQCFQBAYBBYAIIAEJQ</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|F22|Freljord|Ionia|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"06DE006","n":3},{"c":"06RU008","n":3},{"c":"07FR009","n":3},{"c":"08FR024","n":3},{"c":"06FR004","n":3},{"c":"06FR008","n":3},{"c":"06FR039","n":3},{"c":"06DE017","n":2},{"c":"06FR011","n":2},{"c":"06SI003","n":2},{"c":"08DE006","n":2},{"c":"04FR010","n":2},{"c":"04FR012","n":2},{"c":"01FR001","n":1},{"c":"04FR003","n":1},{"c":"01F22001","n":1},{"c":"06IO028","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>hungrylouna129</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4DksskDtcvxtt8JMYwyNMjIIbmau_tz4KwUT-zwcbizxUo3ZMm990UGyxvJ8PHKAEDre0lfPtNGyMw</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>CIDQCBAGBUAQKBQBAEDAMHQBBEDBYAQDBERVQAQGBEECGBACAYERQKBXAEAQGCINAEBAMCIGFM</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04BW013","n":3},{"c":"05BW001","n":3},{"c":"06BW030","n":3},{"c":"09BW028","n":3},{"c":"03MT035","n":3},{"c":"03MT088","n":3},{"c":"06MT008","n":3},{"c":"06MT035","n":3},{"c":"02BW009","n":3},{"c":"02BW024","n":3},{"c":"02BW040","n":3},{"c":"02BW055","n":3},{"c":"03MT013","n":2},{"c":"02BW009","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>mbrookz</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>iMQDykjthqoztGrFSrHwtphL2pV9BIrGgAz1EIFDSRHTboYbSYy9SPFPyLCvPzq3i5PdNMVJIeWEiA</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>CUBQEBAAAQEAEBQAFMYAMAIAAQDBIIREE4BACBAAA4BQCAAKBQNAEAIHAACQCCAMBY</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Shurima</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04DE004","n":3},{"c":"04DE008","n":3},{"c":"06DE043","n":3},{"c":"06DE048","n":3},{"c":"01DE004","n":3},{"c":"01DE006","n":3},{"c":"01DE020","n":3},{"c":"01DE034","n":3},{"c":"01DE036","n":3},{"c":"01DE039","n":3},{"c":"04DE007","n":2},{"c":"01DE010","n":2},{"c":"01DE012","n":2},{"c":"01DE026","n":2},{"c":"01SH000","n":1},{"c":"05FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>SrdasParanga</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>A6p0IhoXbKSbKc-2OXF6DXbe0qG3fpxRZCpsYFt1DN6_mDyJLL-Lt1WMvuIRkpGW91CVR0Ta7bAc1Q</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCAIBBQAQCARJAEBQCFQBAMBBGAIGAIWAEBQBEQUQGBYCBMIRIBABAEASUAIFAIDACBQBEYBAOAQTFEAA</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR012","n":3},{"c":"01IO041","n":3},{"c":"03FR022","n":3},{"c":"03IO019","n":3},{"c":"06IO044","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"07IO011","n":3},{"c":"07IO017","n":3},{"c":"07IO020","n":3},{"c":"01FR042","n":2},{"c":"05IO006","n":2},{"c":"06FR038","n":2},{"c":"07IO019","n":2},{"c":"07IO041","n":2}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5028,16 +5028,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n">
-        <v>26</v>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>TheDescendedOne</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
-        <v>312</v>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>312.0</t>
+        </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -5054,11 +5058,15 @@
           <t>Bandle City|Bilgewater|Freljord|Ionia|Noxus|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H81" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>16</v>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
@@ -5076,16 +5084,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n">
-        <v>27</v>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Vstorm</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
-        <v>304</v>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>304.0</t>
+        </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -5102,11 +5114,15 @@
           <t>Demacia|F22|Freljord|Ionia|Runeterra|Shadow Isles</t>
         </is>
       </c>
-      <c r="H82" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>18</v>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
@@ -5124,16 +5140,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
-        <v>28</v>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>hungrylouna129</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n">
-        <v>298</v>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -5150,11 +5170,15 @@
           <t>Bilgewater|Mount Targon</t>
         </is>
       </c>
-      <c r="H83" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>14</v>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
@@ -5172,16 +5196,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n">
-        <v>30</v>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>mbrookz</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
-        <v>277</v>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>277.0</t>
+        </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -5198,11 +5226,15 @@
           <t>Demacia|Freljord|Shurima</t>
         </is>
       </c>
-      <c r="H84" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>16</v>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
@@ -5220,16 +5252,20 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n">
-        <v>37</v>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>SrdasParanga</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
-        <v>256</v>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>256.0</t>
+        </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -5246,11 +5282,15 @@
           <t>Freljord|Ionia</t>
         </is>
       </c>
-      <c r="H85" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>15</v>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
@@ -5262,6 +5302,256 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>DeadCraft48</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>z99HH4ScYBXXZOteeWfUZCG8HCbuw6GU_bR16cpV42-T_wUxmAw93ad65iutfh2e_H6c54YCFgxC8Q</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>CUCQCAIECQAQIAIPAEDAUKYBA4GA6AQBAEEBABYBAEARSAIBAMRACAQBAMAQMAIVAEDASIYBBEAQUAQDBEZVKBIBAEADCAIDAQJQCBQJFMAQQBISAIBQSDJD</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F08|F19|Freljord|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ020","n":3},{"c":"04FR015","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01FR025","n":2},{"c":"01NX034","n":2},{"c":"02FR003","n":2},{"c":"06FR021","n":2},{"c":"06MT035","n":2},{"c":"09FR010","n":2},{"c":"03MT051","n":2},{"c":"03MT085","n":2},{"c":"01FR000","n":1},{"c":"49FR003","n":1},{"c":"04F19001","n":1},{"c":"06MT043","n":1},{"c":"01F08005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Fathermitch</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>u9P21YdI4OIKc24Y0pF-80wnRRaEBUDTLOJ0i0GI8KLbG_AFSLJkG97OBNPX-I4XWtnnhjdRtGPZtg</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>CEAAAAICAAAAMJY</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Demacia</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02DE000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>iNilesD</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>wyBqeP-e5g-DWGj1HtegH7itQvt6v4ICyf548MkkPS2eOQAg1oZuz0NOBM3NpzMY4X3b_j_0lyxQ8g</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>CQEACAYCAIAQGBAFAECAIEABAUCBSAIGBINACBYEAUBAKCSOSEAQIAIEBQUC2NABAIAQIHBGAA</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03IO002","n":3},{"c":"03PZ005","n":3},{"c":"04PZ016","n":3},{"c":"05PZ025","n":3},{"c":"06BC026","n":3},{"c":"07PZ005","n":3},{"c":"05BC078","n":3},{"c":"05BC145","n":3},{"c":"01PZ012","n":3},{"c":"01PZ040","n":3},{"c":"01PZ045","n":3},{"c":"01PZ052","n":3},{"c":"01PZ028","n":2},{"c":"01PZ038","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Thir</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>PSn5jNtfV5cPKB1w5tU3K4_C3dNJ9MQC0F7qfI93H6EPCuf1SM32zjIn7YY3xzuflYfagd4d7Fr5gg</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>CIDACBAGBUAQKBQBAEDAMHQCAMESGWACAYEQQIYDAIDBQKBXAQAQEBQJAEBQSDIBAQEQKAIGBEIQCAQGBEDCW</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04BW013","n":3},{"c":"05BW001","n":3},{"c":"06BW030","n":3},{"c":"03MT035","n":3},{"c":"03MT088","n":3},{"c":"06MT008","n":3},{"c":"06MT035","n":3},{"c":"02BW024","n":3},{"c":"02BW040","n":3},{"c":"02BW055","n":3},{"c":"02BW009","n":2},{"c":"03MT013","n":2},{"c":"04MT005","n":2},{"c":"06MT017","n":2},{"c":"02BW009","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>superguh</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>TqicWWZomh_rA1Qn7vOBlPdqU3-JB79cAEZHeRK39ZUlLFDVD-yOPZvOAkDOE2V9wqqW_wNtl_RwHA</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBIKGEAQMBBOAIAQINBYAMCQIFQYDEDACAIECAAQGBALAEDQUCIBBEFBIAQFBIA5CAICAUCBWHYCAECAIDYCAUCBKGQ</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC049","n":3},{"c":"06PZ046","n":3},{"c":"01PZ052","n":3},{"c":"01PZ056","n":3},{"c":"05PZ022","n":3},{"c":"05PZ024","n":3},{"c":"05PZ025","n":3},{"c":"01PZ016","n":2},{"c":"03PZ011","n":2},{"c":"07BC009","n":2},{"c":"09BC020","n":2},{"c":"05BC001","n":2},{"c":"05BC209","n":2},{"c":"05PZ027","n":2},{"c":"05PZ031","n":2},{"c":"01PZ004","n":1},{"c":"15IO005","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5308,16 +5308,20 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n">
-        <v>42</v>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>DeadCraft48</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
-        <v>223</v>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>223.0</t>
+        </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -5334,11 +5338,15 @@
           <t>Bandle City|F08|F19|Freljord|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra</t>
         </is>
       </c>
-      <c r="H86" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>19</v>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
@@ -5356,16 +5364,20 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n">
-        <v>44</v>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Fathermitch</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
-        <v>221</v>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>221.0</t>
+        </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -5382,11 +5394,15 @@
           <t>Demacia</t>
         </is>
       </c>
-      <c r="H87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>1</v>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
@@ -5404,16 +5420,20 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B88" s="2" t="n">
-        <v>45</v>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>iNilesD</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
-        <v>220</v>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -5430,20 +5450,30 @@
           <t>Bandle City|Ionia|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H88" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
@@ -5462,16 +5492,20 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n">
-        <v>47</v>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Thir</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n">
-        <v>220</v>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -5488,11 +5522,15 @@
           <t>Bilgewater|Mount Targon</t>
         </is>
       </c>
-      <c r="H89" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>15</v>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
@@ -5510,16 +5548,20 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n">
-        <v>49</v>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>superguh</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
-        <v>216</v>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>216.0</t>
+        </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -5536,11 +5578,15 @@
           <t>Bandle City|Ionia|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H90" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>17</v>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
@@ -5552,6 +5598,1064 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>ThePeterJ</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>bPnRARyfsq_ASQlcALbXWm_d6QwD_ouVJq3On-6b5BOF7uKYmJ5bnffsS30CviSjGqa7PZgAWQKb1A</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>CUEACAICFYAQGAQFAECAIBYBAUFCQAIGAIQACBQMAYAQOAQRAMBAEAIDBEBQCAIBDUAQCARRAEBQEFAEAEAQIHABAQAQUAIGAQVQCBQHFI</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Ionia|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO046","n":3},{"c":"03IO005","n":3},{"c":"04PZ007","n":3},{"c":"05BC040","n":3},{"c":"06IO032","n":3},{"c":"06RU006","n":3},{"c":"07IO017","n":3},{"c":"02IO001","n":3},{"c":"02IO003","n":3},{"c":"02IO009","n":3},{"c":"01FR029","n":2},{"c":"01IO049","n":2},{"c":"03IO020","n":2},{"c":"01FR004","n":1},{"c":"28FR004","n":1},{"c":"01BC001","n":1},{"c":"06PZ043","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>waitimplaying</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>202.0</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>_azDPaOzvLiVWYOIu_tqeRsKBR8jGB0PqWIwKWT4Q7tkGYQL315DorDP9xtQYmJXyLKmpxH_bxvxjA</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAYBAIAQQAIYAIAQCFRGAIAQGHZBAMCAGAQEB4CACBADBAAQMAI4AEEACEYDAEAQCCY6AEAQQAAG</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>F08|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03FR002","n":3},{"c":"08FR024","n":3},{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"04NX002","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"04NX008","n":2},{"c":"06FR028","n":2},{"c":"08FR019","n":2},{"c":"01FR001","n":2},{"c":"01FR011","n":2},{"c":"01FR030","n":2},{"c":"01F08000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>NotreDammit</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>191.0</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Ik2qUvSnwi86IeXEu5fiNj4mTgE6LR2fHlKi_J1gS05olorTm2il2QpyaTh-gdM17lDLdfXLjcZ3lw</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAICBEAQIAQOAEDAECIBBECQ2AQGAUBSMAYBAUKROKQEAEBAKCIBAMBBIAQGAILSEAQGAUHSKAIBAUBBK</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO009","n":3},{"c":"04IO014","n":3},{"c":"06IO009","n":3},{"c":"09SI013","n":3},{"c":"06SI003","n":3},{"c":"06SI038","n":3},{"c":"01SI021","n":3},{"c":"01SI023","n":3},{"c":"01SI042","n":3},{"c":"02SI009","n":2},{"c":"03IO020","n":2},{"c":"06IO023","n":2},{"c":"06IO034","n":2},{"c":"06SI015","n":2},{"c":"06SI037","n":2},{"c":"01SI002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Luiscantera99</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>186.0</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>VKXBpD0UOEbAyh-Hqcmb7jChhZwESsnQ_Aw-310se0znEl_Kea6E3Ad-ShOCK8jxe63sQt7orajPBA</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBIKP4AQMAAGAEEASAYFBEFACAYMBUKAMAIBAANACAQAAEAQKCRRAECQADABA4FASAQJBICBEAQBAUFACAIJAAWQ</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Mount Targon|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC127","n":3},{"c":"06DE006","n":3},{"c":"08MT003","n":3},{"c":"09BC001","n":3},{"c":"09BC003","n":3},{"c":"09BC012","n":3},{"c":"09BC013","n":3},{"c":"09BC020","n":3},{"c":"01DE026","n":2},{"c":"02DE001","n":2},{"c":"05BC049","n":2},{"c":"05DE012","n":2},{"c":"07BC009","n":2},{"c":"09BC004","n":2},{"c":"09BC018","n":2},{"c":"01SI010","n":1},{"c":"01FR009","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Cameron6659</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>s3CY7jSkZBQc86Ss1XF-SgYAOH2gRTkLFFJKmMEldlkC21ECHBkfmaZpIbdNiDzVl0WMpmQN2gJdgQ</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAIFGEAQKCT7AEDAUFICAQCTMNYDBACQOKJKAQDAKFA3FUXAEAIEAU4ACBIKAEAA</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI049","n":3},{"c":"05BC127","n":3},{"c":"06BC021","n":3},{"c":"04SI054","n":3},{"c":"04SI055","n":3},{"c":"08SI007","n":3},{"c":"08SI041","n":3},{"c":"08SI042","n":3},{"c":"06SI020","n":3},{"c":"06SI027","n":3},{"c":"06SI045","n":3},{"c":"06SI046","n":3},{"c":"04SI056","n":2},{"c":"05BC001","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Davebo</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>VLKpCAmlUM3NEPhfXqQhNpavrwVpFqBTl0XhrDvMARySiqz6PJyEtbCAExJgF-KsxVkqbVZgpxDFSQ</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>CICQCAYEDEBAEBQJDIBQCBBHFU2AGCAGBALRSAYIAQCQQEQAAQAQEBADAECAMEABBADAEAIIAQKA</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F16|Freljord|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03PZ025","n":3},{"c":"02BW009","n":3},{"c":"02BW026","n":3},{"c":"01PZ039","n":3},{"c":"01PZ045","n":3},{"c":"01PZ052","n":3},{"c":"08BW008","n":3},{"c":"08BW023","n":3},{"c":"08BW025","n":3},{"c":"08PZ005","n":3},{"c":"08PZ008","n":3},{"c":"08PZ018","n":3},{"c":"01IO004","n":1},{"c":"03FR004","n":1},{"c":"06F16001","n":1},{"c":"08BW002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>사생아</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>173.0</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>F9OZ_-Flq3owGOinq4MYVL8t93hZaWUFRndpsIhOr3j6-D0AQ8hBsrbWEm6hyFMIECkayDR6omW6iA</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>CUDQCBQGDIAQMAAKAEDAEGIBAYBSEAIGAQEACBQFAYBAMBYEAUCACBQCEIAQMCJIAIDACERCAIDAYBI2AQAQMCQ4AEDAEFYBAYEQMAIGA4UA</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|F23|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BW026","n":3},{"c":"06DE010","n":3},{"c":"06IO025","n":3},{"c":"06NX034","n":3},{"c":"06PZ008","n":3},{"c":"06SI006","n":3},{"c":"06SH004","n":3},{"c":"06SH005","n":3},{"c":"06IO034","n":2},{"c":"06MT040","n":2},{"c":"06FR018","n":2},{"c":"06FR034","n":2},{"c":"06RU005","n":2},{"c":"06RU026","n":2},{"c":"01BW010","n":1},{"c":"28FR006","n":1},{"c":"02F23001","n":1},{"c":"06MT006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>killerbag</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>173.0</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>K-AwhCnag9qI4C9bqIB6NQKreWjCPnsFermvHAEOS3BU4FFSydQqt1XvE_qZ9jJKO7N36aIwrjngkw</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>CICACBACBUBACAQTEABAMARDEYCQGAQBAIFBCEQDAEBQEFABAYER2AQBAISTCAQBAMBAOAIGBEDA</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia|Mount Targon|Noxus</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04IO013","n":3},{"c":"01IO019","n":3},{"c":"01IO032","n":3},{"c":"06IO035","n":3},{"c":"06IO038","n":3},{"c":"03IO001","n":3},{"c":"03IO002","n":3},{"c":"03IO010","n":3},{"c":"03IO017","n":3},{"c":"03IO018","n":3},{"c":"03IO020","n":2},{"c":"06MT029","n":2},{"c":"01IO037","n":2},{"c":"01IO049","n":2},{"c":"01NX002","n":1},{"c":"07FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Capuchones</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>172.0</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>ifBVSokXCUevq11fz_t-WfI4tgfBPZ0daZyY0XOtuQfwc8fJmtQnoN-KX0Ug1PTRmc_LSClYeEl1yQ</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>CECQCBQBDQBACAY7EEBAIAYEB4BAQAITDABQCAIWDYTAIAIBAECACBADBAAQMAAGAEEAABQCAEAQCKQBAYARE</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06FR028","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"01FR022","n":3},{"c":"01FR030","n":3},{"c":"01FR038","n":3},{"c":"01FR004","n":2},{"c":"04NX008","n":2},{"c":"06DE006","n":2},{"c":"08DE006","n":2},{"c":"01FR001","n":1},{"c":"42FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>MarioBat</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>LfF_0N00I--nj6QsgNhJxuiuZ920FYOhYtM2t9oHdiPMyKLXruSjpjn7QMj2ydxhN_cXaPVOKLKfvA</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>CQDACBIABQAQMAAGAEDQUCIBBAEQGAQFBIYX6BAJBIAQGBAUAQAQCAA2AEBAAAIBAUFACAQJBIGA2AA</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05DE012","n":3},{"c":"06DE006","n":3},{"c":"07BC009","n":3},{"c":"08MT003","n":3},{"c":"05BC049","n":3},{"c":"05BC127","n":3},{"c":"09BC001","n":3},{"c":"09BC003","n":3},{"c":"09BC004","n":3},{"c":"09BC020","n":3},{"c":"01DE026","n":2},{"c":"02DE001","n":2},{"c":"05BC001","n":2},{"c":"09BC012","n":2},{"c":"09BC013","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Ghostmatterz</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>FOFXozF37zF8ilqEEn08-AAA9YqkzualzgQIwpR5WHUO021_-F3_y3-QBYiFsoK9UOH4ia6jaUnWHQ</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAQCAUAQIAQOAEDAECIBBECQ2BABAUFBKFZKAQDAKAYPEYXACAIBAUBQCAQGAUSS2</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Ionia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02IO005","n":3},{"c":"04IO014","n":3},{"c":"06IO009","n":3},{"c":"09SI013","n":3},{"c":"01SI010","n":3},{"c":"01SI021","n":3},{"c":"01SI023","n":3},{"c":"01SI042","n":3},{"c":"06SI003","n":3},{"c":"06SI015","n":3},{"c":"06SI038","n":3},{"c":"06SI046","n":3},{"c":"01SI003","n":2},{"c":"02BW005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Evilkyatt</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>VIhWFnBFEMr4EV5Wso7qWAXeLXjX7AsH9jGXBsQMzElxqWDkmhYduySwqjiw2LKgm8Vl4x7vCePEVA</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>CIEACAIEFUAQKAAMAEDAMHIBA4AAKAIIAAFACCAJAMBAMAAVDQBAMBAIEYBQCAQAAIAQIAADAIDAABQKAIAQKBBGAEDAAGA</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ045","n":3},{"c":"05DE012","n":3},{"c":"06BW029","n":3},{"c":"07DE005","n":3},{"c":"08DE010","n":3},{"c":"08MT003","n":3},{"c":"06DE021","n":3},{"c":"06DE028","n":3},{"c":"06PZ008","n":3},{"c":"06PZ038","n":3},{"c":"02DE002","n":2},{"c":"04DE003","n":2},{"c":"06DE006","n":2},{"c":"06DE010","n":2},{"c":"01SI004","n":1},{"c":"38FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>AlphaCake</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>9hQmUSqOhNgk3nMQHq2u7g6YKk8wcs7RdPoL5G3f6a3O6KH-u5YPm2MfHRdCO-zSb_e9It9BWKj1Gg</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAYCAIAQMCQ2AEDQIBIBBEFAWAQFBJHJCAIEAECAYKBNGQCACAIEEYAQGBAFAECAIEABA4FASAQBAECACAIHBIIA</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03IO002","n":3},{"c":"06BC026","n":3},{"c":"07PZ005","n":3},{"c":"09BC011","n":3},{"c":"05BC078","n":3},{"c":"05BC145","n":3},{"c":"01PZ012","n":3},{"c":"01PZ040","n":3},{"c":"01PZ045","n":3},{"c":"01PZ052","n":3},{"c":"01PZ038","n":2},{"c":"03PZ005","n":2},{"c":"04PZ016","n":2},{"c":"07BC009","n":2},{"c":"01FR004","n":1},{"c":"01FR007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Habalji</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>jfnUt6y1Tud4BT3rCl4OXpIZGpctBroR3bp6tCwZ83M-Im7W6-uPa5aI5wbitvlUfUYZymuVhePwNA</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAQDAMAQMCQ2AEDAGKIBBEFAWBABAMBAYKBXAUCQUBZJOSRQDJQBAAAQCAIDDE</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02NX003","n":3},{"c":"06BC026","n":3},{"c":"06NX041","n":3},{"c":"09BC011","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01NX055","n":3},{"c":"05BC007","n":3},{"c":"05BC041","n":3},{"c":"05BC116","n":3},{"c":"05BC163","n":3},{"c":"05BC166","n":3},{"c":"01FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>BGA Clid</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4-9P1VbSk7i2bErv7Z6CwNg1mTZhRy3kIVpZ75hfxgd8nFwHQn_4kNsnECo-RwsLfvtgVXE4Ozy-TA</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAIEGQAQKAAMAEDAILQCAEACQKQDAUCBMGI2AQAQGBALAEDQABIBBAAAMBAFAQKRQGY7AEBACAA2FE</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ052","n":3},{"c":"05DE012","n":3},{"c":"06PZ046","n":3},{"c":"01DE040","n":3},{"c":"01DE042","n":3},{"c":"05PZ022","n":3},{"c":"05PZ025","n":3},{"c":"05PZ026","n":3},{"c":"03PZ011","n":2},{"c":"07DE005","n":2},{"c":"08DE006","n":2},{"c":"05PZ021","n":2},{"c":"05PZ024","n":2},{"c":"05PZ027","n":2},{"c":"05PZ031","n":2},{"c":"02FR000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Lambz369</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>kmHJ0fiFL5KAEXQIbr0iiqfUVOoezx8N8Xx1SigEyzXFLzPC4T4GYF10KXmpZ_8G_qQxrT7t4I3TyQ</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>CICQCBAFB4AQMBJLAEEAKHQCAICQQCQFAIDBOLBPGU4AGAICAYTQCBQGEYAQOBICAMAQCBIBAEBAKBYCAIDB2HQ</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04SI015","n":3},{"c":"06SI043","n":3},{"c":"08SI030","n":3},{"c":"02SI008","n":3},{"c":"02SI010","n":3},{"c":"02BW023","n":3},{"c":"02BW044","n":3},{"c":"02BW047","n":3},{"c":"02BW053","n":3},{"c":"02BW056","n":3},{"c":"02BW039","n":2},{"c":"06BW038","n":2},{"c":"07SI002","n":2},{"c":"01FR005","n":1},{"c":"01FR002","n":1},{"c":"05SH002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>netinho99</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>pv-ejnBJpvr2-uknjMz4mPMiw3R4DenY9PoZl1KIB13JDHHA0bveLZ52rxlSXCMHyWvTBN-0c4ubjw</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>CMDQCAIEFYAQGBADAECAOJYBAUCBQAIGAQVACCAEBEBQMBYFGA4AIAIDAQFQCBAHHMAQOBAJAEEAGDAEAEAQILIBAQCAEAIEA5WQEBQEBETA</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia|Noxus|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ046","n":3},{"c":"03PZ003","n":3},{"c":"04SH039","n":3},{"c":"05PZ024","n":3},{"c":"06PZ042","n":3},{"c":"08PZ009","n":3},{"c":"06SH005","n":3},{"c":"06SH048","n":3},{"c":"06SH056","n":3},{"c":"03PZ011","n":2},{"c":"04SH059","n":2},{"c":"07PZ009","n":2},{"c":"08NX012","n":2},{"c":"01FR004","n":1},{"c":"45FR004","n":1},{"c":"04IO001","n":1},{"c":"04SH109","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Worst Jangle NA</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Jsv9vweO73ILxpP8Pe_6VWshG6-jpMFZxZkQkgI1HIGXjlG7ftk3XiHUN1J0NIXGivYj_x7JyDDa8g</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>CUCACAIADIAQQAYDAIBQAAQLAIEAADIZAYAQKAAMAEDAAMABBADQ4AQIAAFBUAQIBEBR4AYDAABQQDQCAEBQABYBBAGA4</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Mount Targon|Noxus|Shurima</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01DE026","n":3},{"c":"08NX003","n":3},{"c":"03DE002","n":3},{"c":"03DE011","n":3},{"c":"08DE013","n":3},{"c":"08DE025","n":3},{"c":"05DE012","n":2},{"c":"06DE048","n":2},{"c":"08SH014","n":2},{"c":"08DE010","n":2},{"c":"08DE026","n":2},{"c":"08MT003","n":2},{"c":"08MT030","n":2},{"c":"03DE003","n":2},{"c":"03DE008","n":2},{"c":"03DE014","n":2},{"c":"01NX000","n":1},{"c":"07FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Griefamere</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>3oeJRVQ8Ka1pd5I4A0MMBdd-pHnUQyUBA5F7AgIdRuZStwgFOk9VXQh0DTxq_fM6AOIvFeANRYqXjg</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>CUFACAIEGYAQEBR4AEBQKBQBAQEQ2AIFAEDACBQCAMAQMAYMAEDAYAQCAIBQGBADAEBQEDBIAAAQCAIDFY</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ054","n":3},{"c":"02BW060","n":3},{"c":"03SI006","n":3},{"c":"04MT013","n":3},{"c":"05FR006","n":3},{"c":"06IO003","n":3},{"c":"06NX012","n":3},{"c":"06RU002","n":3},{"c":"02NX003","n":3},{"c":"02NX004","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6460,16 +6460,20 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B106" s="2" t="n">
-        <v>101</v>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Lambz369</t>
         </is>
       </c>
-      <c r="D106" s="2" t="n">
-        <v>124</v>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -6486,11 +6490,15 @@
           <t>Bilgewater|Freljord|Shadow Isles|Shurima</t>
         </is>
       </c>
-      <c r="H106" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>16</v>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
@@ -6508,16 +6516,20 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B107" s="2" t="n">
-        <v>104</v>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>netinho99</t>
         </is>
       </c>
-      <c r="D107" s="2" t="n">
-        <v>121</v>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -6534,11 +6546,15 @@
           <t>Freljord|Ionia|Noxus|Piltover &amp; Zaun|Shurima</t>
         </is>
       </c>
-      <c r="H107" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>17</v>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
@@ -6556,16 +6572,20 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B108" s="2" t="n">
-        <v>108</v>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Worst Jangle NA</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n">
-        <v>115</v>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -6582,11 +6602,15 @@
           <t>Demacia|Freljord|Mount Targon|Noxus|Shurima</t>
         </is>
       </c>
-      <c r="H108" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>18</v>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
@@ -6604,16 +6628,20 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B109" s="2" t="n">
-        <v>109</v>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Griefamere</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n">
-        <v>115</v>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -6630,29 +6658,289 @@
           <t>Bilgewater|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
         </is>
       </c>
-      <c r="H109" s="2" t="n">
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ054","n":3},{"c":"02BW060","n":3},{"c":"03SI006","n":3},{"c":"04MT013","n":3},{"c":"05FR006","n":3},{"c":"06IO003","n":3},{"c":"06NX012","n":3},{"c":"06RU002","n":3},{"c":"02NX003","n":3},{"c":"02NX004","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Level 5 Vegan</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>gGhQinkdAxnN2dov4wW-SyA-bFirpyYlLtwCg8mYeuB5DswHB7pTdlPql-jxmv554GKZF4qKYpYKiQ</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>CMCQCBQHGAAQOBYJAEEQOCQCAUDQ4EQIAQDQGDI4EUTDWSCMAAAQCBAHHY</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="I109" s="2" t="n">
+      <c r="I110" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J109" s="2" t="n">
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06SH048","n":3},{"c":"07SH009","n":3},{"c":"09SH010","n":3},{"c":"05SH014","n":3},{"c":"05SH018","n":3},{"c":"04SH003","n":3},{"c":"04SH013","n":3},{"c":"04SH028","n":3},{"c":"04SH037","n":3},{"c":"04SH038","n":3},{"c":"04SH059","n":3},{"c":"04SH072","n":3},{"c":"04SH076","n":3},{"c":"01PZ007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky1Striker </t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>z7pM5LeiAfXJjAoYrbnYFkXCM_pO8BbpNEzD7hGg9en0Ar_f_nyxTaIzsr4hVo0G5fgiEbsowIVgFg</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>CECAEAIDD4QQEBADAQHQECABCMMAIAIBCYPCMKIEAECAGCABAYAAMAIGAEJACCAAAYBACAIBFIAQIAYC</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"01FR022","n":3},{"c":"01FR030","n":3},{"c":"01FR038","n":3},{"c":"01FR041","n":3},{"c":"04NX008","n":2},{"c":"06DE006","n":2},{"c":"06FR018","n":2},{"c":"08DE006","n":2},{"c":"01FR001","n":1},{"c":"42FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Pheonixwish</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>cl8N9ojUtJZiDT3O4PII8zqeD1XLqjcacmSQPybLp6_NhNfzUjCHa9AyCDJ7wMuZ2tuWVfO9G3G9pQ</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCBACBYAQKAQ2AEDAGFABA4BDCAQJAMMSCAYBAIDBCGQDAEBRSGZKAIAQCAQ3AEBQEFAA</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Noxus</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04IO014","n":3},{"c":"05IO026","n":3},{"c":"06NX020","n":3},{"c":"07IO049","n":3},{"c":"09NX025","n":3},{"c":"09NX033","n":3},{"c":"01IO006","n":3},{"c":"01IO017","n":3},{"c":"01IO026","n":3},{"c":"01NX025","n":3},{"c":"01NX027","n":3},{"c":"01NX042","n":3},{"c":"01IO027","n":2},{"c":"03IO020","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Estudante de Mat</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>rUh-MxR_6Nd3cz6xcl8hbvAwoxH_jZHnM-5moWJhC4Xr8z4WEinjVmQNf21wGbqwDytgVuZX_XN4Wg</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>CUFACAIEGYAQEBR4AEBQKBQBAQEQ2AIFAEDACBQCAMAQMAYMAEDAYAQCAIBQGBADAEBQEDBIAAAQCAIDFY</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J113" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="K109" s="2" t="n">
+      <c r="K113" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="L109" s="2" t="n">
+      <c r="L113" s="2" t="n">
         <v>7.5</v>
       </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="M113" s="2" t="inlineStr">
         <is>
           <t>aggro</t>
         </is>
       </c>
-      <c r="N109" s="2" t="inlineStr">
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>[{"c":"01PZ054","n":3},{"c":"02BW060","n":3},{"c":"03SI006","n":3},{"c":"04MT013","n":3},{"c":"05FR006","n":3},{"c":"06IO003","n":3},{"c":"06NX012","n":3},{"c":"06RU002","n":3},{"c":"02NX003","n":3},{"c":"02NX004","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>MeteorB</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>KUXM-ICBFTnIpm4YMs2UrWQmQeU2UvU0wz-StZbw8-vCUyeU2-e8t_yF6_qNMzx6Z5zFDzQPuISVfg</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>CUDQCAIFFQAQGAAEAEBQCCQBAQAQ4AIIAEAQEAIBBQQQEBQBEQUQIAIDAEJQCBAAAUAQQAQOAIAQCFBKAMAQCARBAECAGBYBBAGA4</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Ionia|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI044","n":3},{"c":"03DE004","n":3},{"c":"03FR010","n":3},{"c":"04FR014","n":3},{"c":"08FR001","n":3},{"c":"01FR012","n":3},{"c":"01FR033","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"03FR019","n":2},{"c":"04DE005","n":2},{"c":"08IO014","n":2},{"c":"01FR020","n":2},{"c":"01FR042","n":2},{"c":"01FR002","n":1},{"c":"33FR004","n":1},{"c":"03SH001","n":1}]</t>
         </is>
       </c>
     </row>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N114"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6700,16 +6700,20 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B110" s="2" t="n">
-        <v>114</v>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Level 5 Vegan</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n">
-        <v>111</v>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -6726,11 +6730,15 @@
           <t>Piltover &amp; Zaun|Shurima</t>
         </is>
       </c>
-      <c r="H110" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>14</v>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
@@ -6748,16 +6756,20 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B111" s="2" t="n">
-        <v>122</v>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Sky1Striker </t>
         </is>
       </c>
-      <c r="D111" s="2" t="n">
-        <v>103</v>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -6774,11 +6786,15 @@
           <t>Demacia|Freljord|Noxus</t>
         </is>
       </c>
-      <c r="H111" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>16</v>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
@@ -6796,16 +6812,20 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B112" s="2" t="n">
-        <v>130</v>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Pheonixwish</t>
         </is>
       </c>
-      <c r="D112" s="2" t="n">
-        <v>100</v>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6822,11 +6842,15 @@
           <t>Ionia|Noxus</t>
         </is>
       </c>
-      <c r="H112" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>14</v>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
@@ -6844,16 +6868,20 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B113" s="2" t="n">
-        <v>131</v>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Estudante de Mat</t>
         </is>
       </c>
-      <c r="D113" s="2" t="n">
-        <v>100</v>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -6870,20 +6898,30 @@
           <t>Bilgewater|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
         </is>
       </c>
-      <c r="H113" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>7.5</v>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
@@ -6902,16 +6940,20 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B114" s="2" t="n">
-        <v>132</v>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>MeteorB</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
-        <v>100</v>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -6928,11 +6970,15 @@
           <t>Demacia|Freljord|Ionia|Shadow Isles|Shurima</t>
         </is>
       </c>
-      <c r="H114" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>17</v>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
@@ -6944,6 +6990,1046 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>IntoTheDusk</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4CwfSVAdN4m7p5ScQO8-8LoR-RbodZDyMZoY6W_cpwq64il3FKqEwM99CuJJHDkH1IebNboDNi7OFw</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>CUDACBQGDIAQMAAKAEDAEIQBAYBSEAIGA4CQCBQFAYDQCBQKDQAQMAALAEDAEGICAYAREIQCAYCAOCACAYGAKGQCAYDQIKAA</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Demacia|Freljord|Ionia|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BW026","n":3},{"c":"06DE010","n":3},{"c":"06IO034","n":3},{"c":"06NX034","n":3},{"c":"06SH005","n":3},{"c":"06SI006","n":3},{"c":"06BC028","n":2},{"c":"06DE011","n":2},{"c":"06IO025","n":2},{"c":"06FR018","n":2},{"c":"06FR034","n":2},{"c":"06PZ007","n":2},{"c":"06PZ008","n":2},{"c":"06RU005","n":2},{"c":"06RU026","n":2},{"c":"06SH004","n":2},{"c":"06SH040","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Carrot Spirit</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>NF9ZwowvSyBz45YcetDzIlsyVLSXCW7enL4zTVyKjr2XKr2XBFWy1fc_CdtXAjFtiOBxXQRJAYTRUA</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAQDAMAQMCQ2AEDAGKIBBEFAWBABAMBAYKBXAQCQUBZJUMA2MAICAEAQGGIBAUFHIAA</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Noxus</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02NX003","n":3},{"c":"06BC026","n":3},{"c":"06NX041","n":3},{"c":"09BC011","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01NX055","n":3},{"c":"05BC007","n":3},{"c":"05BC041","n":3},{"c":"05BC163","n":3},{"c":"05BC166","n":3},{"c":"01NX025","n":2},{"c":"05BC116","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>DK catmonX</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>bpoOMszo_WlxKnKHIgrSIt2tLo8-wImxEaWLM6K5lD3h_8aVXxLxbNAmKFG-nWUpVs4vaGxe6iYz3w</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBIKXQAQCBQHAUAQOBZOAUCAOAI4J5JWIAQBAQDV2AIFBLDACBQBAECAQAIIBIDAEBAHHOBACAQHBICQ6AYFBINSRJABAMDAOMBRHA</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Ionia|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC188","n":3},{"c":"06SH005","n":3},{"c":"07SH046","n":3},{"c":"04SH001","n":3},{"c":"04SH028","n":3},{"c":"04SH079","n":3},{"c":"04SH083","n":3},{"c":"04SH100","n":3},{"c":"04SH093","n":2},{"c":"05BC198","n":2},{"c":"01FR004","n":1},{"c":"08FR008","n":1},{"c":"10BW002","n":1},{"c":"04SH059","n":1},{"c":"130IO007","n":1},{"c":"10SI015","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>almiral87</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>vvhYHWysWyfwbYlxI13kS7_y1W2gb2B-ThEFjZjOBJvYIET5Ziji5Te94uWel7CNR2Iv2yjxziOfIg</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>CQCACCIKCQBACBI5GEBAMAYMDQBAMBIMFYCQCAYDBUAQGBICAECAKOACAECQGKACAYBQ4DYDAEDAKDQCAECRGLYCAIBQQCI</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|F19|Ionia|Noxus|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"09BC020","n":3},{"c":"01SI029","n":3},{"c":"01SI049","n":3},{"c":"06NX012","n":3},{"c":"06NX028","n":3},{"c":"06SI012","n":3},{"c":"06SI046","n":3},{"c":"03NX013","n":2},{"c":"03SI002","n":2},{"c":"04SI056","n":2},{"c":"01SI003","n":2},{"c":"01SI040","n":2},{"c":"06NX014","n":2},{"c":"06NX015","n":2},{"c":"01BW005","n":1},{"c":"14IO001","n":1},{"c":"05F19047","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Fouur</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>wXbl3uoZp0uLrS0f2bJs6u81liOtfHnpY0NawKgjhgcqobNu8iaIhiqh-ziz5RYGpRyqBJQh6fa_vg</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>CQBQCAYCCQAQMBAVAEEAICIEAEAQINABA4BAWAIIBIDACCAEBAGQCAIEEEAQEBAGAEBQICYBAQCAOAIFAIDACCAEAIAQSARNAIBAEAYFAICQIGBGAIDAEIBEAMAQEDBJGEBQOAQRCMKAIBQEBEQCWLQ</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|F38|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03IO020","n":3},{"c":"06PZ021","n":3},{"c":"08PZ009","n":3},{"c":"01PZ052","n":2},{"c":"07IO011","n":2},{"c":"08BC006","n":2},{"c":"08PZ008","n":2},{"c":"01FR004","n":1},{"c":"33FR002","n":1},{"c":"04BW001","n":1},{"c":"03PZ011","n":1},{"c":"01PZ004","n":1},{"c":"07FR005","n":1},{"c":"02BW001","n":1},{"c":"08PZ002","n":1},{"c":"01MT002","n":1},{"c":"45IO002","n":1},{"c":"02NX005","n":1},{"c":"02SI004","n":1},{"c":"24F38002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>3XT43M3Special</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>n7k1YnEo9x2wXZd2cwZZfIkgRff0QICb3yvfQQ1IuSY1Rbmbbngu4khrmhDTaIg6z2n3i_aBDucpjA</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAIEGQBAEAQDBEBAGBADAUBAMBAUFMBAQBAIBEBQMAQIBUQAEAIEAQIQCBQCBYAA</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ052","n":3},{"c":"02IO003","n":3},{"c":"02IO009","n":3},{"c":"03PZ003","n":3},{"c":"03PZ005","n":3},{"c":"06PZ020","n":3},{"c":"06PZ043","n":3},{"c":"08PZ008","n":3},{"c":"08PZ009","n":3},{"c":"06IO008","n":3},{"c":"06IO013","n":3},{"c":"06IO032","n":3},{"c":"04PZ017","n":2},{"c":"06IO014","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>S0dier</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>bCKEYS_u5YNUPOotflk8jNBu0lAL3VLN57SYLhXlObTD7urr-0hprm2CEFNFBtqrciyvMUA7PXpgSQ</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>CEBQEBADAQHQGAIDD4QTKBIBAECBMHRGFEBACBADBABQCAIBBMYAEAIBAEVACBQBDQ</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"01NX053","n":3},{"c":"01FR004","n":3},{"c":"01FR022","n":3},{"c":"01FR030","n":3},{"c":"01FR038","n":3},{"c":"01FR041","n":3},{"c":"04NX008","n":2},{"c":"01FR001","n":2},{"c":"01FR011","n":2},{"c":"01FR048","n":2},{"c":"01FR001","n":1},{"c":"42FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Hekix</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>1CK23PwoEcTa2_0pqZAlaghwoqIY-CKPaYOVSgXAZrnqcCXnCghPMpvq9XuQL5Y8ut3x99VigcQ3Lg</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCAYJGMAQKCRJAIAQABAVAMDQABIIBMCQMCIICAIR2HYCAEDAAKIBAYEQMAA</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03MT051","n":3},{"c":"05BC041","n":3},{"c":"01DE004","n":3},{"c":"01DE021","n":3},{"c":"07DE005","n":3},{"c":"07DE008","n":3},{"c":"07DE011","n":3},{"c":"06MT008","n":3},{"c":"06MT016","n":3},{"c":"06MT017","n":3},{"c":"06MT029","n":3},{"c":"06MT031","n":3},{"c":"06DE041","n":2},{"c":"06MT006","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>RunTheNets</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Xl7GjY9cJtPZYQXoOlBrT09ubpsjbRH-flmtUGO67un6CYOPZALBjukopexS3Dx2je2OOCT0c2v28Q</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>CICQCBAFB4AQMBJLAEEAKHQDAICQOCAKAQBAMFZHF42QEAIBAUAQIAQGDUSSYOAA</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>midrange</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04SI015","n":3},{"c":"06SI043","n":3},{"c":"08SI030","n":3},{"c":"02SI007","n":3},{"c":"02SI008","n":3},{"c":"02SI010","n":3},{"c":"02BW023","n":3},{"c":"02BW039","n":3},{"c":"02BW047","n":3},{"c":"02BW053","n":3},{"c":"01SI001","n":2},{"c":"02BW029","n":2},{"c":"02BW037","n":2},{"c":"02BW044","n":2},{"c":"02BW056","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>PirataRJ</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>o7RRQb00403JURN5EPFjCfqSpJNmh2GBn7vh_J49v_i2eFWqMNVUrt6P5D_uYpzIJD_AFV2w6FMOAw</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAIBBQAQCARBAEBAEBICAYASIKIDAMAQMCQWAMDQECYUC4BQCAIBEEAQCARRAEDAEIABAEEAUBQ</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>F08|Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR012","n":3},{"c":"01IO033","n":3},{"c":"02IO005","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"03FR006","n":3},{"c":"03FR010","n":3},{"c":"03FR022","n":3},{"c":"07IO011","n":3},{"c":"07IO020","n":3},{"c":"07IO023","n":3},{"c":"01FR033","n":2},{"c":"01IO049","n":2},{"c":"06IO032","n":2},{"c":"01F08010","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>The Condor Hero</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>cLreYqCgVsM-tdtswOoteDVHRuhSGY5uRv2QIM9DRlHpzvUtaJKwhsuJYOSsJAXdB4wNeH9DRX0Jpw</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>CUEQCAIACMAQCBJMAEBQABABAQAAKAIFAAGACBYABMAQQAAZAEEASAYCAYACQMACAECQACICBAAAMCQEAEAQEIIBAQAAOAIEAMDQCCAMBY</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Mount Targon|Noxus|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01DE019","n":3},{"c":"01SI044","n":3},{"c":"03DE004","n":3},{"c":"04DE005","n":3},{"c":"05DE012","n":3},{"c":"07DE011","n":3},{"c":"08DE025","n":3},{"c":"08MT003","n":3},{"c":"06DE040","n":3},{"c":"06DE048","n":3},{"c":"05DE009","n":2},{"c":"08DE006","n":2},{"c":"08DE010","n":2},{"c":"01FR002","n":1},{"c":"33FR004","n":1},{"c":"00SH001","n":1},{"c":"04NX007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Ning Rookie</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>OGxDo6XQKEGpusz5LMePXYA5srW0Ls7PO_DLzRwrMjqjage_6OLgqFMzEl9OGZP-b9qlxJlPbiR7Jw</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>CECQCBICAYAQMBJOAEDQKCQCBACREKQDAECRGKJRAYAQCBIPAEBAKAIBAMCQYAIIAUUQCCIFBYBAIBIFHAAQEAIFGQ3A</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05IO006","n":3},{"c":"06SI046","n":3},{"c":"07SI010","n":3},{"c":"08SI018","n":3},{"c":"08SI042","n":3},{"c":"01SI019","n":3},{"c":"01SI041","n":3},{"c":"01SI049","n":3},{"c":"01SI015","n":2},{"c":"02SI001","n":2},{"c":"03SI012","n":2},{"c":"08SI041","n":2},{"c":"09SI014","n":2},{"c":"04SI005","n":2},{"c":"04SI056","n":2},{"c":"02FR005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>JulioA619</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>HyM6ouqwRnGB8IMDgZZIKEOIs6uvKx5CcxPRIPkU1-ky9UJ0LIPsERL0vXcQnIL4JxsgpWiu4RXJtw</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>CIDACCAJDAAQSABBAEEQENICAMESGWACAYEQQIYEAEBASFA2GQBACAICGEAQSARXAIAQGAQUAIDASBRU</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Ionia|Mount Targon|Noxus</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08MT024","n":3},{"c":"09DE033","n":3},{"c":"09IO053","n":3},{"c":"03MT035","n":3},{"c":"03MT088","n":3},{"c":"06MT008","n":3},{"c":"06MT035","n":3},{"c":"01IO009","n":3},{"c":"01IO020","n":3},{"c":"01IO026","n":3},{"c":"01IO052","n":3},{"c":"01IO049","n":2},{"c":"09IO055","n":2},{"c":"01NX002","n":1},{"c":"20IO006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>PirataDoDavila</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Xb_TdoxL4oP0ryHVyoAfdih7QCTf2cN13JQwZgkYuFuqm_Qv5D45sI2qRBrRPzWspxrHy4EzSpFnYQ</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCBIKP4AQKAAMAEDAABQBBAEQGBIJBIAQGDANCQCQCAIADIAQEAABAECQUMIBA4FASAIJBIJAGAIFBIAQCCIKAQAQSABN</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC127","n":3},{"c":"05DE012","n":3},{"c":"06DE006","n":3},{"c":"08MT003","n":3},{"c":"09BC001","n":3},{"c":"09BC003","n":3},{"c":"09BC012","n":3},{"c":"09BC013","n":3},{"c":"09BC020","n":3},{"c":"01DE026","n":2},{"c":"02DE001","n":2},{"c":"05BC049","n":2},{"c":"07BC009","n":2},{"c":"09BC018","n":2},{"c":"01SI010","n":1},{"c":"01FR009","n":1},{"c":"10PZ001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Voulge</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>5Ekucr8sZhwq2CAYxc3g9EEZkMPtR8iDm3cOdX2MuZNrTn8fhTXOsvOZnOdVudi0Vu-ev4UavO7kMw</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>CQDQCAIBCYAQEBROAEDACFIBA4FASAIIBIBACCABDABAKCQFDUDACBABBIAQKCWZAEAQMAIYAEEACEYCAEAQKKQCAYFCQLYA</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"02BW046","n":3},{"c":"06FR021","n":3},{"c":"07BC009","n":3},{"c":"08BC002","n":3},{"c":"08FR024","n":3},{"c":"05BC005","n":3},{"c":"05BC029","n":3},{"c":"04FR010","n":2},{"c":"05BC217","n":2},{"c":"06FR024","n":2},{"c":"08FR019","n":2},{"c":"01FR005","n":2},{"c":"01FR042","n":2},{"c":"06BC040","n":2},{"c":"06BC047","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Jef Cabeça</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>TDduUr4WgHBujH1fMopZIGNGL57NG8TpKFDpwbwg_yFVtFxPUi6feBLN8uuefvE_ARQSB9ak6L966w</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>CIBACAYJBEBAGBADBMEQCAYEAUAQICIKAECAIBYBAUCCMAIGBEVQCBQEFYAQQBAJAEEAKEQEAMEROKSW3UAQOAIBAQ2ACAYJLQAQIBARAECQIGIBAYES2AIGAQVQCBYJAE</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>F45|F92|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03MT009","n":3},{"c":"03PZ003","n":3},{"c":"03PZ011","n":3},{"c":"03PZ005","n":2},{"c":"04MT010","n":2},{"c":"04PZ007","n":2},{"c":"05PZ038","n":2},{"c":"06MT043","n":2},{"c":"06PZ046","n":2},{"c":"08PZ009","n":2},{"c":"08SI018","n":2},{"c":"03MT023","n":2},{"c":"03MT042","n":2},{"c":"03MT086","n":2},{"c":"03MT221","n":2},{"c":"01FR004","n":1},{"c":"52FR003","n":1},{"c":"09F92001","n":1},{"c":"04PZ017","n":1},{"c":"01SI004","n":1},{"c":"25FR006","n":1},{"c":"09F45001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>SheIsMad</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>NVGTWcWoUZrD62EzcqD1V22S8pfNh_UkFMV2iGllGTXHoBICJCuu3sU7nY2PkweidD7Jsw8UnHZ9Ww</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAQEBIAQMCQ2AEEAUBICA4FASFADAECAQGJUAMCQIAQGBYBQCAIEGUAQKCSGAEEAIGABAEDAIKY</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02PZ010","n":3},{"c":"06BC026","n":3},{"c":"08BC005","n":3},{"c":"07BC009","n":3},{"c":"07BC020","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"05PZ002","n":3},{"c":"05PZ006","n":3},{"c":"05PZ014","n":3},{"c":"01PZ053","n":2},{"c":"05BC070","n":2},{"c":"08PZ024","n":2},{"c":"01BW004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Kon Quinx</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>fx7diLuT9VhmCIpRc8kUUAPVsC_YfH_wonnX6AQziG2-0lrR9733kl9SQQwginETEbyYXZgbc6xDxg</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>CEEACAICEAAQCAYYAEBQEEQBAQBA2AIEAMCACBQCEMAQMAY2AEEAGEYEAEAQGIIBAMBBCAIEAMHQEBQCBMTAIAICAMBQCBQDCQBACARFGEBAIAYCAM</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>F20|Freljord|Ionia|Noxus</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO032","n":3},{"c":"01NX024","n":3},{"c":"03IO018","n":3},{"c":"04IO013","n":3},{"c":"04NX004","n":3},{"c":"06IO035","n":3},{"c":"06NX026","n":3},{"c":"08NX019","n":3},{"c":"01NX033","n":2},{"c":"03IO017","n":2},{"c":"04NX015","n":2},{"c":"06IO011","n":2},{"c":"06IO038","n":2},{"c":"01IO003","n":1},{"c":"03FR006","n":1},{"c":"03F20002","n":1},{"c":"01IO037","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>DrChekhov42</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>1c4nwBwSyv5F1x83lL5dfhKFmmilYJSGA5t0If7XkaoDeMUcqouHaokbFO8-2k5ClT0A1DDCqeWjkw</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>CIEACAIDCQAQCBBUAEBQIBIBAYDB2AIHAMHACBYEBEAQQAYMAMBAGAIHBEBACAYEBMBAKBAYDEBQCAIDFMAQKBBGAIBAGAYI</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F38|Freljord|Noxus|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX020","n":3},{"c":"01PZ052","n":3},{"c":"03PZ005","n":3},{"c":"06BW029","n":3},{"c":"07NX014","n":3},{"c":"07PZ009","n":3},{"c":"08NX012","n":3},{"c":"02NX001","n":3},{"c":"02NX007","n":3},{"c":"02NX009","n":3},{"c":"03PZ011","n":2},{"c":"05PZ024","n":2},{"c":"05PZ025","n":2},{"c":"01FR003","n":1},{"c":"43FR005","n":1},{"c":"04F38002","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7796,16 +7796,20 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B129" s="2" t="n">
-        <v>193</v>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>Swiss Voulge</t>
         </is>
       </c>
-      <c r="D129" s="2" t="n">
-        <v>87</v>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
@@ -7822,11 +7826,15 @@
           <t>Bandle City|Bilgewater|Freljord</t>
         </is>
       </c>
-      <c r="H129" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>16</v>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
@@ -7844,16 +7852,20 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B130" s="2" t="n">
-        <v>195</v>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Jef Cabeça</t>
         </is>
       </c>
-      <c r="D130" s="2" t="n">
-        <v>85</v>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
@@ -7870,11 +7882,15 @@
           <t>F45|F92|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
         </is>
       </c>
-      <c r="H130" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>22</v>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
@@ -7892,16 +7908,20 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B131" s="2" t="n">
-        <v>202</v>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>SheIsMad</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
-        <v>83</v>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
@@ -7918,11 +7938,15 @@
           <t>Bandle City|Bilgewater|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H131" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>15</v>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
@@ -7940,16 +7964,20 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B132" s="2" t="n">
-        <v>205</v>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>Kon Quinx</t>
         </is>
       </c>
-      <c r="D132" s="2" t="n">
-        <v>83</v>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
@@ -7966,11 +7994,15 @@
           <t>F20|Freljord|Ionia|Noxus</t>
         </is>
       </c>
-      <c r="H132" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>17</v>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
@@ -7988,16 +8020,20 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B133" s="2" t="n">
-        <v>207</v>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>DrChekhov42</t>
         </is>
       </c>
-      <c r="D133" s="2" t="n">
-        <v>81</v>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -8014,11 +8050,15 @@
           <t>Bilgewater|F38|Freljord|Noxus|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H133" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>16</v>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
@@ -8030,6 +8070,266 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>ZequiSlo</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>sDHVIztIwYIUMUMQMbtW8_F0xNYe4ZkpSBHW9D2r8pxioi2rKuddbjA33gjylSaOO6jIvO4FCZQXRg</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>CEBAEBIEAYHAIAIEBAMTIOQFAECACCQBBACBQAQFAQBAUAQIAEJRQBABAECBMHRKAIAQCAIBAECACDA</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05PZ006","n":3},{"c":"05PZ014","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"01PZ058","n":3},{"c":"04FR010","n":2},{"c":"08PZ024","n":2},{"c":"05PZ002","n":2},{"c":"05PZ010","n":2},{"c":"08FR019","n":2},{"c":"08FR024","n":2},{"c":"01FR004","n":2},{"c":"01FR022","n":2},{"c":"01FR030","n":2},{"c":"01FR042","n":2},{"c":"01FR001","n":1},{"c":"01FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>DRredstone1221</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>NocTgROEfKLU_VprskbNwWRB6cyrnpCwLffRWT_3Yi24kPQdklHFGjtSPRww5KHRtz55-22d44GyJQ</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBACB4BACAQIFQBQKCQEGE5AGBICAQKRUBABAEBAWAIGAIQACCICGUBAKAQGDABQCAICEEAQGAQTAECQVNQB</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F19|Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04IO015","n":3},{"c":"01IO008","n":3},{"c":"01IO044","n":3},{"c":"05BC004","n":3},{"c":"05BC049","n":3},{"c":"05BC058","n":3},{"c":"05IO004","n":3},{"c":"05IO021","n":3},{"c":"05IO026","n":3},{"c":"01IO011","n":2},{"c":"06IO032","n":2},{"c":"09IO053","n":2},{"c":"05IO006","n":2},{"c":"05IO024","n":2},{"c":"01FR002","n":1},{"c":"33FR003","n":1},{"c":"02F19001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Sigep0361</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>SqxpFUWSXhjOG2G3E32vacxCUd0CcHXo6WH6NjmXhk8oZFEM5YFrkHiN-YDrizXIw-vz7MQZQinCBw</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>CMCACBQGFUAQMBYFAQCAMAIDAUHQMBAHCMLECRCKKAAQCBAGAIBACBAGA4AQQAYM</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BW045","n":3},{"c":"06SH005","n":3},{"c":"04BW001","n":3},{"c":"04BW003","n":3},{"c":"04BW005","n":3},{"c":"04BW015","n":3},{"c":"04SH019","n":3},{"c":"04SH022","n":3},{"c":"04SH065","n":3},{"c":"04SH068","n":3},{"c":"04SH074","n":3},{"c":"04SH080","n":3},{"c":"04BW002","n":2},{"c":"01PZ006","n":1},{"c":"07FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>MrPapichurris</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>k5Mo2wzvsv69wr-ICakBXkpwPqxDhYBp9bOHGBRzFkYUpEMe6ORsHPlEf_A5xI8kguB54rx9M-WHHQ</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>CECQCBABCMAQQAAKAEEACEYCAEABULIHAEAQCCYSDYTCQKQCAEDACHIBBAARQAA</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>midrange</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04FR019","n":3},{"c":"08DE010","n":3},{"c":"08FR019","n":3},{"c":"01DE026","n":3},{"c":"01DE045","n":3},{"c":"01FR001","n":3},{"c":"01FR011","n":3},{"c":"01FR018","n":3},{"c":"01FR030","n":3},{"c":"01FR038","n":3},{"c":"01FR040","n":3},{"c":"01FR042","n":3},{"c":"06FR029","n":2},{"c":"08FR024","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>gabriel1223</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>1WsbtUX9V0m0CYHe8GUY_TGfwxFuO9kepcE4_H4riGZg8gFe-EmFi3WkCuzdZ-FoaTmX5AX3t8UVdQ</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>CUDACAQBAMAQIAIPAEDAUKYBA4GA6AIJAEFAEAIBBAIAMAIBAQKACAIFEUAQGCJHAECQVDABAEDACFIBBACASBYBAEADCAIBAICQCAIDEIAQEBQKAEBQIEYBAQDTCAIIAQMQ</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F19|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02FR003","n":3},{"c":"04FR015","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"09FR010","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01PZ020","n":2},{"c":"01SI037","n":2},{"c":"03MT039","n":2},{"c":"05BC140","n":2},{"c":"06FR021","n":2},{"c":"08PZ009","n":2},{"c":"01FR000","n":1},{"c":"49FR001","n":1},{"c":"02SI001","n":1},{"c":"01NX034","n":1},{"c":"01IO006","n":1},{"c":"10FR003","n":1},{"c":"04F19001","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N138"/>
+  <dimension ref="A1:N143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8076,16 +8076,20 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B134" s="2" t="n">
-        <v>211</v>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>ZequiSlo</t>
         </is>
       </c>
-      <c r="D134" s="2" t="n">
-        <v>75</v>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
@@ -8102,20 +8106,30 @@
           <t>Freljord|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H134" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J134" s="2" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="K134" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="L134" s="2" t="n">
-        <v>12.5</v>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
@@ -8134,16 +8148,20 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B135" s="2" t="n">
-        <v>216</v>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>DRredstone1221</t>
         </is>
       </c>
-      <c r="D135" s="2" t="n">
-        <v>70</v>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
@@ -8160,11 +8178,15 @@
           <t>Bandle City|F19|Freljord|Ionia</t>
         </is>
       </c>
-      <c r="H135" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>17</v>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
@@ -8182,16 +8204,20 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B136" s="2" t="n">
-        <v>218</v>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>Sigep0361</t>
         </is>
       </c>
-      <c r="D136" s="2" t="n">
-        <v>69</v>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8208,11 +8234,15 @@
           <t>Bilgewater|Freljord|Piltover &amp; Zaun|Shurima</t>
         </is>
       </c>
-      <c r="H136" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>15</v>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
@@ -8230,16 +8260,20 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B137" s="2" t="n">
-        <v>219</v>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>MrPapichurris</t>
         </is>
       </c>
-      <c r="D137" s="2" t="n">
-        <v>68</v>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
@@ -8256,20 +8290,30 @@
           <t>Demacia|Freljord</t>
         </is>
       </c>
-      <c r="H137" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="K137" s="2" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>22.5</v>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
@@ -8288,16 +8332,20 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B138" s="2" t="n">
-        <v>221</v>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>gabriel1223</t>
         </is>
       </c>
-      <c r="D138" s="2" t="n">
-        <v>68</v>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -8314,11 +8362,15 @@
           <t>Bandle City|F19|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
         </is>
       </c>
-      <c r="H138" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>20</v>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
@@ -8330,6 +8382,246 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Jøsst</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>XHgsBjE5uwO_L_s6vYm5QzqxMmbjlkVTwRtUnzCdk3V-FSoUuUKB2BdR96DUg93RoTQLjljQ35bjTg</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>CECAEAIBCYTAEAIDD4QQECABCMMAGBADAQEA6BABAEAR4AIEAMBACBQBCIAQQAAGAQAQGAICAECACCQBA4AQWAQBAEUSU</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"04NX004","n":3},{"c":"04NX008","n":3},{"c":"04NX015","n":3},{"c":"01FR030","n":2},{"c":"04NX002","n":2},{"c":"06FR018","n":2},{"c":"08DE006","n":2},{"c":"01NX001","n":1},{"c":"02FR004","n":1},{"c":"01BC001","n":1},{"c":"07FR011","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>CaptainAmericano</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>9AIzKgYjU_clQy6IBUjdxSiosCqltUdHYmWJ46Ok9segKFx9wPVlmq3cgzE6z5caZVKPyP5_Csc0xA</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAIEGQAQGAQUAEBQICYBBACASAIJAI5AEBYCBMKAGAIBAIUQCBIEEYBAOAQRCMEQCAQCAUAQKAQGAECQIGIBAYBCAAIHAIDQCBYECEAQQAQKAIAQEJJRAIDAIEQV</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F08|Freljord|Ionia|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ052","n":3},{"c":"03IO020","n":3},{"c":"03PZ011","n":3},{"c":"08PZ009","n":3},{"c":"09IO058","n":3},{"c":"07IO011","n":3},{"c":"07IO020","n":3},{"c":"01IO041","n":2},{"c":"05PZ038","n":2},{"c":"07IO017","n":2},{"c":"07IO019","n":2},{"c":"01IO002","n":1},{"c":"05FR005","n":1},{"c":"02BW001","n":1},{"c":"05PZ025","n":1},{"c":"01BW002","n":1},{"c":"32FR007","n":1},{"c":"02SH001","n":1},{"c":"07PZ017","n":1},{"c":"01F08002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>VentoBravo PQD</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>FnX0tnqKEgMTrOM2Udhn4qtVd-NMADklHVu7Wq6FdhTa6ZroG_Y2Mzr-ny3_0Isb_9OOnv59Ym51zA</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>CEEQCAQBAIAQGAIWAEBQIBIBAYAAMAIHAQEQCCABDABACAIBCYBACBAIGQBAMAIIBEBACAIBFIAQGBALAA</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02FR002","n":3},{"c":"03FR022","n":3},{"c":"03PZ005","n":3},{"c":"06DE006","n":3},{"c":"07PZ009","n":3},{"c":"08FR024","n":3},{"c":"01FR001","n":3},{"c":"01FR022","n":3},{"c":"01PZ008","n":3},{"c":"01PZ052","n":3},{"c":"06FR008","n":3},{"c":"06FR009","n":3},{"c":"01FR042","n":2},{"c":"03PZ011","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>AltarOfHate</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>YYvkA9rV2i6QVyaYcMnMCPCwJoZskaQBUra6d5hV39qPLX2e5pJLDHcBJG3_eQduTBWJ__Aozhl-iw</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>CMBQCBQFEYBAIBYDDIBQCBIECUVAKAIHAUBACCIHBEBAMBIPEABQCBIBBILQGBAHGM5HEAQBAQDTWAIHA4LQ</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Piltover &amp; Zaun|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06SI038","n":3},{"c":"04SH003","n":3},{"c":"04SH026","n":3},{"c":"01SI004","n":3},{"c":"01SI021","n":3},{"c":"01SI042","n":3},{"c":"07SI002","n":2},{"c":"09SH009","n":2},{"c":"06SI015","n":2},{"c":"06SI032","n":2},{"c":"01SI001","n":2},{"c":"01SI010","n":2},{"c":"01SI023","n":2},{"c":"04SH051","n":2},{"c":"04SH058","n":2},{"c":"04SH114","n":2},{"c":"01PZ007","n":1},{"c":"59FR007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Caitsyth</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>h8BCgMszqXz5pCS7doxfSCNwPjEL4Jr_fcSPpFWcD6Jr9k6SJixurVcExOLnWAU9BXJ7zVj6eVu9NA</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>CECAEAIDD4QQEBADAQHQECABCMMAMAIBCILB4JRJFIAQCBADBABACAIBAQAQIAYC</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"01FR018","n":3},{"c":"01FR022","n":3},{"c":"01FR030","n":3},{"c":"01FR038","n":3},{"c":"01FR041","n":3},{"c":"01FR042","n":3},{"c":"04NX008","n":2},{"c":"01FR001","n":1},{"c":"04FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N143"/>
+  <dimension ref="A1:N153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8388,16 +8388,20 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B139" s="2" t="n">
-        <v>223</v>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>Jøsst</t>
         </is>
       </c>
-      <c r="D139" s="2" t="n">
-        <v>64</v>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
@@ -8414,11 +8418,15 @@
           <t>Bandle City|Demacia|Freljord|Noxus</t>
         </is>
       </c>
-      <c r="H139" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>17</v>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
@@ -8436,16 +8444,20 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B140" s="2" t="n">
-        <v>227</v>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>CaptainAmericano</t>
         </is>
       </c>
-      <c r="D140" s="2" t="n">
-        <v>61</v>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
@@ -8462,11 +8474,15 @@
           <t>Bilgewater|F08|Freljord|Ionia|Piltover &amp; Zaun|Shurima</t>
         </is>
       </c>
-      <c r="H140" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>20</v>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
@@ -8484,16 +8500,20 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B141" s="2" t="n">
-        <v>230</v>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>VentoBravo PQD</t>
         </is>
       </c>
-      <c r="D141" s="2" t="n">
-        <v>53</v>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
@@ -8510,11 +8530,15 @@
           <t>Demacia|Freljord|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H141" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>14</v>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
@@ -8532,16 +8556,20 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B142" s="2" t="n">
-        <v>231</v>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>AltarOfHate</t>
         </is>
       </c>
-      <c r="D142" s="2" t="n">
-        <v>52</v>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
@@ -8558,11 +8586,15 @@
           <t>Freljord|Piltover &amp; Zaun|Shadow Isles|Shurima</t>
         </is>
       </c>
-      <c r="H142" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>18</v>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr"/>
@@ -8580,16 +8612,20 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B143" s="2" t="n">
-        <v>242</v>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>Caitsyth</t>
         </is>
       </c>
-      <c r="D143" s="2" t="n">
-        <v>45</v>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
@@ -8606,11 +8642,15 @@
           <t>Freljord|Noxus</t>
         </is>
       </c>
-      <c r="H143" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>15</v>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J143" s="2" t="inlineStr"/>
       <c r="K143" s="2" t="inlineStr"/>
@@ -8622,6 +8662,542 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>1lud1d0</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>jRy9WzRUavolHuoXSLs57kwiShQXzO3KbkcwG0oqwCuiNfF37LCIxSMifA_I5cvK7ZArVXtAdfMDfA</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>CMAQCBAHCQCQCAIDD4AQGAYNAECQGEYDAQDTOO3WAUCAGAQEBAFA6BQBBACSUAQGAMOSQAQIAMER2AYEAMBQMEYDAQDRAIBQAQAQGCYQEE2Q</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>F08|F29|Ionia|Noxus|Shurima</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04SH020","n":3},{"c":"01NX031","n":2},{"c":"03NX013","n":2},{"c":"05NX019","n":2},{"c":"04SH055","n":2},{"c":"04SH059","n":2},{"c":"04SH118","n":2},{"c":"04NX002","n":2},{"c":"04NX004","n":2},{"c":"04NX008","n":2},{"c":"04NX010","n":2},{"c":"04NX015","n":2},{"c":"01F08005","n":1},{"c":"42IO006","n":1},{"c":"03F29040","n":1},{"c":"02F08003","n":1},{"c":"09F29003","n":1},{"c":"04NX003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>n1cOw1</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>gWLGE1M0AyBdaHFejf6iBykXCU7SQgHtfGRuQcL5YJIjvxZWrh9j4s1r3aauIrDFBf3dDSfh-91png</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAYBAIAQIAISAECQCDYCAQBQIDYDAEAQ4MBTAMAQGHZBEYBACAIBD4BACAYTGQAQCAYDCI</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>midrange</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03FR002","n":3},{"c":"04FR018","n":3},{"c":"05FR015","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"01FR014","n":3},{"c":"01FR048","n":3},{"c":"01FR051","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"01NX038","n":3},{"c":"01FR031","n":2},{"c":"01NX019","n":2},{"c":"01NX052","n":2},{"c":"01NX003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Money Strat</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>aNXe4KyKejRvmnLrmL9naI3QhOodhgMiReNRRT503ZZB7GF4uGwvB8lutK0ac_XQVdco3TxN-ogLSg</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>CICQCAIADIAQGCK4AEEAACQBBACREAQFBEBQMBYBAIAACAIDAAHACBIJBUAQMCJBAEEQAKICAMESGMYCBAEQGFYCAEDQAAQDAMEQGV3E</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Mount Targon|Noxus|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01DE026","n":3},{"c":"03MT092","n":3},{"c":"08DE010","n":3},{"c":"08SI018","n":3},{"c":"05MT003","n":3},{"c":"05MT006","n":3},{"c":"02DE001","n":2},{"c":"03DE014","n":2},{"c":"05MT013","n":2},{"c":"06MT033","n":2},{"c":"09DE041","n":2},{"c":"03MT035","n":2},{"c":"03MT051","n":2},{"c":"08MT003","n":2},{"c":"08MT023","n":2},{"c":"01SH000","n":1},{"c":"02NX003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>JSPope</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>UaG34YMRDb-W7-iBZbPRCrwyVu3E9LrTueArfv1GB6KVgRTOmp24luuTNakw6mUn_Qpqq9NxwFIcKg</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>CIDQCAQAAIAQGAAOAECQADABAYCAQAIIAADACCAJAMCQMAAGBIFRKHADAEBAAAIBAQAAGAIIAAFACAIBAAGQ</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Mount Targon|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02DE002","n":3},{"c":"03DE014","n":3},{"c":"05DE012","n":3},{"c":"06PZ008","n":3},{"c":"08DE006","n":3},{"c":"08MT003","n":3},{"c":"06DE006","n":3},{"c":"06DE010","n":3},{"c":"06DE011","n":3},{"c":"06DE021","n":3},{"c":"06DE028","n":3},{"c":"02DE001","n":2},{"c":"04DE003","n":2},{"c":"08DE010","n":2},{"c":"01FR000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Sartiga</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>WLDSNkghXhLWN4bili67RcwqUiroSia-3tdh4UKOMGobX8xH1cpLMqcHOhdEIdQNi7G6pp2JZvaxpg</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>CUDQCAQBAMAQGBATAEDAUKYBA4EQCAIHBQHQGAIBBAIBSAYDBERTGVICAEAQGIQBAMEROAYBAECBIAIDBEGQCBQBCU</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F13|Freljord|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02FR003","n":3},{"c":"03PZ019","n":3},{"c":"06BC043","n":3},{"c":"07MT001","n":3},{"c":"07RU015","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01FR025","n":3},{"c":"03MT035","n":3},{"c":"03MT051","n":3},{"c":"03MT085","n":3},{"c":"01NX034","n":2},{"c":"03MT023","n":2},{"c":"01FR004","n":1},{"c":"20FR003","n":1},{"c":"09F13001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>DOUBLE A BATTERY</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Zi0ooeaPDWtw0B9w-RjKJY0dQYd5HBm2tsJ7A8KZ8jzmtH8-2iKuFqgrLFsAhewrnQoFgRutqAx-zA</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>CUDQCAIBCYAQMCQ2AEDASHIBAYGACAIIAADACCABCMBAMAIVDQDACAIBFEAQEAICAEDAULABAYES6AIIAEMAEBQBDAQAEAICAEDQCBABBI</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Ionia|Mount Targon|Runeterra</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"06BC026","n":3},{"c":"06MT029","n":3},{"c":"06RU001","n":3},{"c":"08DE006","n":3},{"c":"08FR019","n":3},{"c":"06FR021","n":3},{"c":"06FR028","n":3},{"c":"01FR041","n":2},{"c":"02FR002","n":2},{"c":"06BC044","n":2},{"c":"06MT047","n":2},{"c":"08FR024","n":2},{"c":"06FR024","n":2},{"c":"06FR032","n":2},{"c":"01IO001","n":1},{"c":"07FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Trifle Majere</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>tf641_l66h0MlgDHyL2MBwElSYYiRDAFWzDcQXXd7VZ56yipmoexmw4iN3hV9ypP0tOL4LGrw4tC8g</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCAIFGEAQKCT7AEDQUCIDBACQOJJKAYDAKDAQDMOCMLICAEDQKAQBBAFAEAA</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI049","n":3},{"c":"05BC127","n":3},{"c":"07BC009","n":3},{"c":"08SI007","n":3},{"c":"08SI037","n":3},{"c":"08SI042","n":3},{"c":"06SI012","n":3},{"c":"06SI016","n":3},{"c":"06SI027","n":3},{"c":"06SI028","n":3},{"c":"06SI038","n":3},{"c":"06SI045","n":3},{"c":"07SI002","n":2},{"c":"08BC002","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>zstacks</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>xCbtgFA1YJQrtWRSNqIBB_baxYXZ66BcsBQbAO7etA2BfFCZ987Qsw5255i7DZuwYWIoDYzag-wMPg</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCAYBAIAQMAI4AEEAABQBBAARQAIIAMEQEBADAQHQGAIBCYTDABABAEBSCAIEAMEACBQDDIBACAILFIAA</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03FR002","n":3},{"c":"06FR028","n":3},{"c":"08DE006","n":3},{"c":"08FR024","n":3},{"c":"08NX009","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01FR048","n":3},{"c":"01NX033","n":2},{"c":"04NX008","n":2},{"c":"06NX026","n":2},{"c":"01FR011","n":2},{"c":"01FR042","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>mk7777777</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>z7M8XIW7YOCEDSfWlQSjrOr6gPlQTv4LDmjJathf8WWzBqHw8YoZCg4vLXZbFAnVKxgWL7OAgHjaUA</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>CICACAYJBYAQKCIGAIBQAAQLAICAADQUAQAQOAAFAEDQSAYDAMAACBQZAUBQSAYXKVLWIAICAMAAODQ</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Mount Targon|Noxus</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03MT014","n":3},{"c":"05MT006","n":3},{"c":"03DE002","n":3},{"c":"03DE011","n":3},{"c":"04DE014","n":3},{"c":"04DE020","n":3},{"c":"07DE005","n":2},{"c":"07MT003","n":2},{"c":"03DE001","n":2},{"c":"03DE006","n":2},{"c":"03DE025","n":2},{"c":"03MT003","n":2},{"c":"03MT023","n":2},{"c":"03MT085","n":2},{"c":"03MT087","n":2},{"c":"03MT100","n":2},{"c":"02NX000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Keldog</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>1CKHt5W262OqVUahdjh11tOI_iLOClJy8SS9v3HT9RIEWsSJ40CQAUPI_xtuajXdOFC7cdvA3xsd3A</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>CUDQCBIKDUAQMCJPAEDAYAIBA4FBIAIIAUKQCCIKCQBAMCQLCUCACBIKAEAQMCI5AIDAUHZPAIEAUAQGAIAQMCRLAMCQUEYUWEAQ</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Mount Targon|Noxus|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC029","n":3},{"c":"06MT047","n":3},{"c":"06RU001","n":3},{"c":"07BC020","n":3},{"c":"08SI021","n":3},{"c":"09BC020","n":3},{"c":"06BC011","n":3},{"c":"06BC021","n":3},{"c":"05BC001","n":2},{"c":"06MT029","n":2},{"c":"06BC031","n":2},{"c":"06BC047","n":2},{"c":"08BC002","n":2},{"c":"08BC006","n":2},{"c":"01BW010","n":1},{"c":"43NX005","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N153"/>
+  <dimension ref="A1:N168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8964,16 +8964,20 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B149" s="2" t="n">
-        <v>254</v>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>DOUBLE A BATTERY</t>
         </is>
       </c>
-      <c r="D149" s="2" t="n">
-        <v>23</v>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
@@ -8990,11 +8994,15 @@
           <t>Bandle City|Demacia|Freljord|Ionia|Mount Targon|Runeterra</t>
         </is>
       </c>
-      <c r="H149" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>17</v>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
@@ -9012,16 +9020,20 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B150" s="2" t="n">
-        <v>255</v>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Trifle Majere</t>
         </is>
       </c>
-      <c r="D150" s="2" t="n">
-        <v>23</v>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
@@ -9038,11 +9050,15 @@
           <t>Bandle City|Shadow Isles</t>
         </is>
       </c>
-      <c r="H150" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>14</v>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
@@ -9060,16 +9076,20 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B151" s="2" t="n">
-        <v>257</v>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>zstacks</t>
         </is>
       </c>
-      <c r="D151" s="2" t="n">
-        <v>20</v>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -9086,11 +9106,15 @@
           <t>Demacia|Freljord|Noxus</t>
         </is>
       </c>
-      <c r="H151" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>15</v>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J151" s="2" t="inlineStr"/>
       <c r="K151" s="2" t="inlineStr"/>
@@ -9108,16 +9132,20 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B152" s="2" t="n">
-        <v>259</v>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>mk7777777</t>
         </is>
       </c>
-      <c r="D152" s="2" t="n">
-        <v>16</v>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
@@ -9134,11 +9162,15 @@
           <t>Demacia|Mount Targon|Noxus</t>
         </is>
       </c>
-      <c r="H152" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>17</v>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr"/>
@@ -9156,16 +9188,20 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B153" s="2" t="n">
-        <v>260</v>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>Keldog</t>
         </is>
       </c>
-      <c r="D153" s="2" t="n">
-        <v>15</v>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
@@ -9182,11 +9218,15 @@
           <t>Bandle City|Bilgewater|Mount Targon|Noxus|Runeterra|Shadow Isles</t>
         </is>
       </c>
-      <c r="H153" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>16</v>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J153" s="2" t="inlineStr"/>
       <c r="K153" s="2" t="inlineStr"/>
@@ -9198,6 +9238,840 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Arfilion</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>w5T0Juwqz8aUwHcRj5-fehs9dULlHagJG9j561E4xl9-xHA2rI0-dBNq-JoOIVyCNOtgVQxCNIGf4Q</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>CEEACAIFFEAQEAYJAECAGBABAUBQCAIGAMNQCCAFFEBAIBIQDQBQMBIQFUXAEAIGAUKAEAIFAEYQCAIGAUSQ</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Noxus|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI041","n":3},{"c":"02NX009","n":3},{"c":"04NX004","n":3},{"c":"05NX001","n":3},{"c":"06NX027","n":3},{"c":"08SI041","n":3},{"c":"04SI016","n":3},{"c":"04SI028","n":3},{"c":"06SI016","n":3},{"c":"06SI045","n":3},{"c":"06SI046","n":3},{"c":"06SI020","n":2},{"c":"01SI001","n":2},{"c":"01SI049","n":2},{"c":"01BW005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>O ViiLão</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>DXYPj2zbMB7NxuSLESG0SJsgelVNXkRHdZuTgBx2wSEneCIBAZMyyMZaMbAeDDsIQHPIQp7uho9Nrw</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>CIBQCAYJGYAQICINAMAQECAPFYDQCAQCAUAQGAQUAEDASIIBBEBDWAQBAIFTCAQGAIFCAAYDBENBWYADAEAQEAQBAQEQ4AIFBEHA</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>F14|Freljord|Ionia|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03MT054","n":3},{"c":"04MT013","n":3},{"c":"01IO008","n":3},{"c":"01IO015","n":3},{"c":"01IO046","n":3},{"c":"02IO005","n":2},{"c":"03IO020","n":2},{"c":"06MT033","n":2},{"c":"09IO059","n":2},{"c":"01IO011","n":2},{"c":"01IO049","n":2},{"c":"06IO010","n":2},{"c":"06IO032","n":2},{"c":"03MT026","n":2},{"c":"03MT027","n":2},{"c":"03MT096","n":2},{"c":"01FR002","n":1},{"c":"02FR004","n":1},{"c":"09F14001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Tu4VRFnHjgnlpffO</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>BpYGlOm4Ey6kNjMWtrHlSUfugD0WvesWCu0JkVoeaKE1FWDR4uPe0z0pgpwlet1UTz1gqGH-KSLD-Q</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>CECACBQCBEAQSBINAMAQKFIXFICQMBIDB4QCMLIEAEAQKMIBAIBAKAIGAUSQCBYFAIBACAIFBIAQIAQO</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06IO009","n":3},{"c":"09SI013","n":3},{"c":"01SI021","n":3},{"c":"01SI023","n":3},{"c":"01SI042","n":3},{"c":"06SI003","n":3},{"c":"06SI015","n":3},{"c":"06SI032","n":3},{"c":"06SI038","n":3},{"c":"06SI045","n":3},{"c":"01SI049","n":2},{"c":"02IO005","n":2},{"c":"06SI037","n":2},{"c":"07SI002","n":2},{"c":"01FR005","n":1},{"c":"10FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>yummyfridchicken</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>PUsNURJe2VxdHbUpClnEirFULa8D5oRJ0Lw4JUkQuci-AAcn6c5q-1_0rUDp_9C-DrY2dLf3FYamGQ</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>CQAQCCAEBEBQCAICFEBAMBASCUBAOAQLCQHACAICGEAQEAQFAEBAIBQBAMBBIAIDAQFQCBICAYAQOBAJAEEAUBQBBACBUAQGAIQCIAQHAIIRGAYBAQASCNAFAYCASIBIFMXAMBIEBIIRQGI3EY</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F11|F36|Freljord|Ionia|Noxus|Piltover &amp; Zaun|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08PZ009","n":3},{"c":"01IO041","n":2},{"c":"06PZ018","n":2},{"c":"06PZ021","n":2},{"c":"07IO011","n":2},{"c":"07IO020","n":2},{"c":"01FR002","n":1},{"c":"49FR002","n":1},{"c":"02SI001","n":1},{"c":"02PZ006","n":1},{"c":"01NX002","n":1},{"c":"20FR003","n":1},{"c":"04F11001","n":1},{"c":"05IO006","n":1},{"c":"01SH004","n":1},{"c":"09FR008","n":1},{"c":"10BW001","n":1},{"c":"08PZ026","n":1},{"c":"02BW002","n":1},{"c":"32F36002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Edgy Dank Memer</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>F74AKcKMmPGOnYg66v1j86wCa8V6a1aGJrZDLcyWZ85FJLfiGjvMJR1wC_Nzsz-vWuaUikoWp-d0eg</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAIFAEAQGAIWAEEACAICAYASIKIDAQCTKNZYAQAQCDAXFI2AEAIBAUOQCBYFAEAA</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI001","n":3},{"c":"03FR022","n":3},{"c":"08FR001","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"04SI053","n":3},{"c":"04SI055","n":3},{"c":"04SI056","n":3},{"c":"01FR012","n":3},{"c":"01FR023","n":3},{"c":"01FR042","n":3},{"c":"01FR052","n":3},{"c":"01SI029","n":2},{"c":"07SI001","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>ANG3L</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>64T_QJuxrjgymcgVU_WRi83XMzxl5n3CFbhCLnEpra1r8axDA_rRCCP2Lvk2rIRx-TL7jn-FAfdNqQ</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>CIDACBYJBEAQQAI6AIDACJBJAIEASAY7AMAQCDBBFICAGCIOCVLWIAABAEBQCFQ</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Mount Targon|Noxus</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"07MT009","n":3},{"c":"08FR030","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"08MT003","n":3},{"c":"08MT031","n":3},{"c":"01FR012","n":3},{"c":"01FR033","n":3},{"c":"01FR042","n":3},{"c":"03MT014","n":3},{"c":"03MT021","n":3},{"c":"03MT087","n":3},{"c":"03MT100","n":3},{"c":"01NX001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Sly Red Fox</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>qNGovuOe08n5NBGIEcT_dIfURM1u8IzaHv10QLvx21USMMmEfqS3Pf7tdM7_gh9Hxo-sVjCBaXMUCQ</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>CEBQCAIDCMAQIAYEAQDAKDAQDQTAQAIDAMBQCBADCYAQMBINAEDQKAQBBABRGAIJAUGQEAIDBUPQEAQDAMEQCAQBAUAQG</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX019","n":3},{"c":"04NX004","n":3},{"c":"06SI012","n":3},{"c":"06SI016","n":3},{"c":"06SI028","n":3},{"c":"06SI038","n":3},{"c":"03NX003","n":2},{"c":"04NX022","n":2},{"c":"06SI013","n":2},{"c":"07SI002","n":2},{"c":"08NX019","n":2},{"c":"09SI013","n":2},{"c":"01NX013","n":2},{"c":"01NX031","n":2},{"c":"02NX003","n":2},{"c":"02NX009","n":2},{"c":"02FR005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Eksirf</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>suoMpWzGhtjvF_YYo5Yz40FMKQk5OdgLb3OF_JE5690sWdr1F5HzX1HoRMd2zOvlW2IdzkrNq7UuOw</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>CMCACBQGFUAQMBYFAQCAOE2EJJIAMBAGAEBAGBAFB4AQCBAHIEBACBAGA4AQIBYW</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BW045","n":3},{"c":"06SH005","n":3},{"c":"04SH019","n":3},{"c":"04SH068","n":3},{"c":"04SH074","n":3},{"c":"04SH080","n":3},{"c":"04BW001","n":3},{"c":"04BW002","n":3},{"c":"04BW003","n":3},{"c":"04BW004","n":3},{"c":"04BW005","n":3},{"c":"04BW015","n":3},{"c":"04SH065","n":2},{"c":"01PZ006","n":1},{"c":"07FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Street Saint</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>E7smQaEa-hHpUuWQqVn-mefaJrXHeFLEoMWV-L32PyWbHALmGjQ3ddKMC9eUIgCOIYgT5g7IyJBAwQ</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>CUCQCAYAA4AQMABEAEEAYDQCAYASIKIDAEAQCFZKAQAQQAAZAEEACDACAQAQUDQDAEAQYFA6AIAQIAIMAEEACCA</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03DE007","n":3},{"c":"06DE036","n":3},{"c":"08RU014","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"01FR001","n":3},{"c":"01FR023","n":3},{"c":"01FR042","n":3},{"c":"08DE025","n":2},{"c":"08FR012","n":2},{"c":"04FR010","n":2},{"c":"04FR014","n":2},{"c":"01FR012","n":2},{"c":"01FR020","n":2},{"c":"01FR030","n":2},{"c":"01PZ001","n":1},{"c":"12FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Wolfstocs</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>-M26hvluB9ZYDHpEv8BjleefydV21zzm2QSdI0mNwXnlvMyFNXLt07NFAgW2BGCGksvQ0-vqMu_Fyw</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>CECACAIBAEAQKBACAEEAIGACAECAQGIGAEBACAQBAICAUAIDAQCQCCABCMBACBBUHICACAIEBMPCUAYBAUCA4AIGAQVQGAIBA4KCM</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>F43|Freljord|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR001","n":3},{"c":"05PZ002","n":3},{"c":"08PZ024","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"02FR002","n":2},{"c":"02PZ010","n":2},{"c":"03PZ005","n":2},{"c":"08FR019","n":2},{"c":"01PZ052","n":2},{"c":"01PZ058","n":2},{"c":"01FR004","n":2},{"c":"01FR011","n":2},{"c":"01FR030","n":2},{"c":"01FR042","n":2},{"c":"01SI004","n":1},{"c":"14FR006","n":1},{"c":"04F43003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Kidrobot123</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>GGgM83nY2yjo8GRYdcY5-_C1fzPnQr8h6htZVFs3CSPZbiBv9fHW5AGWk06pyekwDQTitQueVleKdA</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>CECACCABDABACAIWEYBACAY7EEBQIAYEBAHQMAIEAMBACBQAAYAQQAAGAEEACEYCAEAR4KICAYAREHAA</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08FR024","n":3},{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"04NX004","n":3},{"c":"04NX008","n":3},{"c":"04NX015","n":3},{"c":"04NX002","n":2},{"c":"06DE006","n":2},{"c":"08DE006","n":2},{"c":"08FR019","n":2},{"c":"01FR030","n":2},{"c":"01FR041","n":2},{"c":"06FR018","n":2},{"c":"06FR028","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>VICEREME</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>0dOWqKCbYXD-5wmCrgaSwfICOpIbHqvGMZDNw-U50Xbf-OOjPJxG97aGKvpXz5701cWy3A_mK6PFxg</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>CMCACCIHBEBACAQMFIBQIAQFBMHAKBAHAMGRUM3SAEAQEAQKAQAQGAQFAECAOOYBBEBDGAQEAICAQ</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>F59|Freljord|Ionia|Noxus|Shurima</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"09SH009","n":3},{"c":"01IO012","n":3},{"c":"01IO042","n":3},{"c":"04IO005","n":3},{"c":"04IO011","n":3},{"c":"04IO014","n":3},{"c":"04SH003","n":3},{"c":"04SH013","n":3},{"c":"04SH026","n":3},{"c":"04SH051","n":3},{"c":"04SH114","n":3},{"c":"02IO010","n":2},{"c":"01NX002","n":1},{"c":"05FR004","n":1},{"c":"07F59001","n":1},{"c":"09IO051","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>cloite</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>S5FeQ_9nYTSQwyzmssTeHjZtfnkDOY3-IkDlNjCoY-lrZ1-TX6gxgYaqnpjF5OIyCnEyB_-uuFMDVg</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>CUBQCAYBBIAQQAIBAEEAYDQGAEAQKLABAYACIAIIAIHAEAIBC4QQEBQBEQUQECAADENAQAIBAIQQCAYAA4AQMAJGAEEAUBABBAABMAQBAEGDIAQDAEERMBAIAEBAYDYS</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|F08|F22|Freljord|Ionia|Runeterra|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03FR010","n":3},{"c":"08FR001","n":3},{"c":"08RU014","n":3},{"c":"01SI044","n":2},{"c":"06DE036","n":2},{"c":"08IO014","n":2},{"c":"01FR023","n":2},{"c":"01FR033","n":2},{"c":"06FR036","n":2},{"c":"06FR041","n":2},{"c":"08DE025","n":2},{"c":"08DE026","n":2},{"c":"01FR002","n":1},{"c":"33FR003","n":1},{"c":"00SH001","n":1},{"c":"06FR038","n":1},{"c":"01F08010","n":1},{"c":"04FR008","n":1},{"c":"00F22002","n":1},{"c":"01FR012","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Mzhkm</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>535</v>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>wKRwXzXitOo8tiys3ThWEcY6NOqbxCgRL6LZa2_S69LCgiqhZdeCqkDtBim83OCOSHJ0lI82rvz5uA</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>CEBQCCABCMBQKBACAYHAIAIEBAMTIOQGAEBQCAQBAMCAWAIEAEFACBIEBIAQQBAYAIAQCBBKAIAQCAI6AEEACGA</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08FR019","n":3},{"c":"05PZ002","n":3},{"c":"05PZ006","n":3},{"c":"05PZ014","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"01PZ058","n":3},{"c":"03FR002","n":2},{"c":"03PZ011","n":2},{"c":"04FR010","n":2},{"c":"05PZ010","n":2},{"c":"08PZ024","n":2},{"c":"01FR004","n":2},{"c":"01FR042","n":2},{"c":"01FR001","n":1},{"c":"30FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>mbrookz</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>iMQDykjthqoztGrFSrHwtphL2pV9BIrGgAz1EIFDSRHTboYbSYy9SPFPyLCvPzq3i5PdNMVJIeWEiA</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>CQEQCBAJBAAQIBIHAECQU5YBA4EQCAIJBEBAEAIFFM3AEAYJH5OQEBIFAMHQECAFCUUAAAIBAECQS</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Mount Targon|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04MT008","n":3},{"c":"04SI007","n":3},{"c":"05BC119","n":3},{"c":"07MT001","n":3},{"c":"09MT002","n":3},{"c":"01SI043","n":3},{"c":"01SI054","n":3},{"c":"03MT063","n":3},{"c":"03MT093","n":3},{"c":"05SI003","n":3},{"c":"05SI015","n":3},{"c":"08SI021","n":3},{"c":"08SI040","n":3},{"c":"01FR005","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N168"/>
+  <dimension ref="A1:N193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9972,16 +9972,20 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B167" s="2" t="n">
-        <v>9</v>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>Mzhkm</t>
         </is>
       </c>
-      <c r="D167" s="2" t="n">
-        <v>535</v>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>535.0</t>
+        </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
@@ -9998,11 +10002,15 @@
           <t>Freljord|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H167" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I167" s="2" t="n">
-        <v>17</v>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J167" s="2" t="inlineStr"/>
       <c r="K167" s="2" t="inlineStr"/>
@@ -10020,16 +10028,20 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B168" s="2" t="n">
-        <v>10</v>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>mbrookz</t>
         </is>
       </c>
-      <c r="D168" s="2" t="n">
-        <v>533</v>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>533.0</t>
+        </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
@@ -10046,29 +10058,1431 @@
           <t>Bandle City|Freljord|Mount Targon|Shadow Isles</t>
         </is>
       </c>
-      <c r="H168" s="2" t="n">
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04MT008","n":3},{"c":"04SI007","n":3},{"c":"05BC119","n":3},{"c":"07MT001","n":3},{"c":"09MT002","n":3},{"c":"01SI043","n":3},{"c":"01SI054","n":3},{"c":"03MT063","n":3},{"c":"03MT093","n":3},{"c":"05SI003","n":3},{"c":"05SI015","n":3},{"c":"08SI021","n":3},{"c":"08SI040","n":3},{"c":"01FR005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Scilla</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>528.0</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>vwIBeem3KeMHt2DXT689hGEUoZwydZ1S7q2GcWLHvl4GxNDmaxHhI4X25Rx9afLQ0Z4io5Xm3dC2-A</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>CEAAAAICAAAAMJY</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Demacia</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02DE000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>NotreDammit</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>521.0</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Ik2qUvSnwi86IeXEu5fiNj4mTgE6LR2fHlKi_J1gS05olorTm2il2QpyaTh-gdM17lDLdfXLjcZ3lw</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>CECACCABDABACAY7EEBAIAYEB4BQCAIWDYTAKAIBAEVACAYBAIAQMAI4AEEAABQCAQBQECADAEDACEQBBAARGAQBAECCS</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|F19|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08FR024","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"01FR022","n":3},{"c":"01FR030","n":3},{"c":"01FR038","n":3},{"c":"01FR042","n":2},{"c":"03FR002","n":2},{"c":"06FR028","n":2},{"c":"08DE006","n":2},{"c":"04NX002","n":2},{"c":"04NX008","n":2},{"c":"01BW001","n":1},{"c":"18FR008","n":1},{"c":"01F19002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>armroselund</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>516.0</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>AvHH9Z3PuNMHXtDRIB6qNKFH7fPKoZYur2Tn_8Tcqn9kEVRsfHD85_OqRAdblbmzCO7CndVSWr9dwA</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCAIFGEAQKCT7AEDQUCIDBACQOJJKAYDAKDAQDMOCMLICAEDQKAQBBAFAEAA</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI049","n":3},{"c":"05BC127","n":3},{"c":"07BC009","n":3},{"c":"08SI007","n":3},{"c":"08SI037","n":3},{"c":"08SI042","n":3},{"c":"06SI012","n":3},{"c":"06SI016","n":3},{"c":"06SI027","n":3},{"c":"06SI028","n":3},{"c":"06SI038","n":3},{"c":"06SI045","n":3},{"c":"07SI002","n":2},{"c":"08BC002","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>hungrylouna129</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>434.0</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>4DksskDtcvxtt8JMYwyNMjIIbmau_tz4KwUT-zwcbizxUo3ZMm990UGyxvJ8PHKAEDre0lfPtNGyMw</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>CIDQCBAGBUAQKBQBAEDAMHQBBEDBYAQDBERVQAQGBEECGBACAYERQKBXAEAQGCINAEBAMCIGFM</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04BW013","n":3},{"c":"05BW001","n":3},{"c":"06BW030","n":3},{"c":"09BW028","n":3},{"c":"03MT035","n":3},{"c":"03MT088","n":3},{"c":"06MT008","n":3},{"c":"06MT035","n":3},{"c":"02BW009","n":3},{"c":"02BW024","n":3},{"c":"02BW040","n":3},{"c":"02BW055","n":3},{"c":"03MT013","n":2},{"c":"02BW009","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Barbaronte</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>410.0</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>9a2qB8uTMNBKODgBHYOYsiFBKF34wGbJqeLclag9IqdLeNQMkyJqQ0bKJX8uos1ZzoXkuPnf2YM41Q</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAIEGQAQKBAWAEDQUFABBAFAMAQFBIA2MAIEAYFA6EITEACQCAIEAEAQEBAGAECQVNQBAECQIGIBAYCC4AA</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr"/>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ052","n":3},{"c":"05PZ022","n":3},{"c":"07BC020","n":3},{"c":"08BC006","n":3},{"c":"05BC001","n":3},{"c":"05BC166","n":3},{"c":"06BC015","n":3},{"c":"06BC017","n":3},{"c":"06BC019","n":3},{"c":"06BC032","n":3},{"c":"01PZ001","n":2},{"c":"02PZ006","n":2},{"c":"05BC182","n":2},{"c":"05PZ025","n":2},{"c":"06PZ046","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sky1Striker </t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>362.0</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>z7pM5LeiAfXJjAoYrbnYFkXCM_pO8BbpNEzD7hGg9en0Ar_f_nyxTaIzsr4hVo0G5fgiEbsowIVgFg</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>CUCQCCAKCQAQQAYDAEEQUFACAUFDDGABAMDAUDYRCUCQCAYAAQAQKCQBAEDQUCIBBAFAMAIJAUHAMAIFBILQCBICCQAQMCQXAEEAUBABBAGA4AIIAUSQ</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|F08|F20|Freljord|Noxus|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr"/>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08BC020","n":3},{"c":"08NX003","n":3},{"c":"09BC020","n":3},{"c":"05BC049","n":3},{"c":"05BC152","n":3},{"c":"06BC015","n":3},{"c":"06BC017","n":3},{"c":"06BC021","n":3},{"c":"03DE004","n":2},{"c":"05BC001","n":2},{"c":"07BC009","n":2},{"c":"08BC006","n":2},{"c":"09SI014","n":2},{"c":"01SI010","n":1},{"c":"23FR005","n":1},{"c":"02F20001","n":1},{"c":"06BC023","n":1},{"c":"01F08010","n":1},{"c":"04FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Kyo1035</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>359.0</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>1nAUNIIOPo7lSaGbshYaN3Db-aMceqGvyCbbwClP5lRyYFPTp67mI3nHPjpiQoWcrlMIFTIclO1RLA</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>CQBQCAIEGQAQQBAJAMDQECYRCQEACAICFEAQEAQFAEBQEFABAMCAWAIFAIDACBYCCMAQQCQGAICQIGAZAQAQCARRAECQIJQBAYBCABAGAQEREFJL</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F38|Freljord|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ052","n":3},{"c":"08PZ009","n":3},{"c":"07IO011","n":3},{"c":"07IO017","n":3},{"c":"07IO020","n":3},{"c":"01IO041","n":2},{"c":"02IO005","n":2},{"c":"03IO020","n":2},{"c":"03PZ011","n":2},{"c":"05IO006","n":2},{"c":"07IO019","n":2},{"c":"08BC006","n":2},{"c":"05PZ024","n":2},{"c":"05PZ025","n":2},{"c":"01FR002","n":1},{"c":"49FR005","n":1},{"c":"04F38001","n":1},{"c":"06IO032","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Borden</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>354.0</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>qK9glayGZ5epQctvwehXPI9r5oRK7o06vZ6d6XJXNy_B35V-NIfKnsbD6sbg9oW4vlzESUqjtMEecA</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>CQBQCBAFAUAQMBJOAIEAKBZKAYAQKCT7AEDAKFABA4CQEAQEAUCBAAQIAUSSSAYBAUAR2MIFAEDQKCQBBAFAMAQEAUBTQAQFBIATCAQGAUDRW</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Ionia|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04SI005","n":3},{"c":"06SI046","n":3},{"c":"08SI007","n":3},{"c":"08SI042","n":3},{"c":"05BC127","n":2},{"c":"06SI020","n":2},{"c":"07SI002","n":2},{"c":"04SI004","n":2},{"c":"04SI016","n":2},{"c":"08SI037","n":2},{"c":"08SI041","n":2},{"c":"01SI001","n":2},{"c":"01SI029","n":2},{"c":"01SI049","n":2},{"c":"01SH005","n":1},{"c":"10FR008","n":1},{"c":"10BW002","n":1},{"c":"04SI003","n":1},{"c":"56IO005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Vstorm</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>327.0</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>JpFQzWqtPpJDo8r48y6HblRG0dMn8GhRylC5B7wzHUXJ31GaT8brYA4Uitv1OdWhB1kCmC7JEk8fCg</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAYFBYAQIAQOAECQEGQBAYCRAAIJAUGQEAICAY4QMAIBAIIQCAYCCQAQMARCAEDAKDYBBABBOAQBAUVDCAYBAEBBWAQBAUBSEAQGAUOC4</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia|Noxus|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03SI014","n":3},{"c":"04IO014","n":3},{"c":"05IO026","n":3},{"c":"06SI016","n":3},{"c":"09SI013","n":3},{"c":"01IO006","n":3},{"c":"01IO057","n":3},{"c":"01IO017","n":2},{"c":"03IO020","n":2},{"c":"06IO034","n":2},{"c":"06SI015","n":2},{"c":"08IO023","n":2},{"c":"01SI042","n":2},{"c":"01SI049","n":2},{"c":"01FR002","n":1},{"c":"27IO001","n":1},{"c":"05NX034","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>TheDescendedOne</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>312.0</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>wqJCOLzA1vVNBe2YPW9IadtgQ7Zh-na8CkFIUpQYVvqOtpQJRdchMv2NMKd38jhUoG9EZrv8X1TxTw</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>CUEACAICFYAQGAQFAECAIBYBAUFCQAIGAIQACBQMAYAQOAQRAMBAEAIDBEBQCAIBDUAQCARRAEBQEFAEAEAQIHABAQAQUAIGAQVQCBQHFI</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Ionia|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO046","n":3},{"c":"03IO005","n":3},{"c":"04PZ007","n":3},{"c":"05BC040","n":3},{"c":"06IO032","n":3},{"c":"06RU006","n":3},{"c":"07IO017","n":3},{"c":"02IO001","n":3},{"c":"02IO003","n":3},{"c":"02IO009","n":3},{"c":"01FR029","n":2},{"c":"01IO049","n":2},{"c":"03IO020","n":2},{"c":"01FR004","n":1},{"c":"28FR004","n":1},{"c":"01BC001","n":1},{"c":"06PZ043","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Im Bard Out</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>311.0</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Yz3vZckMMsL-Dws1t-3XJfGXMMs6-aF_NVmV38P_BTavVKVSeopCEa87wrihIzczQX0FLehUySyTFw</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCBQCEAAQMBZQAEEQOCQCAQDSOSIDBEBC2MZ2A4AQCARRAEBQEFABAYDQKAIHAIKACCAKAYAQQAQKAEEQENYBAICAOALK</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Ionia|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr"/>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06IO032","n":3},{"c":"06SH048","n":3},{"c":"09SH010","n":3},{"c":"04SH039","n":3},{"c":"04SH073","n":3},{"c":"09IO045","n":3},{"c":"09IO051","n":3},{"c":"09IO058","n":3},{"c":"01IO049","n":2},{"c":"03IO020","n":2},{"c":"06SH005","n":2},{"c":"07IO020","n":2},{"c":"08BC006","n":2},{"c":"08IO010","n":2},{"c":"09IO055","n":2},{"c":"02PZ007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Thir</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>266.0</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>PSn5jNtfV5cPKB1w5tU3K4_C3dNJ9MQC0F7qfI93H6EPCuf1SM32zjIn7YY3xzuflYfagd4d7Fr5gg</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>CIDACBAGBUAQKBQBAEDAMHQCAMESGWACAYEQQIYDAIDBQKBXAQAQEBQJAEBQSDIBAQEQKAIGBEIQCAQGBEDCW</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04BW013","n":3},{"c":"05BW001","n":3},{"c":"06BW030","n":3},{"c":"03MT035","n":3},{"c":"03MT088","n":3},{"c":"06MT008","n":3},{"c":"06MT035","n":3},{"c":"02BW024","n":3},{"c":"02BW040","n":3},{"c":"02BW055","n":3},{"c":"02BW009","n":2},{"c":"03MT013","n":2},{"c":"04MT005","n":2},{"c":"06MT017","n":2},{"c":"02BW009","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>사생아</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>263.0</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>F9OZ_-Flq3owGOinq4MYVL8t93hZaWUFRndpsIhOr3j6-D0AQ8hBsrbWEm6hyFMIECkayDR6omW6iA</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBIKP4AQMAAGAEEASAYFBEFACAYMBUKAMAIBAANACAQAAEAQKCRRAECQADABA4FASAQJBICBEAQBAUFACAIJAAWQ</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Mount Targon|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr"/>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC127","n":3},{"c":"06DE006","n":3},{"c":"08MT003","n":3},{"c":"09BC001","n":3},{"c":"09BC003","n":3},{"c":"09BC012","n":3},{"c":"09BC013","n":3},{"c":"09BC020","n":3},{"c":"01DE026","n":2},{"c":"02DE001","n":2},{"c":"05BC049","n":2},{"c":"05DE012","n":2},{"c":"07BC009","n":2},{"c":"09BC004","n":2},{"c":"09BC018","n":2},{"c":"01SI010","n":1},{"c":"01FR009","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>SrdasParanga</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>259.0</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>A6p0IhoXbKSbKc-2OXF6DXbe0qG3fpxRZCpsYFt1DN6_mDyJLL-Lt1WMvuIRkpGW91CVR0Ta7bAc1Q</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCAIBBQAQCARJAEBQCFQBAMBBGAIGAIWAEBQBEQUQGBYCBMIRIBABAEASUAIFAIDACBQBEYBAOAQTFEAA</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR012","n":3},{"c":"01IO041","n":3},{"c":"03FR022","n":3},{"c":"03IO019","n":3},{"c":"06IO044","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"07IO011","n":3},{"c":"07IO017","n":3},{"c":"07IO020","n":3},{"c":"01FR042","n":2},{"c":"05IO006","n":2},{"c":"06FR038","n":2},{"c":"07IO019","n":2},{"c":"07IO041","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>iNilesD</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>257.0</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>wyBqeP-e5g-DWGj1HtegH7itQvt6v4ICyf548MkkPS2eOQAg1oZuz0NOBM3NpzMY4X3b_j_0lyxQ8g</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAYCAIAQIBAQAECQIGIBAYFBUBABAQGBYKBNAQCQUTSUSEA6MAICAEAQIJYBAMCBSAA</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03IO002","n":3},{"c":"04PZ016","n":3},{"c":"05PZ025","n":3},{"c":"06BC026","n":3},{"c":"01PZ012","n":3},{"c":"01PZ028","n":3},{"c":"01PZ040","n":3},{"c":"01PZ045","n":3},{"c":"05BC078","n":3},{"c":"05BC084","n":3},{"c":"05BC145","n":3},{"c":"05BC230","n":3},{"c":"01PZ039","n":2},{"c":"03PZ025","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Tu4VRFnHjgnlpffO</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>BpYGlOm4Ey6kNjMWtrHlSUfugD0WvesWCu0JkVoeaKE1FWDR4uPe0z0pgpwlet1UTz1gqGH-KSLD-Q</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>CECACBQCBEAQSBINAMAQKFIXFICQMBIDB4QCMLIEAEAQKMIBAIBAKAIGAUSQCBYFAIBACAIFBIAQIAQO</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr"/>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06IO009","n":3},{"c":"09SI013","n":3},{"c":"01SI021","n":3},{"c":"01SI023","n":3},{"c":"01SI042","n":3},{"c":"06SI003","n":3},{"c":"06SI015","n":3},{"c":"06SI032","n":3},{"c":"06SI038","n":3},{"c":"06SI045","n":3},{"c":"01SI049","n":2},{"c":"02IO005","n":2},{"c":"06SI037","n":2},{"c":"07SI002","n":2},{"c":"01FR005","n":1},{"c":"10FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Money Strat</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>aNXe4KyKejRvmnLrmL9naI3QhOodhgMiReNRRT503ZZB7GF4uGwvB8lutK0ac_XQVdco3TxN-ogLSg</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>CICQCAIADIAQGCK4AEEAACQBBACREAQFBEBQMBYBAIAACAIDAAHACBIJBUAQMCJBAEEQAKICAMESGMYCBAEQGFYCAEDQAAQDAMEQGV3E</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|Mount Targon|Noxus|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr"/>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01DE026","n":3},{"c":"03MT092","n":3},{"c":"08DE010","n":3},{"c":"08SI018","n":3},{"c":"05MT003","n":3},{"c":"05MT006","n":3},{"c":"02DE001","n":2},{"c":"03DE014","n":2},{"c":"05MT013","n":2},{"c":"06MT033","n":2},{"c":"09DE041","n":2},{"c":"03MT035","n":2},{"c":"03MT051","n":2},{"c":"08MT003","n":2},{"c":"08MT023","n":2},{"c":"01SH000","n":1},{"c":"02NX003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Capuchones</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>239.0</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>ifBVSokXCUevq11fz_t-WfI4tgfBPZ0daZyY0XOtuQfwc8fJmtQnoN-KX0Ug1PTRmc_LSClYeEl1yQ</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>CIBQCAQGCYAQIAADAIBAAAQGBEAQEAAEAEBQADQBAQAAEAIFAYAQCBIABQAQMABKAEDQABIDAIDA6LJ6AQAQACI5EASQA</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>midrange</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02BW022","n":3},{"c":"04DE003","n":3},{"c":"02DE002","n":3},{"c":"02DE006","n":3},{"c":"02DE004","n":2},{"c":"03DE014","n":2},{"c":"04DE002","n":2},{"c":"05BW001","n":2},{"c":"05DE012","n":2},{"c":"06DE042","n":2},{"c":"07DE005","n":2},{"c":"02BW015","n":2},{"c":"02BW045","n":2},{"c":"02BW062","n":2},{"c":"01DE009","n":2},{"c":"01DE029","n":2},{"c":"01DE032","n":2},{"c":"01DE037","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>DeadCraft48</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>z99HH4ScYBXXZOteeWfUZCG8HCbuw6GU_bR16cpV42-T_wUxmAw93ad65iutfh2e_H6c54YCFgxC8Q</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>CUCQCAIECQAQIAIPAEDAUKYBA4GA6AQBAEEBABYBAEARSAIBAMRACAQBAMAQMAIVAEDASIYBBEAQUAQDBEZVKBIBAEADCAIDAQJQCBQJFMAQQBISAIBQSDJD</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F08|F19|Freljord|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr"/>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ020","n":3},{"c":"04FR015","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01FR025","n":2},{"c":"01NX034","n":2},{"c":"02FR003","n":2},{"c":"06FR021","n":2},{"c":"06MT035","n":2},{"c":"09FR010","n":2},{"c":"03MT051","n":2},{"c":"03MT085","n":2},{"c":"01FR000","n":1},{"c":"49FR003","n":1},{"c":"04F19001","n":1},{"c":"06MT043","n":1},{"c":"01F08005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>waitimplaying</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>236.0</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>_azDPaOzvLiVWYOIu_tqeRsKBR8jGB0PqWIwKWT4Q7tkGYQL315DorDP9xtQYmJXyLKmpxH_bxvxjA</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAYBAIAQQAIYAIAQCFRGAIAQGHZBAMCAGAQEB4CACBADBAAQMAI4AEEACEYDAEAQCCY6AEAQQAAG</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>F08|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03FR002","n":3},{"c":"08FR024","n":3},{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"04NX002","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"04NX008","n":2},{"c":"06FR028","n":2},{"c":"08FR019","n":2},{"c":"01FR001","n":2},{"c":"01FR011","n":2},{"c":"01FR030","n":2},{"c":"01F08000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>aKutti</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>24yZlYbjb0BtW0Ov9SebTBWxAk6MjX0CT6zVIgV9Ygdpxu3rO7FW8pFwTmpysdoZGJD8pfhDoCeqlg</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>CUDACAQBAMAQGBATAEDAUKYBA4GA6AIIAIFAGAIBBAIBSAYBAEBAEAIBAQKACCIBBIEQCAIAGEAQCAZCAEBAMCQBAQAQ6AIEA4YQCBQBCUAQOAQUAEEAIGICAEBAKLQ</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|F34|F49|Freljord|Ionia|Piltover &amp; Zaun|Runeterra|Shurima</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr"/>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02FR003","n":3},{"c":"03PZ019","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"08IO010","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01FR025","n":3},{"c":"01IO002","n":2},{"c":"01PZ020","n":2},{"c":"09FR010","n":2},{"c":"01FR000","n":1},{"c":"49FR001","n":1},{"c":"03F34001","n":1},{"c":"02BW010","n":1},{"c":"01PZ001","n":1},{"c":"15FR004","n":1},{"c":"07F49001","n":1},{"c":"06FR021","n":1},{"c":"01SH002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Jøsst</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>XHgsBjE5uwO_L_s6vYm5QzqxMmbjlkVTwRtUnzCdk3V-FSoUuUKB2BdR96DUg93RoTQLjljQ35bjTg</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>CECAEAIBCYTAEAIDD4QQECABCMMAGBADAQEA6BABAEAR4AIEAMBACBQBCIAQQAAGAQAQGAICAECACCQBA4AQWAQBAEUSU</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr"/>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"04NX004","n":3},{"c":"04NX008","n":3},{"c":"04NX015","n":3},{"c":"01FR030","n":2},{"c":"04NX002","n":2},{"c":"06FR018","n":2},{"c":"08DE006","n":2},{"c":"01NX001","n":1},{"c":"02FR004","n":1},{"c":"01BC001","n":1},{"c":"07FR011","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>ThePeterJ</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>bPnRARyfsq_ASQlcALbXWm_d6QwD_ouVJq3On-6b5BOF7uKYmJ5bnffsS30CviSjGqa7PZgAWQKb1A</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>CUDACAYCAUAQIBAHAECQUKABAYBCAAIGBQDAGAQCAEBQSBABAEAR2AIDAIKACBYCFEBACAROGEDACAIEDQAQIAIKAEDAIKYBAYDSUAIHAIIQCCACBI</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Ionia|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="I168" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J168" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K168" s="2" t="n">
+      <c r="I191" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr"/>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03IO005","n":3},{"c":"04PZ007","n":3},{"c":"05BC040","n":3},{"c":"06IO032","n":3},{"c":"06RU006","n":3},{"c":"02IO001","n":3},{"c":"02IO003","n":3},{"c":"02IO009","n":3},{"c":"01FR029","n":2},{"c":"03IO020","n":2},{"c":"07IO041","n":2},{"c":"01IO046","n":2},{"c":"01IO049","n":2},{"c":"01FR004","n":1},{"c":"28FR004","n":1},{"c":"01BC001","n":1},{"c":"06PZ043","n":1},{"c":"01BW007","n":1},{"c":"42FR007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>gabriel1223</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>1WsbtUX9V0m0CYHe8GUY_TGfwxFuO9kepcE4_H4riGZg8gFe-EmFi3WkCuzdZ-FoaTmX5AX3t8UVdQ</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>CQCACAICGEAQOBRLAEEQEOQIAYDAMBYLB4KRYHRIAIAQQCQGAIDAMEBDAEAQGAQU</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Ionia|Noxus</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I192" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="L168" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="M168" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="N168" s="2" t="inlineStr">
-        <is>
-          <t>[{"c":"04MT008","n":3},{"c":"04SI007","n":3},{"c":"05BC119","n":3},{"c":"07MT001","n":3},{"c":"09MT002","n":3},{"c":"01SI043","n":3},{"c":"01SI054","n":3},{"c":"03MT063","n":3},{"c":"03MT093","n":3},{"c":"05SI003","n":3},{"c":"05SI015","n":3},{"c":"08SI021","n":3},{"c":"08SI040","n":3},{"c":"01FR005","n":1}]</t>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr"/>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO049","n":3},{"c":"07BW043","n":3},{"c":"09IO058","n":3},{"c":"06BW006","n":3},{"c":"06BW007","n":3},{"c":"06BW011","n":3},{"c":"06BW015","n":3},{"c":"06BW021","n":3},{"c":"06BW028","n":3},{"c":"06BW030","n":3},{"c":"06BW040","n":3},{"c":"08BC006","n":2},{"c":"06BW016","n":2},{"c":"06BW035","n":2},{"c":"01NX002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>JulioA619</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>HyM6ouqwRnGB8IMDgZZIKEOIs6uvKx5CcxPRIPkU1-ky9UJ0LIPsERL0vXcQnIL4JxsgpWiu4RXJtw</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>CICQCCAJDAAQSARVAIBQSI2YAIDASCBDAQAQECIUDI2AEAIJAAQQECICG45AIAIBAIYQCAYCCQAQMCIGAEEAECQ</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|F20|Freljord|Ionia|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I193" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr"/>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08MT024","n":3},{"c":"09IO053","n":3},{"c":"03MT035","n":3},{"c":"03MT088","n":3},{"c":"06MT008","n":3},{"c":"06MT035","n":3},{"c":"01IO009","n":3},{"c":"01IO020","n":3},{"c":"01IO026","n":3},{"c":"01IO052","n":3},{"c":"09DE033","n":2},{"c":"09IO055","n":2},{"c":"09IO058","n":2},{"c":"01FR002","n":1},{"c":"49FR003","n":1},{"c":"02F20001","n":1},{"c":"06MT006","n":1}]</t>
         </is>
       </c>
     </row>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N193"/>
+  <dimension ref="A1:N211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11252,16 +11252,20 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="B189" s="2" t="n">
-        <v>71</v>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
           <t>aKutti</t>
         </is>
       </c>
-      <c r="D189" s="2" t="n">
-        <v>223</v>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>223.0</t>
+        </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
@@ -11278,11 +11282,15 @@
           <t>Bandle City|Bilgewater|F34|F49|Freljord|Ionia|Piltover &amp; Zaun|Runeterra|Shurima</t>
         </is>
       </c>
-      <c r="H189" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I189" s="2" t="n">
-        <v>20</v>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="J189" s="2" t="inlineStr"/>
       <c r="K189" s="2" t="inlineStr"/>
@@ -11300,16 +11308,20 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="B190" s="2" t="n">
-        <v>75</v>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
           <t>Jøsst</t>
         </is>
       </c>
-      <c r="D190" s="2" t="n">
-        <v>218</v>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>218.0</t>
+        </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
@@ -11326,11 +11338,15 @@
           <t>Bandle City|Demacia|Freljord|Noxus</t>
         </is>
       </c>
-      <c r="H190" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I190" s="2" t="n">
-        <v>17</v>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
       <c r="K190" s="2" t="inlineStr"/>
@@ -11348,16 +11364,20 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="B191" s="2" t="n">
-        <v>77</v>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
           <t>ThePeterJ</t>
         </is>
       </c>
-      <c r="D191" s="2" t="n">
-        <v>212</v>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>212.0</t>
+        </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
@@ -11374,11 +11394,15 @@
           <t>Bandle City|Bilgewater|Freljord|Ionia|Piltover &amp; Zaun|Runeterra</t>
         </is>
       </c>
-      <c r="H191" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I191" s="2" t="n">
-        <v>19</v>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="J191" s="2" t="inlineStr"/>
       <c r="K191" s="2" t="inlineStr"/>
@@ -11396,16 +11420,20 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="B192" s="2" t="n">
-        <v>85</v>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
           <t>gabriel1223</t>
         </is>
       </c>
-      <c r="D192" s="2" t="n">
-        <v>190</v>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>190.0</t>
+        </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
@@ -11422,11 +11450,15 @@
           <t>Bandle City|Bilgewater|Ionia|Noxus</t>
         </is>
       </c>
-      <c r="H192" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I192" s="2" t="n">
-        <v>15</v>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr"/>
@@ -11444,16 +11476,20 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="B193" s="2" t="n">
-        <v>86</v>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
           <t>JulioA619</t>
         </is>
       </c>
-      <c r="D193" s="2" t="n">
-        <v>188</v>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>188.0</t>
+        </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
@@ -11470,11 +11506,15 @@
           <t>Demacia|F20|Freljord|Ionia|Mount Targon</t>
         </is>
       </c>
-      <c r="H193" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I193" s="2" t="n">
-        <v>17</v>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J193" s="2" t="inlineStr"/>
       <c r="K193" s="2" t="inlineStr"/>
@@ -11486,6 +11526,1006 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Sigep0361</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>SqxpFUWSXhjOG2G3E32vacxCUd0CcHXo6WH6NjmXhk8oZFEM5YFrkHiN-YDrizXIw-vz7MQZQinCBw</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>CMCACBQGFUAQMBYFAQCAMAIDAUHQMBAHCMLECRCKKAAQCBAGAIBACBAGA4AQQAYM</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr"/>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BW045","n":3},{"c":"06SH005","n":3},{"c":"04BW001","n":3},{"c":"04BW003","n":3},{"c":"04BW005","n":3},{"c":"04BW015","n":3},{"c":"04SH019","n":3},{"c":"04SH022","n":3},{"c":"04SH065","n":3},{"c":"04SH068","n":3},{"c":"04SH074","n":3},{"c":"04SH080","n":3},{"c":"04BW002","n":2},{"c":"01PZ006","n":1},{"c":"07FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Cameron6659</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>s3CY7jSkZBQc86Ss1XF-SgYAOH2gRTkLFFJKmMEldlkC21ECHBkfmaZpIbdNiDzVl0WMpmQN2gJdgQ</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAIFGEAQKCT7AEDAUFICAQCTMNYDBACQOKJKAQDAKFA3FUXAEAIEAU4ACBIKAEAA</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr"/>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI049","n":3},{"c":"05BC127","n":3},{"c":"06BC021","n":3},{"c":"04SI054","n":3},{"c":"04SI055","n":3},{"c":"08SI007","n":3},{"c":"08SI041","n":3},{"c":"08SI042","n":3},{"c":"06SI020","n":3},{"c":"06SI027","n":3},{"c":"06SI045","n":3},{"c":"06SI046","n":3},{"c":"04SI056","n":2},{"c":"05BC001","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Habalji</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>jfnUt6y1Tud4BT3rCl4OXpIZGpctBroR3bp6tCwZ83M-Im7W6-uPa5aI5wbitvlUfUYZymuVhePwNA</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAQDAMAQMCQ2AEDAGKIBBEFAWBABAMBAYKBXAUCQUBZJOSRQDJQBAAAQCAIDDE</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr"/>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02NX003","n":3},{"c":"06BC026","n":3},{"c":"06NX041","n":3},{"c":"09BC011","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01NX055","n":3},{"c":"05BC007","n":3},{"c":"05BC041","n":3},{"c":"05BC116","n":3},{"c":"05BC163","n":3},{"c":"05BC166","n":3},{"c":"01FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>superguh</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>177.0</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>TqicWWZomh_rA1Qn7vOBlPdqU3-JB79cAEZHeRK39ZUlLFDVD-yOPZvOAkDOE2V9wqqW_wNtl_RwHA</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>CQBQCBQEFYBACBBUHACAKBAWDAMRWBQBAECBAAIDAQFQCBIED4AQOCQJAEEQUFADAUFACMORAEBQCBAEB4AQKCWVAEAQKBAV</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F213|Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr"/>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06PZ046","n":3},{"c":"01PZ052","n":3},{"c":"01PZ056","n":3},{"c":"05PZ022","n":3},{"c":"05PZ024","n":3},{"c":"05PZ025","n":3},{"c":"05PZ027","n":3},{"c":"01PZ016","n":2},{"c":"03PZ011","n":2},{"c":"05PZ031","n":2},{"c":"07BC009","n":2},{"c":"09BC020","n":2},{"c":"05BC001","n":2},{"c":"05BC049","n":2},{"c":"05BC209","n":2},{"c":"01PZ004","n":1},{"c":"15FR005","n":1},{"c":"10F213001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Trifle Majere</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>tf641_l66h0MlgDHyL2MBwElSYYiRDAFWzDcQXXd7VZ56yipmoexmw4iN3hV9ypP0tOL4LGrw4tC8g</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCAIFGEAQKCT7AEDQUCIDBACQOJJKAYDAKDAQDMOCMLICAEDQKAQBBAFAEAA</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr"/>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI049","n":3},{"c":"05BC127","n":3},{"c":"07BC009","n":3},{"c":"08SI007","n":3},{"c":"08SI037","n":3},{"c":"08SI042","n":3},{"c":"06SI012","n":3},{"c":"06SI016","n":3},{"c":"06SI027","n":3},{"c":"06SI028","n":3},{"c":"06SI038","n":3},{"c":"06SI045","n":3},{"c":"07SI002","n":2},{"c":"08BC002","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Bardo Sanderson</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>V2mlYc2m7KOi_6BrQ8DdTfB43KD-QiqONY9BLhkMU9SWk2FV12fcTUEg3m2mI1OnVZIMFDRr36nFLQ</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>CQDACBIKP4AQKAAMAEDAABQBBAAAUAIIBEBQKCIKAEBQIDIUAQAQOCQJAEDQABIBBAAAMAIJBIGAEAIFBIYQCCIAFU</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Mount Targon|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr"/>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC127","n":3},{"c":"05DE012","n":3},{"c":"06DE006","n":3},{"c":"08DE010","n":3},{"c":"08MT003","n":3},{"c":"09BC001","n":3},{"c":"09BC003","n":3},{"c":"09BC004","n":3},{"c":"09BC013","n":3},{"c":"09BC020","n":3},{"c":"07BC009","n":2},{"c":"07DE005","n":2},{"c":"08DE006","n":2},{"c":"09BC012","n":2},{"c":"01SI010","n":1},{"c":"49FR009","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>killerbag</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>K-AwhCnag9qI4C9bqIB6NQKreWjCPnsFermvHAEOS3BU4FFSydQqt1XvE_qZ9jJKO7N36aIwrjngkw</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>CICACBACBUBACAQTEABAMARDEYCQGAQBAIFBCEQDAEBQEFABAYER2AQBAISTCAQBAMBAOAIGBEDA</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia|Mount Targon|Noxus</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr"/>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04IO013","n":3},{"c":"01IO019","n":3},{"c":"01IO032","n":3},{"c":"06IO035","n":3},{"c":"06IO038","n":3},{"c":"03IO001","n":3},{"c":"03IO002","n":3},{"c":"03IO010","n":3},{"c":"03IO017","n":3},{"c":"03IO018","n":3},{"c":"03IO020","n":2},{"c":"06MT029","n":2},{"c":"01IO037","n":2},{"c":"01IO049","n":2},{"c":"01NX002","n":1},{"c":"07FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Thetalhes</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>YvhJoVzodaz_VFYfZpw56tpW1moPX-oTAN9jnC-V3UNe9F8BHromSh6FzZOnZktlKLMVmcyqxnrjpQ</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAQBAIAQGBAFAECQIAQBBACBQBABAQEBSNBVAUAQCBB2AEDAIKYBBAARGAQBAECB4AQEAEEQUAQBAMAQEAIFAQHA</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr"/>
+      <c r="M201" s="2" t="inlineStr"/>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02FR002","n":3},{"c":"03PZ005","n":3},{"c":"05PZ002","n":3},{"c":"08PZ024","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"01PZ053","n":3},{"c":"01PZ058","n":2},{"c":"06PZ043","n":2},{"c":"08FR019","n":2},{"c":"01FR004","n":2},{"c":"01FR030","n":2},{"c":"04FR009","n":2},{"c":"04FR010","n":2},{"c":"01NX001","n":1},{"c":"02FR005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>mk7777777</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>z7M8XIW7YOCEDSfWlQSjrOr6gPlQTv4LDmjJathf8WWzBqHw8YoZCg4vLXZbFAnVKxgWL7OAgHjaUA</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>CIDACBAAAMAQKAAMAEDQABICAEAB2KYDAIDBMKB6AMBAAAQGBEBQCAQGFUAQEAAKAECQMAIBAECAAAQ</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr"/>
+      <c r="M202" s="2" t="inlineStr"/>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04DE003","n":3},{"c":"05DE012","n":3},{"c":"07DE005","n":3},{"c":"01DE029","n":3},{"c":"01DE043","n":3},{"c":"02BW022","n":3},{"c":"02BW040","n":3},{"c":"02BW062","n":3},{"c":"02DE002","n":3},{"c":"02DE006","n":3},{"c":"02DE009","n":3},{"c":"02BW045","n":2},{"c":"02DE010","n":2},{"c":"05BW001","n":2},{"c":"01PZ000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>MarioBat</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>LfF_0N00I--nj6QsgNhJxuiuZ920FYOhYtM2t9oHdiPMyKLXruSjpjn7QMj2ydxhN_cXaPVOKLKfvA</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>CMBQCBQHGMBAKBYLBYDAIBYDBUOCKJSIAMAQKBYHAEEQODADAQDTWTDNAIAQKBYCAICAOAJ6</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr"/>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06SH051","n":3},{"c":"05SH011","n":3},{"c":"05SH014","n":3},{"c":"04SH003","n":3},{"c":"04SH013","n":3},{"c":"04SH028","n":3},{"c":"04SH037","n":3},{"c":"04SH038","n":3},{"c":"04SH072","n":3},{"c":"05SH007","n":2},{"c":"09SH012","n":2},{"c":"04SH059","n":2},{"c":"04SH076","n":2},{"c":"04SH109","n":2},{"c":"01SI007","n":1},{"c":"02IO004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Davebo</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>VLKpCAmlUM3NEPhfXqQhNpavrwVpFqBTl0XhrDvMARySiqz6PJyEtbCAExJgF-KsxVkqbVZgpxDFSQ</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>CICQCAYEDEBAEBQJDIBQCBBHFU2AGCAGBALRSAYIAQCQQEQAAQAQEBADAECAMEABBADAEAIIAQKA</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F16|Freljord|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr"/>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03PZ025","n":3},{"c":"02BW009","n":3},{"c":"02BW026","n":3},{"c":"01PZ039","n":3},{"c":"01PZ045","n":3},{"c":"01PZ052","n":3},{"c":"08BW008","n":3},{"c":"08BW023","n":3},{"c":"08BW025","n":3},{"c":"08PZ005","n":3},{"c":"08PZ008","n":3},{"c":"08PZ018","n":3},{"c":"01IO004","n":1},{"c":"03FR004","n":1},{"c":"06F16001","n":1},{"c":"08BW002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Caitsyth</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>h8BCgMszqXz5pCS7doxfSCNwPjEL4Jr_fcSPpFWcD6Jr9k6SJixurVcExOLnWAU9BXJ7zVj6eVu9NA</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>CECAEAIDD4QQEBADAQHQECABCMMAMAIBCILB4JRJFIAQCBADBABACAIBAQAQIAYC</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr"/>
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"01FR018","n":3},{"c":"01FR022","n":3},{"c":"01FR030","n":3},{"c":"01FR038","n":3},{"c":"01FR041","n":3},{"c":"01FR042","n":3},{"c":"04NX008","n":2},{"c":"01FR001","n":1},{"c":"04FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Evilkyatt</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>VIhWFnBFEMr4EV5Wso7qWAXeLXjX7AsH9jGXBsQMzElxqWDkmhYduySwqjiw2LKgm8Vl4x7vCePEVA</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>CIEACAIEFUAQKAAMAEDAMHIBA4AAKAIIAAFACCAJAMBAMAAVDQBAMBAIEYBQCAQAAIAQIAADAIDAABQKAIAQKBBGAEDAAGA</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr"/>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ045","n":3},{"c":"05DE012","n":3},{"c":"06BW029","n":3},{"c":"07DE005","n":3},{"c":"08DE010","n":3},{"c":"08MT003","n":3},{"c":"06DE021","n":3},{"c":"06DE028","n":3},{"c":"06PZ008","n":3},{"c":"06PZ038","n":3},{"c":"02DE002","n":2},{"c":"04DE003","n":2},{"c":"06DE006","n":2},{"c":"06DE010","n":2},{"c":"01SI004","n":1},{"c":"38FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Referencer</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>sDf5tgw_un8gYbKIM-epWQDDzlxTQtLPB0Ia95B0yRJE_DL2K7xjtLfK6GucjSVjbKkuHTPDDM0_Zw</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>CICQCAYEDEBAEBQJDIBAQBAICIBQCBBHFU2AGCAGBALRSAQBAQDBAAIIAQCQGAIBAQAQCAQEAMAQQBAU</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Noxus|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr"/>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03PZ025","n":3},{"c":"02BW009","n":3},{"c":"02BW026","n":3},{"c":"08PZ008","n":3},{"c":"08PZ018","n":3},{"c":"01PZ039","n":3},{"c":"01PZ045","n":3},{"c":"01PZ052","n":3},{"c":"08BW008","n":3},{"c":"08BW023","n":3},{"c":"08BW025","n":3},{"c":"04BW016","n":2},{"c":"08PZ005","n":2},{"c":"01FR004","n":1},{"c":"01FR002","n":1},{"c":"04NX001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>AlphaCake</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>9hQmUSqOhNgk3nMQHq2u7g6YKk8wcs7RdPoL5G3f6a3O6KH-u5YPm2MfHRdCO-zSb_e9It9BWKj1Gg</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAYCAIAQMCQ2AEDQIBIBBEFAWAQFBJHJCAIEAECAYKBNGQCACAIEEYAQGBAFAECAIEABA4FASAQBAECACAIHBIIA</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03IO002","n":3},{"c":"06BC026","n":3},{"c":"07PZ005","n":3},{"c":"09BC011","n":3},{"c":"05BC078","n":3},{"c":"05BC145","n":3},{"c":"01PZ012","n":3},{"c":"01PZ040","n":3},{"c":"01PZ045","n":3},{"c":"01PZ052","n":3},{"c":"01PZ038","n":2},{"c":"03PZ005","n":2},{"c":"04PZ016","n":2},{"c":"07BC009","n":2},{"c":"01FR004","n":1},{"c":"01FR007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>DRredstone1221</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>NocTgROEfKLU_VprskbNwWRB6cyrnpCwLffRWT_3Yi24kPQdklHFGjtSPRww5KHRtz55-22d44GyJQ</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>CQDACBIKIYAQOCQUAEDQIEIBBAFAKAQFAQDA4AYBAQEBSNAFAEAQINIBAICAUAIFBIYQCBYKBEBAKBACBIAQCBYKB4</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I209" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr"/>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC070","n":3},{"c":"07BC020","n":3},{"c":"07PZ017","n":3},{"c":"08BC005","n":3},{"c":"05PZ006","n":3},{"c":"05PZ014","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"01PZ053","n":2},{"c":"02PZ010","n":2},{"c":"05BC049","n":2},{"c":"07BC009","n":2},{"c":"05PZ002","n":2},{"c":"05PZ010","n":2},{"c":"01SH010","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>BQOM</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>SMuWNdjF_ddF3z1o4zAo9IEMpJTNPDc3oSs3Km2WkvA7cMFZh0V1WYQMGyFOIIiG9XDxYfpViJIyYA</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>CIDACBQEFYAQOCINAEEQSAQCBAERQHYDAMEROV3AAMCQIFQZDIBQCAIEAQAQGCLEAEDASLIBAECQIGY</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I210" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06PZ046","n":3},{"c":"07MT013","n":3},{"c":"09MT002","n":3},{"c":"08MT024","n":3},{"c":"08MT031","n":3},{"c":"03MT023","n":3},{"c":"03MT087","n":3},{"c":"03MT096","n":3},{"c":"05PZ022","n":3},{"c":"05PZ025","n":3},{"c":"05PZ026","n":3},{"c":"01PZ004","n":2},{"c":"03MT100","n":2},{"c":"06MT045","n":2},{"c":"01SI004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Ghostmatterz</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>FOFXozF37zF8ilqEEn08-AAA9YqkzualzgQIwpR5WHUO021_-F3_y3-QBYiFsoK9UOH4ia6jaUnWHQ</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAQCAUAQIAQOAEDAECIBBECQ2BABAUFBKFZKAQDAKAYPEYXACAIBAUBQCAQGAUSS2</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Ionia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I211" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr"/>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02IO005","n":3},{"c":"04IO014","n":3},{"c":"06IO009","n":3},{"c":"09SI013","n":3},{"c":"01SI010","n":3},{"c":"01SI021","n":3},{"c":"01SI023","n":3},{"c":"01SI042","n":3},{"c":"06SI003","n":3},{"c":"06SI015","n":3},{"c":"06SI038","n":3},{"c":"06SI046","n":3},{"c":"01SI003","n":2},{"c":"02BW005","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N211"/>
+  <dimension ref="A1:N221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12388,16 +12388,20 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B209" s="2" t="n">
-        <v>137</v>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
           <t>DRredstone1221</t>
         </is>
       </c>
-      <c r="D209" s="2" t="n">
-        <v>132</v>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
@@ -12414,11 +12418,15 @@
           <t>Bandle City|Piltover &amp; Zaun|Shurima</t>
         </is>
       </c>
-      <c r="H209" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I209" s="2" t="n">
-        <v>16</v>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="J209" s="2" t="inlineStr"/>
       <c r="K209" s="2" t="inlineStr"/>
@@ -12436,16 +12444,20 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B210" s="2" t="n">
-        <v>138</v>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
           <t>BQOM</t>
         </is>
       </c>
-      <c r="D210" s="2" t="n">
-        <v>132</v>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
@@ -12462,11 +12474,15 @@
           <t>Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
         </is>
       </c>
-      <c r="H210" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I210" s="2" t="n">
-        <v>15</v>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J210" s="2" t="inlineStr"/>
       <c r="K210" s="2" t="inlineStr"/>
@@ -12484,16 +12500,20 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B211" s="2" t="n">
-        <v>146</v>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
           <t>Ghostmatterz</t>
         </is>
       </c>
-      <c r="D211" s="2" t="n">
-        <v>125</v>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
@@ -12510,11 +12530,15 @@
           <t>Bilgewater|Ionia|Shadow Isles</t>
         </is>
       </c>
-      <c r="H211" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I211" s="2" t="n">
-        <v>14</v>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J211" s="2" t="inlineStr"/>
       <c r="K211" s="2" t="inlineStr"/>
@@ -12526,6 +12550,552 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>SNGSwordKey</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>mWbI5IcyaXBE-DXBG0xjdevifvCa_8EuIPknWORQNftR0X3bE4M-q5DIWRqWc5g20CtxNTtvuyayHA</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>CMCACBQGFUAQMBYFAQCAOE2EJJIAKBAGAEBQIBIPAIAQIBQCAICAOFSBAEAQIBZ3</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr"/>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BW045","n":3},{"c":"06SH005","n":3},{"c":"04SH019","n":3},{"c":"04SH068","n":3},{"c":"04SH074","n":3},{"c":"04SH080","n":3},{"c":"04BW001","n":3},{"c":"04BW003","n":3},{"c":"04BW004","n":3},{"c":"04BW005","n":3},{"c":"04BW015","n":3},{"c":"04BW002","n":2},{"c":"04SH022","n":2},{"c":"04SH065","n":2},{"c":"01PZ007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>netinho99</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>pv-ejnBJpvr2-uknjMz4mPMiw3R4DenY9PoZl1KIB13JDHHA0bveLZ52rxlSXCMHyWvTBN-0c4ubjw</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>CIDACAYBCYAQMAJEAEEASHYCBAAQCEQDAEARIFZUAMBQSASAK4BACAIBFIAQGAITAIAQQAIIAIBQSBKU</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>F08|Freljord|Ionia|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr"/>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03FR022","n":3},{"c":"06FR036","n":3},{"c":"08MT031","n":3},{"c":"08FR001","n":3},{"c":"08FR018","n":3},{"c":"01FR020","n":3},{"c":"01FR023","n":3},{"c":"01FR052","n":3},{"c":"03MT002","n":3},{"c":"03MT064","n":3},{"c":"03MT087","n":3},{"c":"01FR042","n":2},{"c":"03FR019","n":2},{"c":"01F08001","n":1},{"c":"08IO003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>TheTiger18</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>8fE12p60nc7tjECPV0-xqhtcFfPPZfRUxwgZpp8e1CV-xHF5i9rGYIMkMYhGT0be6LtVoMexQXRU8g</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>CQBQCAYCCQAQMBAVAEEAICICAEAQINABA4BAWDYBAECCCAICAICQCAQEAYAQGBALAECQEBQBA4CASAIIBIDACCAGDQAQQBA2AEEQENICAYBCAJADAEBCSLRRAMDQEEITCQCAMBAJCIVS4BIFAQFBCGAZEY</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F08|F28|F32|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr"/>
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03IO020","n":3},{"c":"06PZ021","n":3},{"c":"08PZ009","n":3},{"c":"01PZ052","n":2},{"c":"07IO011","n":2},{"c":"01FR004","n":1},{"c":"33FR002","n":1},{"c":"02SI001","n":1},{"c":"02PZ006","n":1},{"c":"01NX004","n":1},{"c":"11FR005","n":1},{"c":"02BW001","n":1},{"c":"07PZ009","n":1},{"c":"01F08010","n":1},{"c":"06FR008","n":1},{"c":"06F28001","n":1},{"c":"08PZ026","n":1},{"c":"01MT002","n":1},{"c":"53IO006","n":1},{"c":"02F32036","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Worst Jangle NA</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Jsv9vweO73ILxpP8Pe_6VWshG6-jpMFZxZkQkgI1HIGXjlG7ftk3XiHUN1J0NIXGivYj_x7JyDDa8g</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>CUBQCCAJDYBAQAANDECAGAACBAFQ4BQBAMAAGAIEAAKACCAADIAQQCIDAEEAGAYCAEABGGQEAEEAACQBBAGA4AIIA4HAEAYAAQDQ</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>Demacia|F08|F14|Freljord|Mount Targon|Noxus|Shurima</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr"/>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08MT030","n":3},{"c":"08DE013","n":3},{"c":"08DE025","n":3},{"c":"03DE002","n":3},{"c":"03DE008","n":3},{"c":"03DE011","n":3},{"c":"03DE014","n":3},{"c":"03DE003","n":2},{"c":"04DE020","n":2},{"c":"08DE026","n":2},{"c":"08MT003","n":2},{"c":"08NX003","n":2},{"c":"01DE019","n":2},{"c":"01DE026","n":2},{"c":"01F08000","n":1},{"c":"10FR008","n":1},{"c":"12F14001","n":1},{"c":"08SH014","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Griefamere</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>3oeJRVQ8Ka1pd5I4A0MMBdd-pHnUQyUBA5F7AgIdRuZStwgFOk9VXQh0DTxq_fM6AOIvFeANRYqXjg</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>CUFACAIEGYAQEBR4AEBQKBQBAQEQ2AIFAEDACBQCAMAQMAYMAEDAYAQCAIBQGBADAEBQEDBIAAAQCAIDFY</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ054","n":3},{"c":"02BW060","n":3},{"c":"03SI006","n":3},{"c":"04MT013","n":3},{"c":"05FR006","n":3},{"c":"06IO003","n":3},{"c":"06NX012","n":3},{"c":"06RU002","n":3},{"c":"02NX003","n":3},{"c":"02NX004","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Fake o natty</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Ao_9cse6D8IYhbnJ52WgdKa57ebZ2Sb1R-ReHtKELhl91W4vHqSPLYAmz6K0oX7HKKuQwyOdXfpayQ</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>CMCQCAICFIAQMBZCAEEQOCIEAQDQGGRTOICQIAQEAUEASCYCAEBQEFABAQDV2AA</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Shurima</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I217" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J217" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="K217" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L217" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO042","n":3},{"c":"06SH034","n":3},{"c":"09SH009","n":3},{"c":"04SH003","n":3},{"c":"04SH026","n":3},{"c":"04SH051","n":3},{"c":"04SH114","n":3},{"c":"04IO004","n":3},{"c":"04IO005","n":3},{"c":"04IO008","n":3},{"c":"04IO009","n":3},{"c":"04IO011","n":3},{"c":"03IO020","n":2},{"c":"04SH093","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>XxzarathosxX</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>O6w7sP8jerF8FePPw9ieWuvzOqYI57IA2NpKemLm4yjzoW_LLw6mxpS7lzgFoB8jWBlskVDP0c-9Eg</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAICFEAQGAIWAEDACJABAYBCYAYBAEAQYIIDA4BAWEYUAQAQCARRAEDACKIBA4BBCAQBAEKCUAA</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I218" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr"/>
+      <c r="L218" s="2" t="inlineStr"/>
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO041","n":3},{"c":"03FR022","n":3},{"c":"06FR036","n":3},{"c":"06IO044","n":3},{"c":"01FR001","n":3},{"c":"01FR012","n":3},{"c":"01FR033","n":3},{"c":"07IO011","n":3},{"c":"07IO019","n":3},{"c":"07IO020","n":3},{"c":"01IO049","n":2},{"c":"06FR041","n":2},{"c":"07IO017","n":2},{"c":"01FR020","n":2},{"c":"01FR042","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Lambz369</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>kmHJ0fiFL5KAEXQIbr0iiqfUVOoezx8N8Xx1SigEyzXFLzPC4T4GYF10KXmpZ_8G_qQxrT7t4I3TyQ</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBQEFYAQSCQUAMAQIEBUHABQKBAWDAMQIAIBAUAQCAYEBMAQOBICAEEAKBYGAECQKAYBAYCSAAIHAQHQCCAEDEBACBIPDUBAKBA2DM</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F08|F32|Freljord|Ionia|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="I219" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="inlineStr"/>
+      <c r="L219" s="2" t="inlineStr"/>
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06PZ046","n":3},{"c":"09BC020","n":3},{"c":"01PZ016","n":3},{"c":"01PZ052","n":3},{"c":"01PZ056","n":3},{"c":"05PZ022","n":3},{"c":"05PZ024","n":3},{"c":"05PZ025","n":3},{"c":"01SI001","n":2},{"c":"03PZ011","n":2},{"c":"07SI002","n":2},{"c":"08SI007","n":2},{"c":"01SI005","n":1},{"c":"03FR006","n":1},{"c":"05F32001","n":1},{"c":"07PZ015","n":1},{"c":"01F08004","n":1},{"c":"25IO001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>1lud1d0</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>jRy9WzRUavolHuoXSLs57kwiShQXzO3KbkcwG0oqwCuiNfF37LCIxSMifA_I5cvK7ZArVXtAdfMDfA</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>CMAAMAIDAMGQCBIDCMAQQBJKAIAQGCY7AMCAOFBXHMCAIAYCAQEA6BQBAIBQUAQGAMOSQAQIAMER2AYBAMICCNIEAQBQGBQKCMCAIBYQEAYHM</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>F08|F29|Ionia|Noxus|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I220" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr"/>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03NX013","n":2},{"c":"05NX019","n":2},{"c":"08SI042","n":2},{"c":"01NX011","n":2},{"c":"01NX031","n":2},{"c":"04SH020","n":2},{"c":"04SH055","n":2},{"c":"04SH059","n":2},{"c":"04NX002","n":2},{"c":"04NX004","n":2},{"c":"04NX008","n":2},{"c":"04NX015","n":2},{"c":"01IO003","n":1},{"c":"10IO006","n":1},{"c":"03F29040","n":1},{"c":"02F08003","n":1},{"c":"09F29003","n":1},{"c":"01NX016","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>SanDuke</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>z_0mzRNSBBhTMJpBRRnVNPZ-xvroZtyBWvVb47heHWyBXP0RF4SKMXhjNcqM1KnT2CfV6_HZvDz6QA</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>CUCQCAIECQAQIAIPAEDAUKYBA4GA6AQBAEEBABYBAEARSAIBAMRACAQBAMAQMAIVAEDASIYBBEAQUAQDBEZVKBIBAEADCAIDAQJQCBQJFMAQQBISAIBQSDJD</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F08|F19|Freljord|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I221" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr"/>
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ020","n":3},{"c":"04FR015","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01FR025","n":2},{"c":"01NX034","n":2},{"c":"02FR003","n":2},{"c":"06FR021","n":2},{"c":"06MT035","n":2},{"c":"09FR010","n":2},{"c":"03MT051","n":2},{"c":"03MT085","n":2},{"c":"01FR000","n":1},{"c":"49FR003","n":1},{"c":"04F19001","n":1},{"c":"06MT043","n":1},{"c":"01F08005","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N221"/>
+  <dimension ref="A1:N236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12852,16 +12852,20 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B217" s="2" t="n">
-        <v>162</v>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
           <t>Fake o natty</t>
         </is>
       </c>
-      <c r="D217" s="2" t="n">
-        <v>115</v>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
@@ -12878,20 +12882,30 @@
           <t>Ionia|Shurima</t>
         </is>
       </c>
-      <c r="H217" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I217" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J217" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="K217" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L217" s="2" t="n">
-        <v>15</v>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
@@ -12910,16 +12924,20 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B218" s="2" t="n">
-        <v>163</v>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
           <t>XxzarathosxX</t>
         </is>
       </c>
-      <c r="D218" s="2" t="n">
-        <v>115</v>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
@@ -12936,11 +12954,15 @@
           <t>Freljord|Ionia</t>
         </is>
       </c>
-      <c r="H218" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I218" s="2" t="n">
-        <v>15</v>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J218" s="2" t="inlineStr"/>
       <c r="K218" s="2" t="inlineStr"/>
@@ -12958,16 +12980,20 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B219" s="2" t="n">
-        <v>164</v>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
           <t>Lambz369</t>
         </is>
       </c>
-      <c r="D219" s="2" t="n">
-        <v>114</v>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
@@ -12984,11 +13010,15 @@
           <t>Bandle City|F08|F32|Freljord|Ionia|Piltover &amp; Zaun|Shadow Isles</t>
         </is>
       </c>
-      <c r="H219" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="I219" s="2" t="n">
-        <v>18</v>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J219" s="2" t="inlineStr"/>
       <c r="K219" s="2" t="inlineStr"/>
@@ -13006,16 +13036,20 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B220" s="2" t="n">
-        <v>165</v>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
           <t>1lud1d0</t>
         </is>
       </c>
-      <c r="D220" s="2" t="n">
-        <v>114</v>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
@@ -13032,11 +13066,15 @@
           <t>F08|F29|Ionia|Noxus|Shadow Isles|Shurima</t>
         </is>
       </c>
-      <c r="H220" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I220" s="2" t="n">
-        <v>18</v>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J220" s="2" t="inlineStr"/>
       <c r="K220" s="2" t="inlineStr"/>
@@ -13054,16 +13092,20 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B221" s="2" t="n">
-        <v>167</v>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
           <t>SanDuke</t>
         </is>
       </c>
-      <c r="D221" s="2" t="n">
-        <v>113</v>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
@@ -13080,11 +13122,15 @@
           <t>Bandle City|F08|F19|Freljord|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra</t>
         </is>
       </c>
-      <c r="H221" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I221" s="2" t="n">
-        <v>19</v>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="J221" s="2" t="inlineStr"/>
       <c r="K221" s="2" t="inlineStr"/>
@@ -13096,6 +13142,852 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Kon Quinx</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>fx7diLuT9VhmCIpRc8kUUAPVsC_YfH_wonnX6AQziG2-0lrR9733kl9SQQwginETEbyYXZgbc6xDxg</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>CMDQCAICEAAQGAQRAECAEDIBAYBROAIGA4CQEBAHCRWQEBQCEIRQKAIDAIJACBAHG4AQKBYWAEDQEEICAYBAWJQBAECAOOY</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Noxus|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr"/>
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO032","n":3},{"c":"03IO017","n":3},{"c":"04IO013","n":3},{"c":"06NX023","n":3},{"c":"06SH005","n":3},{"c":"04SH020","n":3},{"c":"04SH109","n":3},{"c":"06IO034","n":3},{"c":"06IO035","n":3},{"c":"03IO018","n":2},{"c":"04SH055","n":2},{"c":"05SH022","n":2},{"c":"07IO017","n":2},{"c":"06IO011","n":2},{"c":"06IO038","n":2},{"c":"01PZ007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>deucetech</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>vC5TrzN8NIFHXXlujRpo_WtwlrLB1vwh6gauic3KeAUu2fosQbhEfKoOOV4hLZiK-2-trXNRdc-oBg</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAIFAEAQGAIDAEDACJABA4CQEAQIAEAR4BABAEGBIFZKAUAQCAJUAEAQKHIBAQAQYAIGAEUQCBQFEAAA</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr"/>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI001","n":3},{"c":"03FR003","n":3},{"c":"06FR036","n":3},{"c":"07SI002","n":3},{"c":"08FR001","n":3},{"c":"08FR030","n":3},{"c":"01FR012","n":3},{"c":"01FR020","n":3},{"c":"01FR023","n":3},{"c":"01FR042","n":3},{"c":"01FR052","n":2},{"c":"01SI029","n":2},{"c":"04FR012","n":2},{"c":"06FR041","n":2},{"c":"06SI032","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Giggleblaster</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>uSfeKJ4rzZO4HbtUtBMWHBI_-NDcAPu_Itf2Q474LSIshl2Cod4aLncjQyIucn4VEQGvqz8BSsjf-A</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>CECACAIBEYAQCAY7AEBQCAQCAQBQIDYGAEAQGIIBBAAAMAIIAEMAEBADAIEAEBQBCIQAKAIBBMLB4KJKAEAQMAI4</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="inlineStr"/>
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR038","n":3},{"c":"01NX031","n":3},{"c":"03FR002","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"01NX033","n":2},{"c":"08DE006","n":2},{"c":"08FR024","n":2},{"c":"04NX002","n":2},{"c":"04NX008","n":2},{"c":"06FR018","n":2},{"c":"06FR032","n":2},{"c":"01FR011","n":2},{"c":"01FR022","n":2},{"c":"01FR030","n":2},{"c":"01FR041","n":2},{"c":"01FR042","n":2},{"c":"01BW001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>Luiscantera99</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>VKXBpD0UOEbAyh-Hqcmb7jChhZwESsnQ_Aw-310se0znEl_Kea6E3Ad-ShOCK8jxe63sQt7orajPBA</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBIKP4AQMAAGAEEASAYFBEFACAYMBUKAMAIBAANACAQAAEAQKCRRAECQADABA4FASAQJBICBEAQBAUFACAIJAAWQ</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Mount Targon|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr"/>
+      <c r="M225" s="2" t="inlineStr"/>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC127","n":3},{"c":"06DE006","n":3},{"c":"08MT003","n":3},{"c":"09BC001","n":3},{"c":"09BC003","n":3},{"c":"09BC012","n":3},{"c":"09BC013","n":3},{"c":"09BC020","n":3},{"c":"01DE026","n":2},{"c":"02DE001","n":2},{"c":"05BC049","n":2},{"c":"05DE012","n":2},{"c":"07BC009","n":2},{"c":"09BC004","n":2},{"c":"09BC018","n":2},{"c":"01SI010","n":1},{"c":"01FR009","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>LGD Gamiño</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>9IL5Ef4JoDTZJphowMi_Yl-aILi61M66mcqNhy9aC2nRYDytWXsTGYzEQoKqwKFRkdUWPmCP6H-H_w</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>CQEACAIBCYAQGCJIAECQCDYBAUEQUAIGAEOACBYJAMAQQAAGAEEACGAEAECQUHIBBACREAQBAEESSAYDBELTOVICAEDACIABAYEQM</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Demacia|Freljord|Mount Targon|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr"/>
+      <c r="M226" s="2" t="inlineStr"/>
+      <c r="N226" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"03MT040","n":3},{"c":"05FR015","n":3},{"c":"05MT010","n":3},{"c":"06FR028","n":3},{"c":"07MT003","n":3},{"c":"08DE006","n":3},{"c":"08FR024","n":3},{"c":"05BC029","n":2},{"c":"08SI018","n":2},{"c":"01FR009","n":2},{"c":"01FR041","n":2},{"c":"03MT023","n":2},{"c":"03MT055","n":2},{"c":"03MT085","n":2},{"c":"01BW001","n":1},{"c":"32FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>IntoTheDusk</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>4CwfSVAdN4m7p5ScQO8-8LoR-RbodZDyMZoY6W_cpwq64il3FKqEwM99CuJJHDkH1IebNboDNi7OFw</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>CICQCBAFB4AQMBJLAEEAKHQCAICQQCQFAIDBOLBPGU4AIAIBAUAQCAQGE4AQMBRGAEDQMKYBAIBAMHRF</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Ionia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr"/>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04SI015","n":3},{"c":"06SI043","n":3},{"c":"08SI030","n":3},{"c":"02SI008","n":3},{"c":"02SI010","n":3},{"c":"02BW023","n":3},{"c":"02BW044","n":3},{"c":"02BW047","n":3},{"c":"02BW053","n":3},{"c":"02BW056","n":3},{"c":"01SI001","n":2},{"c":"02BW039","n":2},{"c":"06BW038","n":2},{"c":"07BW043","n":2},{"c":"02IO006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Voulge</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>5Ekucr8sZhwq2CAYxc3g9EEZkMPtR8iDm3cOdX2MuZNrTn8fhTXOsvOZnOdVudi0Vu-ev4UavO7kMw</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>CQDQCAIBCYAQEBROAEDACFIBA4FASAIIBIBACCABDABAKCQFDUDACBABBIAQKCWZAEAQMAIYAEEACEYCAEAQKKQCAYFCQLYA</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr"/>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"02BW046","n":3},{"c":"06FR021","n":3},{"c":"07BC009","n":3},{"c":"08BC002","n":3},{"c":"08FR024","n":3},{"c":"05BC005","n":3},{"c":"05BC029","n":3},{"c":"04FR010","n":2},{"c":"05BC217","n":2},{"c":"06FR024","n":2},{"c":"08FR019","n":2},{"c":"01FR005","n":2},{"c":"01FR042","n":2},{"c":"06BC040","n":2},{"c":"06BC047","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>PirataDoDavila</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Xb_TdoxL4oP0ryHVyoAfdih7QCTf2cN13JQwZgkYuFuqm_Qv5D45sI2qRBrRPzWspxrHy4EzSpFnYQ</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>CUCQCBQGDUAQMAAGAEDAYCABBAARQAQGAECAWBQBAEARMAIDAEBACBQGDMAQMBIDAIDAAEIYAMDACCAMCICACBABBIAQMAJHAEEAABQBBAARG</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|F39|Freljord|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr"/>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BW029","n":3},{"c":"06DE006","n":3},{"c":"06RU008","n":3},{"c":"08FR024","n":3},{"c":"06FR004","n":3},{"c":"06FR011","n":3},{"c":"01FR022","n":2},{"c":"03FR002","n":2},{"c":"06BW027","n":2},{"c":"06SI003","n":2},{"c":"06DE017","n":2},{"c":"06DE024","n":2},{"c":"06FR008","n":2},{"c":"06FR012","n":2},{"c":"06FR018","n":2},{"c":"01PZ001","n":1},{"c":"10FR006","n":1},{"c":"01F39001","n":1},{"c":"08DE006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>ZequiSlo</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>sDHVIztIwYIUMUMQMbtW8_F0xNYe4ZkpSBHW9D2r8pxioi2rKuddbjA33gjylSaOO6jIvO4FCZQXRg</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>CEBAEBIEAYHAIAIEBAMTIOQFAECACCQBBACBQAQFAQBAUAQIAEJRQBABAECBMHRKAIAQCAIBAECACDA</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="K230" s="2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05PZ006","n":3},{"c":"05PZ014","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"01PZ058","n":3},{"c":"04FR010","n":2},{"c":"08PZ024","n":2},{"c":"05PZ002","n":2},{"c":"05PZ010","n":2},{"c":"08FR019","n":2},{"c":"08FR024","n":2},{"c":"01FR004","n":2},{"c":"01FR022","n":2},{"c":"01FR030","n":2},{"c":"01FR042","n":2},{"c":"01FR001","n":1},{"c":"01FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>Kidrobot123</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>GGgM83nY2yjo8GRYdcY5-_C1fzPnQr8h6htZVFs3CSPZbiBv9fHW5AGWk06pyekwDQTitQueVleKdA</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCAIBBQAQCARJAEBQCFQBAMBBGAIGAIWAEBQBEQUQGBYCBMIRIBABAEASUAIFAIDACBQBEYBAOAQTFEAA</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr"/>
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR012","n":3},{"c":"01IO041","n":3},{"c":"03FR022","n":3},{"c":"03IO019","n":3},{"c":"06IO044","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"07IO011","n":3},{"c":"07IO017","n":3},{"c":"07IO020","n":3},{"c":"01FR042","n":2},{"c":"05IO006","n":2},{"c":"06FR038","n":2},{"c":"07IO019","n":2},{"c":"07IO041","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>sminkly</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>GVZv9Ipg_24v_SAhcv8fLdi2p9VSf79Q_xo8l8cJt3TNg7nx7FMC7knNBf6FxUFb2WiRHxRGUyJKuA</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAICBEAQIAACAECQADACAEAB2KYCA4AAKDQEAMBACAQKCEBACAYCCIBACAQGHEAQCBQAGA</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Demacia|Ionia</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I232" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr"/>
+      <c r="L232" s="2" t="inlineStr"/>
+      <c r="M232" s="2" t="inlineStr"/>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO009","n":3},{"c":"04DE002","n":3},{"c":"05DE012","n":3},{"c":"01DE029","n":3},{"c":"01DE043","n":3},{"c":"07DE005","n":3},{"c":"07DE014","n":3},{"c":"03IO001","n":3},{"c":"03IO002","n":3},{"c":"03IO010","n":3},{"c":"03IO017","n":3},{"c":"03IO018","n":2},{"c":"01IO006","n":2},{"c":"01IO057","n":2},{"c":"01BW000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>Bonesteeler</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>UMNYDLzfXcTOvXZOnv79Ho7d62dNNcIdInO0r-8gfug8eLnQKircEehlav_5Z6ZgrPV5014jvo7_Ng</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>CQEACAYCAIAQGBAFAECAIEABAYFBUAIHAQCQCCIKBMBAKCSOSEAQIAIEBQUC2NABAIAQIHBGAA</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Ionia|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I233" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J233" s="2" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="K233" s="2" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="L233" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N233" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03IO002","n":3},{"c":"03PZ005","n":3},{"c":"04PZ016","n":3},{"c":"06BC026","n":3},{"c":"07PZ005","n":3},{"c":"09BC011","n":3},{"c":"05BC078","n":3},{"c":"05BC145","n":3},{"c":"01PZ012","n":3},{"c":"01PZ040","n":3},{"c":"01PZ045","n":3},{"c":"01PZ052","n":3},{"c":"01PZ028","n":2},{"c":"01PZ038","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Pheonixwish</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>cl8N9ojUtJZiDT3O4PII8zqeD1XLqjcacmSQPybLp6_NhNfzUjCHa9AyCDJ7wMuZ2tuWVfO9G3G9pQ</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAYEDEAQKAYGAEEAIEQEAEBQYFBHFADACBABBQOCOKBNAAAQCAIDA4</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I234" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J234" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K234" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L234" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N234" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03PZ025","n":3},{"c":"05NX006","n":3},{"c":"08PZ018","n":3},{"c":"01NX012","n":3},{"c":"01NX020","n":3},{"c":"01NX039","n":3},{"c":"01NX040","n":3},{"c":"01PZ001","n":3},{"c":"01PZ012","n":3},{"c":"01PZ028","n":3},{"c":"01PZ039","n":3},{"c":"01PZ040","n":3},{"c":"01PZ045","n":3},{"c":"01FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Estudante de Mat</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>rUh-MxR_6Nd3cz6xcl8hbvAwoxH_jZHnM-5moWJhC4Xr8z4WEinjVmQNf21wGbqwDytgVuZX_XN4Wg</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>CUFACAIEGYAQEBR4AEBQKBQBAQEQ2AIFAEDACBQCAMAQMAYMAEDAYAQCAIBQGBADAEBQEDBIAAAQCAIDFY</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I235" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J235" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K235" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L235" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N235" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ054","n":3},{"c":"02BW060","n":3},{"c":"03SI006","n":3},{"c":"04MT013","n":3},{"c":"05FR006","n":3},{"c":"06IO003","n":3},{"c":"06NX012","n":3},{"c":"06RU002","n":3},{"c":"02NX003","n":3},{"c":"02NX004","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01FR003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>MeteorB</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>KUXM-ICBFTnIpm4YMs2UrWQmQeU2UvU0wz-StZbw8-vCUyeU2-e8t_yF6_qNMzx6Z5zFDzQPuISVfg</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>CUFACAIBCYAQCAYPAEBQCAQBAUFKCAIBA4DCUAIHAEIACBYECUAQODAMAICQCDYRAIEACEYYAIAQMAAGAEDACKAA</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Demacia|Freljord|Noxus|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I236" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr"/>
+      <c r="M236" s="2" t="inlineStr"/>
+      <c r="N236" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"01NX015","n":3},{"c":"03FR002","n":3},{"c":"05BC161","n":3},{"c":"07BW042","n":3},{"c":"07FR016","n":3},{"c":"07PZ021","n":3},{"c":"07RU012","n":3},{"c":"05FR015","n":3},{"c":"05FR017","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"06DE006","n":2},{"c":"06FR040","n":2}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N236"/>
+  <dimension ref="A1:N250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13724,16 +13724,20 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B232" s="2" t="n">
-        <v>189</v>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
           <t>sminkly</t>
         </is>
       </c>
-      <c r="D232" s="2" t="n">
-        <v>100</v>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
@@ -13750,11 +13754,15 @@
           <t>Bilgewater|Demacia|Ionia</t>
         </is>
       </c>
-      <c r="H232" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I232" s="2" t="n">
-        <v>15</v>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J232" s="2" t="inlineStr"/>
       <c r="K232" s="2" t="inlineStr"/>
@@ -13772,16 +13780,20 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B233" s="2" t="n">
-        <v>193</v>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
           <t>Bonesteeler</t>
         </is>
       </c>
-      <c r="D233" s="2" t="n">
-        <v>100</v>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
@@ -13798,20 +13810,30 @@
           <t>Bandle City|Ionia|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H233" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I233" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J233" s="2" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="K233" s="2" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L233" s="2" t="n">
-        <v>0</v>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="M233" s="2" t="inlineStr">
         <is>
@@ -13830,16 +13852,20 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B234" s="2" t="n">
-        <v>195</v>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
           <t>Pheonixwish</t>
         </is>
       </c>
-      <c r="D234" s="2" t="n">
-        <v>100</v>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
@@ -13856,20 +13882,30 @@
           <t>Freljord|Noxus|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H234" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I234" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J234" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K234" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L234" s="2" t="n">
-        <v>0</v>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="M234" s="2" t="inlineStr">
         <is>
@@ -13888,16 +13924,20 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B235" s="2" t="n">
-        <v>196</v>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
           <t>Estudante de Mat</t>
         </is>
       </c>
-      <c r="D235" s="2" t="n">
-        <v>100</v>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
@@ -13914,20 +13954,30 @@
           <t>Bilgewater|Freljord|Ionia|Mount Targon|Noxus|Piltover &amp; Zaun|Runeterra|Shadow Isles</t>
         </is>
       </c>
-      <c r="H235" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I235" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J235" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K235" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="L235" s="2" t="n">
-        <v>7.5</v>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="K235" s="2" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
       </c>
       <c r="M235" s="2" t="inlineStr">
         <is>
@@ -13946,16 +13996,20 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B236" s="2" t="n">
-        <v>197</v>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
           <t>MeteorB</t>
         </is>
       </c>
-      <c r="D236" s="2" t="n">
-        <v>100</v>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -13972,11 +14026,15 @@
           <t>Bandle City|Bilgewater|Demacia|Freljord|Noxus|Piltover &amp; Zaun|Runeterra</t>
         </is>
       </c>
-      <c r="H236" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I236" s="2" t="n">
-        <v>14</v>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J236" s="2" t="inlineStr"/>
       <c r="K236" s="2" t="inlineStr"/>
@@ -13988,6 +14046,774 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Carrot Spirit</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>NF9ZwowvSyBz45YcetDzIlsyVLSXCW7enL4zTVyKjr2XKr2XBFWy1fc_CdtXAjFtiOBxXQRJAYTRUA</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAQDAMAQMCQ2AEDAGKIBBEFAWBABAMBAYKBXAQCQUBZJUMA2MAICAEAQGGIBAUFHIAA</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Noxus</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr"/>
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr"/>
+      <c r="M237" s="2" t="inlineStr"/>
+      <c r="N237" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02NX003","n":3},{"c":"06BC026","n":3},{"c":"06NX041","n":3},{"c":"09BC011","n":3},{"c":"01NX002","n":3},{"c":"01NX012","n":3},{"c":"01NX040","n":3},{"c":"01NX055","n":3},{"c":"05BC007","n":3},{"c":"05BC041","n":3},{"c":"05BC163","n":3},{"c":"05BC166","n":3},{"c":"01NX025","n":2},{"c":"05BC116","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>DK catmonX</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>bpoOMszo_WlxKnKHIgrSIt2tLo8-wImxEaWLM6K5lD3h_8aVXxLxbNAmKFG-nWUpVs4vaGxe6iYz3w</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBIKXQAQCBQHAUAQOBZOAUCAOAI4J5JWIAQBAQDV2AIFBLDACBQBAECAQAIIBIDAEBAHHOBACAQHBICQ6AYFBINSRJABAMDAOMBRHA</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Ionia|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr"/>
+      <c r="M238" s="2" t="inlineStr"/>
+      <c r="N238" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC188","n":3},{"c":"06SH005","n":3},{"c":"07SH046","n":3},{"c":"04SH001","n":3},{"c":"04SH028","n":3},{"c":"04SH079","n":3},{"c":"04SH083","n":3},{"c":"04SH100","n":3},{"c":"04SH093","n":2},{"c":"05BC198","n":2},{"c":"01FR004","n":1},{"c":"08FR008","n":1},{"c":"10BW002","n":1},{"c":"04SH059","n":1},{"c":"130IO007","n":1},{"c":"10SI015","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>almiral87</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>vvhYHWysWyfwbYlxI13kS7_y1W2gb2B-ThEFjZjOBJvYIET5Ziji5Te94uWel7CNR2Iv2yjxziOfIg</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>CQCACAYFCAAQKCUYAEAQKBIJAIDAIKROAIAQKBIOAMEAIAIIBEEQCAQEAYAQGBAEAECAKOABAUCBWAIFAUBQEBAEA4IQGAIED4SDIAYBAUAR2NQEAYCBEIRIFM</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Ionia|Noxus|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr"/>
+      <c r="K239" s="2" t="inlineStr"/>
+      <c r="L239" s="2" t="inlineStr"/>
+      <c r="M239" s="2" t="inlineStr"/>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03SI016","n":3},{"c":"05BC152","n":3},{"c":"05SI009","n":3},{"c":"06PZ042","n":3},{"c":"06PZ046","n":3},{"c":"05SI014","n":2},{"c":"08PZ001","n":2},{"c":"08PZ008","n":2},{"c":"08PZ009","n":2},{"c":"01IO004","n":1},{"c":"06FR003","n":1},{"c":"04PZ001","n":1},{"c":"04SI056","n":1},{"c":"01SI004","n":1},{"c":"27FR005","n":1},{"c":"05NX002","n":1},{"c":"04PZ007","n":1},{"c":"17NX001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Fouur</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>wXbl3uoZp0uLrS0f2bJs6u81liOtfHnpY0NawKgjhgcqobNu8iaIhiqh-ziz5RYGpRyqBJQh6fa_vg</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCAYEBMAQMBBOAEDQKAQDAECBANBYAMCQIFQYDEBQCAIFAEAQSCQUAIEAKBYSAQAQKBA7AECQKAYBA4CA6AQBAUOTC</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Freljord|Noxus|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr"/>
+      <c r="K240" s="2" t="inlineStr"/>
+      <c r="L240" s="2" t="inlineStr"/>
+      <c r="M240" s="2" t="inlineStr"/>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03PZ011","n":3},{"c":"06PZ046","n":3},{"c":"07SI002","n":3},{"c":"01PZ016","n":3},{"c":"01PZ052","n":3},{"c":"01PZ056","n":3},{"c":"05PZ022","n":3},{"c":"05PZ024","n":3},{"c":"05PZ025","n":3},{"c":"01SI001","n":2},{"c":"09BC020","n":2},{"c":"08SI007","n":2},{"c":"08SI018","n":2},{"c":"01SI004","n":1},{"c":"31FR005","n":1},{"c":"05NX001","n":1},{"c":"07PZ015","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>jeebeleebus</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>08wyC1618GPiQUr95n1IJMUvaEEHk3PzKIwMcDv26zKfeyBQXOBF8p9Fjtc1nZXCa7Z59XpR-GuXxQ</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBQCEABAIBZHJEBAMBYFGABQSARNGM5AMAICAICQCAYCCQAQQCQGAEEAGDABBEBDOAIJA4FAGAIBAIYQCBQHHABAIBYBM4</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F56|Freljord|Ionia|Noxus|Shurima</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr"/>
+      <c r="K241" s="2" t="inlineStr"/>
+      <c r="L241" s="2" t="inlineStr"/>
+      <c r="M241" s="2" t="inlineStr"/>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06IO032","n":3},{"c":"04SH039","n":3},{"c":"04SH073","n":3},{"c":"06SH005","n":3},{"c":"06SH048","n":3},{"c":"09IO045","n":3},{"c":"09IO051","n":3},{"c":"09IO058","n":3},{"c":"02IO005","n":2},{"c":"03IO020","n":2},{"c":"08BC006","n":2},{"c":"08NX012","n":2},{"c":"09IO055","n":2},{"c":"09SH010","n":2},{"c":"01FR002","n":1},{"c":"49FR006","n":1},{"c":"07F56002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Azaker</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>zOrNs85F6cZ9fzgWiqDd0A4JHnETPHSHgwqj_-A50pc-9CuohVY6oW6ArKlK-MSQJ8wTkgOI6WftOw</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>CQCACCAKAYBAOCIDBUBQMCIKFMWQIAYJH5FWA3QDAEAQEGABAIBAMAYDBE5FJWIBAA</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Ionia|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr"/>
+      <c r="K242" s="2" t="inlineStr"/>
+      <c r="L242" s="2" t="inlineStr"/>
+      <c r="M242" s="2" t="inlineStr"/>
+      <c r="N242" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08BC006","n":3},{"c":"07MT003","n":3},{"c":"07MT013","n":3},{"c":"06MT010","n":3},{"c":"06MT043","n":3},{"c":"06MT045","n":3},{"c":"03MT063","n":3},{"c":"03MT075","n":3},{"c":"03MT096","n":3},{"c":"03MT110","n":3},{"c":"01IO024","n":2},{"c":"02IO006","n":2},{"c":"03MT058","n":2},{"c":"03MT084","n":2},{"c":"03MT217","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>S0dier</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>bCKEYS_u5YNUPOotflk8jNBu0lAL3VLN57SYLhXlObTD7urr-0hprm2CEFNFBtqrciyvMUA7PXpgSQ</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>CEBQEBADAQHQGAIDD4QTKBIBAECBMHRGFEBACBADBABQCAIBBMYAEAIBAEVACBQBDQ</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr"/>
+      <c r="K243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr"/>
+      <c r="M243" s="2" t="inlineStr"/>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"01NX031","n":3},{"c":"01NX033","n":3},{"c":"01NX053","n":3},{"c":"01FR004","n":3},{"c":"01FR022","n":3},{"c":"01FR030","n":3},{"c":"01FR038","n":3},{"c":"01FR041","n":3},{"c":"04NX008","n":2},{"c":"01FR001","n":2},{"c":"01FR011","n":2},{"c":"01FR048","n":2},{"c":"01FR001","n":1},{"c":"42FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Hekix</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>1CK23PwoEcTa2_0pqZAlaghwoqIY-CKPaYOVSgXAZrnqcCXnCghPMpvq9XuQL5Y8ut3x99VigcQ3Lg</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>CUDACAIBD4AQGBQRAEEAUBQCA4FASEQDAYFA6EJAAQCQUAJIGGMACAIBAYBRQAQBBAFBKAIIBQHA</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|F08|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr"/>
+      <c r="L244" s="2" t="inlineStr"/>
+      <c r="M244" s="2" t="inlineStr"/>
+      <c r="N244" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR031","n":3},{"c":"03BW017","n":3},{"c":"08BC006","n":3},{"c":"07BC009","n":3},{"c":"07BC018","n":3},{"c":"06BC015","n":3},{"c":"06BC017","n":3},{"c":"06BC032","n":3},{"c":"05BC001","n":3},{"c":"05BC040","n":3},{"c":"05BC049","n":3},{"c":"05BC152","n":3},{"c":"06NX024","n":2},{"c":"01F08010","n":1},{"c":"21FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>SilentRevelation</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>am-FJH5U92ZZ_-7A6GXhZCPQVBXPsCtH_UaynHKgFy0ybDIMXgQfoX9uCYd4OnWn9Kr-w5Z40R1Yvw</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAIBBQAQCARJAEBQCFQBA4BAWAQGAESCSCABAEBDCAIDAIKACBICAYAQMAJGAEDAELACAEARIKQCAIBAKCICA4BBCFAA</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr"/>
+      <c r="K245" s="2" t="inlineStr"/>
+      <c r="L245" s="2" t="inlineStr"/>
+      <c r="M245" s="2" t="inlineStr"/>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR012","n":3},{"c":"01IO041","n":3},{"c":"03FR022","n":3},{"c":"07IO011","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"01IO049","n":2},{"c":"03IO020","n":2},{"c":"05IO006","n":2},{"c":"06FR038","n":2},{"c":"06IO044","n":2},{"c":"01FR020","n":2},{"c":"01FR042","n":2},{"c":"02IO005","n":2},{"c":"02IO009","n":2},{"c":"07IO017","n":2},{"c":"07IO020","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>PirataRJ</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>o7RRQb00403JURN5EPFjCfqSpJNmh2GBn7vh_J49v_i2eFWqMNVUrt6P5D_uYpzIJD_AFV2w6FMOAw</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>CIDACAIDFAAQEAYDAECQMAIBAYDASAQGAMGCABQCAYEQ2FRXHQ7AEAIEAMLACBQGFUAA</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Noxus</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX040","n":3},{"c":"02NX003","n":3},{"c":"05BW001","n":3},{"c":"06BW009","n":3},{"c":"06NX012","n":3},{"c":"06NX032","n":3},{"c":"02BW009","n":3},{"c":"02BW013","n":3},{"c":"02BW022","n":3},{"c":"02BW055","n":3},{"c":"02BW060","n":3},{"c":"02BW062","n":3},{"c":"04NX022","n":2},{"c":"06BW045","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>specops282</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>kFlWEhpA7WCIER_-s5OVmguqc2bm8KifmcWC9zTMv2WLgzTW6p7u9Y7no29WTQf0XfDz7oKx-NEedA</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBIEAYAQOCQUAEDQIEIDAECAQGJVAUAQOCQJAEEAIGACAECDIOQCAUFACRQFAUCAECQNBYJQA</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I247" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J247" s="2" t="inlineStr"/>
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr"/>
+      <c r="M247" s="2" t="inlineStr"/>
+      <c r="N247" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05PZ006","n":3},{"c":"07BC020","n":3},{"c":"07PZ017","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ053","n":3},{"c":"07BC009","n":2},{"c":"08PZ024","n":2},{"c":"01PZ052","n":2},{"c":"01PZ058","n":2},{"c":"05BC001","n":2},{"c":"05BC070","n":2},{"c":"05PZ002","n":2},{"c":"05PZ010","n":2},{"c":"05PZ013","n":2},{"c":"05PZ014","n":2},{"c":"05PZ019","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Ning Rookie</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>OGxDo6XQKEGpusz5LMePXYA5srW0Ls7PO_DLzRwrMjqjage_6OLgqFMzEl9OGZP-b9qlxJlPbiR7Jw</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>CQCACAYJKEAQKCRJAEDASCADAEABKHJLBEAQEAAHAEBQSIYBAQEREAIGAAUQCBYAAUAQQCIYAEEQAIICAEAAEMYCAYEQIHIA</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I248" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr"/>
+      <c r="M248" s="2" t="inlineStr"/>
+      <c r="N248" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03MT081","n":3},{"c":"05BC041","n":3},{"c":"06MT008","n":3},{"c":"01DE021","n":3},{"c":"01DE029","n":3},{"c":"01DE043","n":3},{"c":"02DE007","n":2},{"c":"03MT035","n":2},{"c":"04MT018","n":2},{"c":"06DE041","n":2},{"c":"07DE005","n":2},{"c":"08MT024","n":2},{"c":"09DE033","n":2},{"c":"01DE002","n":2},{"c":"01DE051","n":2},{"c":"06MT004","n":2},{"c":"06MT029","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>3XT43M3Special</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>n7k1YnEo9x2wXZd2cwZZfIkgRff0QICb3yvfQQ1IuSY1Rbmbbngu4khrmhDTaIg6z2n3i_aBDucpjA</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>CQBQCBQHGABAIBZHJEBQSARNGM5AOAIDAIKACBAHAEAQKAQGAEEAUBQBBEDQUAQGA4CTQAQHAIJRIAYBAYBCIAIIAMGAEBAHHOFAC</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Ionia|Runeterra|Shurima</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I249" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
+      <c r="K249" s="2" t="inlineStr"/>
+      <c r="L249" s="2" t="inlineStr"/>
+      <c r="M249" s="2" t="inlineStr"/>
+      <c r="N249" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06SH048","n":3},{"c":"04SH039","n":3},{"c":"04SH073","n":3},{"c":"09IO045","n":3},{"c":"09IO051","n":3},{"c":"09IO058","n":3},{"c":"03IO020","n":2},{"c":"04SH001","n":2},{"c":"05IO006","n":2},{"c":"08BC006","n":2},{"c":"09SH010","n":2},{"c":"06SH005","n":2},{"c":"06SH056","n":2},{"c":"07IO019","n":2},{"c":"07IO020","n":2},{"c":"01BW002","n":1},{"c":"36FR008","n":1},{"c":"03RU002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Jef Cabeça</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>TDduUr4WgHBujH1fMopZIGNGL57NG8TpKFDpwbwg_yFVtFxPUi6feBLN8uuefvE_ARQSB9ak6L966w</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>CIBACAYJBEBAGBADBMEQCAYEAUAQICIKAECAIBYBAUCCMAIGBEVQCBQEFYAQQBAJAEEAKEQEAMEROKSW3UAQOAIBAQ2ACAYJLQAQIBARAECQIGIBAYES2AIGAQVQCBYJAE</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>F45|F92|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I250" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="inlineStr"/>
+      <c r="L250" s="2" t="inlineStr"/>
+      <c r="M250" s="2" t="inlineStr"/>
+      <c r="N250" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03MT009","n":3},{"c":"03PZ003","n":3},{"c":"03PZ011","n":3},{"c":"03PZ005","n":2},{"c":"04MT010","n":2},{"c":"04PZ007","n":2},{"c":"05PZ038","n":2},{"c":"06MT043","n":2},{"c":"06PZ046","n":2},{"c":"08PZ009","n":2},{"c":"08SI018","n":2},{"c":"03MT023","n":2},{"c":"03MT042","n":2},{"c":"03MT086","n":2},{"c":"03MT221","n":2},{"c":"01FR004","n":1},{"c":"52FR003","n":1},{"c":"09F92001","n":1},{"c":"04PZ017","n":1},{"c":"01SI004","n":1},{"c":"25FR006","n":1},{"c":"09F45001","n":1}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N250"/>
+  <dimension ref="A1:N257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -14628,16 +14628,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B247" s="2" t="n">
-        <v>247</v>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
           <t>specops282</t>
         </is>
       </c>
-      <c r="D247" s="2" t="n">
-        <v>100</v>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
@@ -14654,11 +14658,15 @@
           <t>Bandle City|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H247" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I247" s="2" t="n">
-        <v>17</v>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J247" s="2" t="inlineStr"/>
       <c r="K247" s="2" t="inlineStr"/>
@@ -14676,16 +14684,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B248" s="2" t="n">
-        <v>249</v>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
           <t>Ning Rookie</t>
         </is>
       </c>
-      <c r="D248" s="2" t="n">
-        <v>99</v>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -14702,11 +14714,15 @@
           <t>Bandle City|Demacia|Mount Targon</t>
         </is>
       </c>
-      <c r="H248" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I248" s="2" t="n">
-        <v>17</v>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J248" s="2" t="inlineStr"/>
       <c r="K248" s="2" t="inlineStr"/>
@@ -14724,16 +14740,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B249" s="2" t="n">
-        <v>260</v>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
           <t>3XT43M3Special</t>
         </is>
       </c>
-      <c r="D249" s="2" t="n">
-        <v>88</v>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
@@ -14750,11 +14770,15 @@
           <t>Bandle City|Bilgewater|Freljord|Ionia|Runeterra|Shurima</t>
         </is>
       </c>
-      <c r="H249" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I249" s="2" t="n">
-        <v>18</v>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J249" s="2" t="inlineStr"/>
       <c r="K249" s="2" t="inlineStr"/>
@@ -14772,16 +14796,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B250" s="2" t="n">
-        <v>268</v>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
           <t>Jef Cabeça</t>
         </is>
       </c>
-      <c r="D250" s="2" t="n">
-        <v>85</v>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
@@ -14798,11 +14826,15 @@
           <t>F45|F92|Freljord|Mount Targon|Piltover &amp; Zaun|Shadow Isles</t>
         </is>
       </c>
-      <c r="H250" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I250" s="2" t="n">
-        <v>22</v>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="J250" s="2" t="inlineStr"/>
       <c r="K250" s="2" t="inlineStr"/>
@@ -14814,6 +14846,392 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>hobbbess</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>_gEo4Op585KVM_Sfc-uKfbfgCusB2Acr6bA86TPIUE9i7O8nFBz-H2qFjrM7bkJacTF59uUt3DdREw</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCAQCAUAQEAYJAEBQEBICAEBSULQCAYBAGCQCAYBQ2IIDAEBAQDZOAIAQOAYOAEEQEOYA</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Noxus</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr">
+        <is>
+          <t>midrange</t>
+        </is>
+      </c>
+      <c r="N251" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02IO005","n":3},{"c":"02NX009","n":3},{"c":"03IO005","n":3},{"c":"01NX042","n":3},{"c":"01NX046","n":3},{"c":"06IO003","n":3},{"c":"06IO010","n":3},{"c":"06NX013","n":3},{"c":"06NX033","n":3},{"c":"01IO008","n":3},{"c":"01IO015","n":3},{"c":"01IO046","n":3},{"c":"07NX014","n":2},{"c":"09IO059","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Dewei</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>ewsK3n40ORg5WAKrtoqRjPpiEXK0qPlxI4lyQLsBDd3PSawGLkYfMkn_bUyf0KTc_TfLyKMr35NgCg</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAYFBYAQIAQOAECQEGQBBECQ2AQGAUIBYBABAIDBCGZZAUAQCBJRAEBQEFABAYBCEAIGAUHQCCACC4AA</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr"/>
+      <c r="M252" s="2" t="inlineStr"/>
+      <c r="N252" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03SI014","n":3},{"c":"04IO014","n":3},{"c":"05IO026","n":3},{"c":"09SI013","n":3},{"c":"06SI016","n":3},{"c":"06SI028","n":3},{"c":"01IO006","n":3},{"c":"01IO017","n":3},{"c":"01IO027","n":3},{"c":"01IO057","n":3},{"c":"01SI049","n":2},{"c":"03IO020","n":2},{"c":"06IO034","n":2},{"c":"06SI015","n":2},{"c":"08IO023","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>DrChekhov42</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>1c4nwBwSyv5F1x83lL5dfhKFmmilYJSGA5t0If7XkaoDeMUcqouHaokbFO8-2k5ClT0A1DDCqeWjkw</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>CIEACAIDCQAQCBBUAEBQIBIBAYDB2AIHAMHACBYEBEAQQAYMAMBAGAIHBEBACAYEBMBAKBAYDEBQCAIDFMAQKBBGAIBAGAYI</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F38|Freljord|Noxus|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr"/>
+      <c r="M253" s="2" t="inlineStr"/>
+      <c r="N253" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX020","n":3},{"c":"01PZ052","n":3},{"c":"03PZ005","n":3},{"c":"06BW029","n":3},{"c":"07NX014","n":3},{"c":"07PZ009","n":3},{"c":"08NX012","n":3},{"c":"02NX001","n":3},{"c":"02NX007","n":3},{"c":"02NX009","n":3},{"c":"03PZ011","n":2},{"c":"05PZ024","n":2},{"c":"05PZ025","n":2},{"c":"01FR003","n":1},{"c":"43FR005","n":1},{"c":"04F38002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Level 5 Vegan</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>gGhQinkdAxnN2dov4wW-SyA-bFirpyYlLtwCg8mYeuB5DswHB7pTdlPql-jxmv554GKZF4qKYpYKiQ</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>CMCQCCIHBEBAOBYJE4BQIBYDEZWQGBIHA4FQ4BAGA4CSIMBTAAAQCBAHHY</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I254" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="inlineStr"/>
+      <c r="M254" s="2" t="inlineStr"/>
+      <c r="N254" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"09SH009","n":3},{"c":"07SH009","n":3},{"c":"07SH039","n":3},{"c":"04SH003","n":3},{"c":"04SH038","n":3},{"c":"04SH109","n":3},{"c":"05SH007","n":3},{"c":"05SH011","n":3},{"c":"05SH014","n":3},{"c":"06SH005","n":3},{"c":"06SH036","n":3},{"c":"06SH048","n":3},{"c":"06SH051","n":3},{"c":"01PZ007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Quanco of Fate</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>5FezBzVTTfc8nOd123FpKdH6kGu3avX9z-M5hGJmVGlR8oqDDpcxzP72VIqK-NyEBAxW3DOxfQV5aQ</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>CMCQCBIGAEAQMBQJAEEQOCIEAIDACCJNHYCQIBYDDITDG4QBAEEAMCACAEBAMFQBAQDQK</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Ionia|Shurima</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I255" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="inlineStr"/>
+      <c r="M255" s="2" t="inlineStr"/>
+      <c r="N255" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BW001","n":3},{"c":"06BW009","n":3},{"c":"09SH009","n":3},{"c":"02BW001","n":3},{"c":"02BW009","n":3},{"c":"02BW045","n":3},{"c":"02BW062","n":3},{"c":"04SH003","n":3},{"c":"04SH026","n":3},{"c":"04SH038","n":3},{"c":"04SH051","n":3},{"c":"04SH114","n":3},{"c":"08BW008","n":2},{"c":"01IO006","n":1},{"c":"22FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>SheIsMad</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>NVGTWcWoUZrD62EzcqD1V22S8pfNh_UkFMV2iGllGTXHoBICJCuu3sU7nY2PkweidD7Jsw8UnHZ9Ww</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>CQDACAQEBIAQMCQ2AEEAUBICA4FASFADAECAQGJUAMCQIAQGBYBQCAIEGUAQKCSGAEEAIGABAEDAIKY</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Piltover &amp; Zaun</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I256" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="inlineStr"/>
+      <c r="L256" s="2" t="inlineStr"/>
+      <c r="M256" s="2" t="inlineStr"/>
+      <c r="N256" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02PZ010","n":3},{"c":"06BC026","n":3},{"c":"08BC005","n":3},{"c":"07BC009","n":3},{"c":"07BC020","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"01PZ052","n":3},{"c":"05PZ002","n":3},{"c":"05PZ006","n":3},{"c":"05PZ014","n":3},{"c":"01PZ053","n":2},{"c":"05BC070","n":2},{"c":"08PZ024","n":2},{"c":"01BW004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>RunTheNets</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>Xl7GjY9cJtPZYQXoOlBrT09ubpsjbRH-flmtUGO67un6CYOPZALBjukopexS3Dx2je2OOCT0c2v28Q</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>CQDACBICDIAQMAQKAEDQEFABBEFAWAQBAIEA6AQFBI5NKAIGAEBAEBIBAMBBIAIFBIAQCBQKFQAQSAR3AMAQELRRHAAA</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Ionia</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I257" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J257" s="2" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="K257" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L257" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M257" s="2" t="inlineStr">
+        <is>
+          <t>midrange</t>
+        </is>
+      </c>
+      <c r="N257" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05IO026","n":3},{"c":"06IO010","n":3},{"c":"07IO020","n":3},{"c":"09BC011","n":3},{"c":"01IO008","n":3},{"c":"01IO015","n":3},{"c":"05BC058","n":3},{"c":"05BC213","n":3},{"c":"02IO005","n":2},{"c":"03IO020","n":2},{"c":"05BC001","n":2},{"c":"06BC044","n":2},{"c":"09IO059","n":2},{"c":"01IO046","n":2},{"c":"01IO049","n":2},{"c":"01IO056","n":2}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N257"/>
+  <dimension ref="A1:N267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -15036,16 +15036,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B254" s="2" t="n">
-        <v>286</v>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
           <t>Level 5 Vegan</t>
         </is>
       </c>
-      <c r="D254" s="2" t="n">
-        <v>76</v>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
@@ -15062,11 +15066,15 @@
           <t>Piltover &amp; Zaun|Shurima</t>
         </is>
       </c>
-      <c r="H254" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I254" s="2" t="n">
-        <v>14</v>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J254" s="2" t="inlineStr"/>
       <c r="K254" s="2" t="inlineStr"/>
@@ -15084,16 +15092,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B255" s="2" t="n">
-        <v>288</v>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
           <t>Quanco of Fate</t>
         </is>
       </c>
-      <c r="D255" s="2" t="n">
-        <v>76</v>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
@@ -15110,11 +15122,15 @@
           <t>Bilgewater|Freljord|Ionia|Shurima</t>
         </is>
       </c>
-      <c r="H255" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I255" s="2" t="n">
-        <v>15</v>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J255" s="2" t="inlineStr"/>
       <c r="K255" s="2" t="inlineStr"/>
@@ -15132,16 +15148,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B256" s="2" t="n">
-        <v>302</v>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
           <t>SheIsMad</t>
         </is>
       </c>
-      <c r="D256" s="2" t="n">
-        <v>56</v>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
@@ -15158,11 +15178,15 @@
           <t>Bandle City|Bilgewater|Piltover &amp; Zaun</t>
         </is>
       </c>
-      <c r="H256" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I256" s="2" t="n">
-        <v>15</v>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J256" s="2" t="inlineStr"/>
       <c r="K256" s="2" t="inlineStr"/>
@@ -15180,16 +15204,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B257" s="2" t="n">
-        <v>304</v>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
           <t>RunTheNets</t>
         </is>
       </c>
-      <c r="D257" s="2" t="n">
-        <v>55</v>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
@@ -15206,29 +15234,569 @@
           <t>Bandle City|Ionia</t>
         </is>
       </c>
-      <c r="H257" s="2" t="n">
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="K257" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="inlineStr">
+        <is>
+          <t>midrange</t>
+        </is>
+      </c>
+      <c r="N257" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05IO026","n":3},{"c":"06IO010","n":3},{"c":"07IO020","n":3},{"c":"09BC011","n":3},{"c":"01IO008","n":3},{"c":"01IO015","n":3},{"c":"05BC058","n":3},{"c":"05BC213","n":3},{"c":"02IO005","n":2},{"c":"03IO020","n":2},{"c":"05BC001","n":2},{"c":"06BC044","n":2},{"c":"09IO059","n":2},{"c":"01IO046","n":2},{"c":"01IO049","n":2},{"c":"01IO056","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Sly Red Fox</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>qNGovuOe08n5NBGIEcT_dIfURM1u8IzaHv10QLvx21USMMmEfqS3Pf7tdM7_gh9Hxo-sVjCBaXMUCQ</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>CEBQCAIDCMAQIAYEAQDAKDAQDQTAQAIDAMBQCBADCYAQMBINAEDQKAQBBABRGAIJAUGQEAIDBUPQEAQDAMEQCAQBAUAQG</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="inlineStr"/>
+      <c r="M258" s="2" t="inlineStr"/>
+      <c r="N258" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX019","n":3},{"c":"04NX004","n":3},{"c":"06SI012","n":3},{"c":"06SI016","n":3},{"c":"06SI028","n":3},{"c":"06SI038","n":3},{"c":"03NX003","n":2},{"c":"04NX022","n":2},{"c":"06SI013","n":2},{"c":"07SI002","n":2},{"c":"08NX019","n":2},{"c":"09SI013","n":2},{"c":"01NX013","n":2},{"c":"01NX031","n":2},{"c":"02NX003","n":2},{"c":"02NX009","n":2},{"c":"02FR005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>MonetaryUnit</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>DBjybqm2VOhhlFSxje1m5AfAemgS_Jj8m1MEaeVj8p8uLbDNstu7WtSPuDSZgLDX07Qk1XyD1JzHBw</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>CUCACAYJC4AQMCRLAEDQYDYDAEAQQEAZAYAQCBAUAEBACAYBAQAQ6AIGAEKQEBQJEIVQEBYJAEBQMAIBAMRACAYECMAQQCIYAEEAIGIBBACREAIJAEFA</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|F08|F19|Freljord|Mount Targon|Piltover &amp; Zaun|Runeterra</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr"/>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="inlineStr"/>
+      <c r="M259" s="2" t="inlineStr"/>
+      <c r="N259" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03MT023","n":3},{"c":"06BC043","n":3},{"c":"07RU015","n":3},{"c":"01FR008","n":3},{"c":"01FR016","n":3},{"c":"01FR025","n":3},{"c":"01PZ020","n":2},{"c":"02FR003","n":2},{"c":"04FR015","n":2},{"c":"06FR021","n":2},{"c":"06MT034","n":2},{"c":"06MT043","n":2},{"c":"07MT001","n":2},{"c":"07MT003","n":2},{"c":"01FR003","n":1},{"c":"34FR003","n":1},{"c":"04F19001","n":1},{"c":"08MT024","n":1},{"c":"01F08004","n":1},{"c":"25FR008","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>VentoBravo PQD</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>FnX0tnqKEgMTrOM2Udhn4qtVd-NMADklHVu7Wq6FdhTa6ZroG_Y2Mzr-ny3_0Isb_9OOnv59Ym51zA</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCBQHAUAQOBZOAEEAUBICAUFLYAOGAEDQIBYBBUOE6U25MQBACBQHGAAQOCQPAA</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Shurima</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="inlineStr"/>
+      <c r="M260" s="2" t="inlineStr"/>
+      <c r="N260" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06SH005","n":3},{"c":"07SH046","n":3},{"c":"08BC005","n":3},{"c":"05BC188","n":3},{"c":"05BC198","n":3},{"c":"04SH001","n":3},{"c":"04SH013","n":3},{"c":"04SH028","n":3},{"c":"04SH079","n":3},{"c":"04SH083","n":3},{"c":"04SH093","n":3},{"c":"04SH100","n":3},{"c":"06SH048","n":2},{"c":"07BC015","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>VHL Ngrett</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>EPXRToDP4JIdIIk9PjHHUXM3AAGQym3KUCaOaa2G7Cc5Q8Om54xM-sFc7uFQO3F51s6p0mxbWC5UkA</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAIDEEAQQAIYAICAGBAPAIDACEQ4AQAQCAISDYTAGAIEAMEACCABCMBACAIWFEAQEAIBAQVA</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr"/>
+      <c r="K261" s="2" t="inlineStr"/>
+      <c r="L261" s="2" t="inlineStr"/>
+      <c r="M261" s="2" t="inlineStr"/>
+      <c r="N261" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX033","n":3},{"c":"08FR024","n":3},{"c":"04NX004","n":3},{"c":"04NX015","n":3},{"c":"06FR018","n":3},{"c":"06FR028","n":3},{"c":"01FR001","n":3},{"c":"01FR018","n":3},{"c":"01FR030","n":3},{"c":"01FR038","n":3},{"c":"04NX008","n":2},{"c":"08FR019","n":2},{"c":"01FR022","n":2},{"c":"01FR041","n":2},{"c":"02FR001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Bluxplayer</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>MuF8i7nQoRAvEOCfDn4dKxSuxhpWg5p5Vse7JXuT9fSxaOhUXvMjhXfJQVRVhtqOrxMcRbvmlkSCkA</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>CMCACCIHBEBACAQGFICQIAQEAUEASDQFAQDQGGRTLVZAAAIBAYDQK</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Ionia|Shurima</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="inlineStr"/>
+      <c r="L262" s="2" t="inlineStr"/>
+      <c r="M262" s="2" t="inlineStr"/>
+      <c r="N262" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"09SH009","n":3},{"c":"01IO006","n":3},{"c":"01IO042","n":3},{"c":"04IO004","n":3},{"c":"04IO005","n":3},{"c":"04IO008","n":3},{"c":"04IO009","n":3},{"c":"04IO014","n":3},{"c":"04SH003","n":3},{"c":"04SH026","n":3},{"c":"04SH051","n":3},{"c":"04SH093","n":3},{"c":"04SH114","n":3},{"c":"01BW007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>JSPope</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>UaG34YMRDb-W7-iBZbPRCrwyVu3E9LrTueArfv1GB6KVgRTOmp24luuTNakw6mUn_Qpqq9NxwFIcKg</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCBIKP4AQOCQJAEEAABQBBAEQGBQJBIAQGBAMBUKAKAIBAANACAQAAEAQGAAOAEDAABQBBAAAUAA</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Mount Targon</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="I257" s="2" t="n">
+      <c r="I263" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J263" s="2" t="inlineStr"/>
+      <c r="K263" s="2" t="inlineStr"/>
+      <c r="L263" s="2" t="inlineStr"/>
+      <c r="M263" s="2" t="inlineStr"/>
+      <c r="N263" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC127","n":3},{"c":"07BC009","n":3},{"c":"08DE006","n":3},{"c":"08MT003","n":3},{"c":"09BC001","n":3},{"c":"09BC003","n":3},{"c":"09BC004","n":3},{"c":"09BC012","n":3},{"c":"09BC013","n":3},{"c":"09BC020","n":3},{"c":"01DE026","n":2},{"c":"02DE001","n":2},{"c":"03DE014","n":2},{"c":"06DE006","n":2},{"c":"08DE010","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>felotop</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>clwRkJSUP-oBTqlnZYb47ieKjXSS7DSXb0-ncfqorIZ6xaGymjYbAxps3h8_C8IJQfXAU228klFpww</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>CECQCBACBYAQMAQJAIAQECI3AIDAKJRNAQAQKCQVC4VAIAIBAIBQCAIFAQAQMAQXAIDAKAYPAA</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>Ionia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I264" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="inlineStr"/>
+      <c r="L264" s="2" t="inlineStr"/>
+      <c r="M264" s="2" t="inlineStr"/>
+      <c r="N264" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04IO014","n":3},{"c":"06IO009","n":3},{"c":"01IO009","n":3},{"c":"01IO027","n":3},{"c":"06SI038","n":3},{"c":"06SI045","n":3},{"c":"01SI010","n":3},{"c":"01SI021","n":3},{"c":"01SI023","n":3},{"c":"01SI042","n":3},{"c":"01IO003","n":2},{"c":"01SI004","n":2},{"c":"06IO023","n":2},{"c":"06SI003","n":2},{"c":"06SI015","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>O ViiLão</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>DXYPj2zbMB7NxuSLESG0SJsgelVNXkRHdZuTgBx2wSEneCIBAZMyyMZaMbAeDDsIQHPIQp7uho9Nrw</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>CECACBABCMAQIBIFAEDAKLQEAEAQCCYSEYDQCAIFGEAQGAIWAEDACEQBA4CQEAIIAEJQCCAFA4BQCAI6FAVACAIBAUAQ</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I265" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J265" s="2" t="inlineStr"/>
+      <c r="K265" s="2" t="inlineStr"/>
+      <c r="L265" s="2" t="inlineStr"/>
+      <c r="M265" s="2" t="inlineStr"/>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04FR019","n":3},{"c":"04SI005","n":3},{"c":"06SI046","n":3},{"c":"01FR001","n":3},{"c":"01FR011","n":3},{"c":"01FR018","n":3},{"c":"01FR038","n":3},{"c":"01SI049","n":2},{"c":"03FR022","n":2},{"c":"06FR018","n":2},{"c":"07SI002","n":2},{"c":"08FR019","n":2},{"c":"08SI007","n":2},{"c":"01FR030","n":2},{"c":"01FR040","n":2},{"c":"01FR042","n":2},{"c":"01FR005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>AltarOfHate</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>YYvkA9rV2i6QVyaYcMnMCPCwJoZskaQBUra6d5hV39qPLX2e5pJLDHcBJG3_eQduTBWJ__Aozhl-iw</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>CMBQCBQFEYBAIBYDDIBQCBIECUVAKAIHAUBACCIHBEBAMBIPEABQCBIBBILQGBAHGM5HEAQBAQDTWAIHA4LQ</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Piltover &amp; Zaun|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I266" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J266" s="2" t="inlineStr"/>
+      <c r="K266" s="2" t="inlineStr"/>
+      <c r="L266" s="2" t="inlineStr"/>
+      <c r="M266" s="2" t="inlineStr"/>
+      <c r="N266" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06SI038","n":3},{"c":"04SH003","n":3},{"c":"04SH026","n":3},{"c":"01SI004","n":3},{"c":"01SI021","n":3},{"c":"01SI042","n":3},{"c":"07SI002","n":2},{"c":"09SH009","n":2},{"c":"06SI015","n":2},{"c":"06SI032","n":2},{"c":"01SI001","n":2},{"c":"01SI010","n":2},{"c":"01SI023","n":2},{"c":"04SH051","n":2},{"c":"04SH058","n":2},{"c":"04SH114","n":2},{"c":"01PZ007","n":1},{"c":"59FR007","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>themeatlo4f</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>vfai8B0y0F_I-kqRK5K_OP4MOfMROeyjVsdFwMjqLHNUbJ5KEb8FLEepnELsSEY0AbLVmQ5Ummp02A</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>CMBAIBAGAEBQKDYEAQDRGRCKKABQCBQGFUBQIBQCAQDQIBAHCY5UCUYA</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Shurima</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I267" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J257" s="2" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="K257" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L257" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="M257" s="2" t="inlineStr">
-        <is>
-          <t>midrange</t>
-        </is>
-      </c>
-      <c r="N257" s="2" t="inlineStr">
-        <is>
-          <t>[{"c":"05IO026","n":3},{"c":"06IO010","n":3},{"c":"07IO020","n":3},{"c":"09BC011","n":3},{"c":"01IO008","n":3},{"c":"01IO015","n":3},{"c":"05BC058","n":3},{"c":"05BC213","n":3},{"c":"02IO005","n":2},{"c":"03IO020","n":2},{"c":"05BC001","n":2},{"c":"06BC044","n":2},{"c":"09IO059","n":2},{"c":"01IO046","n":2},{"c":"01IO049","n":2},{"c":"01IO056","n":2}]</t>
+      <c r="J267" s="2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="K267" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L267" s="2" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04BW001","n":3},{"c":"04BW003","n":3},{"c":"04BW005","n":3},{"c":"04BW015","n":3},{"c":"04SH019","n":3},{"c":"04SH068","n":3},{"c":"04SH074","n":3},{"c":"04SH080","n":3},{"c":"06BW045","n":2},{"c":"04BW002","n":2},{"c":"04BW004","n":2},{"c":"04BW007","n":2},{"c":"04SH022","n":2},{"c":"04SH059","n":2},{"c":"04SH065","n":2},{"c":"04SH083","n":2}]</t>
         </is>
       </c>
     </row>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N267"/>
+  <dimension ref="A1:N271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -15556,16 +15556,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B263" s="2" t="n">
-        <v>314</v>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
           <t>JSPope</t>
         </is>
       </c>
-      <c r="D263" s="2" t="n">
-        <v>51</v>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
@@ -15582,11 +15586,15 @@
           <t>Bandle City|Demacia|Mount Targon</t>
         </is>
       </c>
-      <c r="H263" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I263" s="2" t="n">
-        <v>15</v>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J263" s="2" t="inlineStr"/>
       <c r="K263" s="2" t="inlineStr"/>
@@ -15604,16 +15612,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B264" s="2" t="n">
-        <v>320</v>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
           <t>felotop</t>
         </is>
       </c>
-      <c r="D264" s="2" t="n">
-        <v>48</v>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
@@ -15630,11 +15642,15 @@
           <t>Ionia|Shadow Isles</t>
         </is>
       </c>
-      <c r="H264" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I264" s="2" t="n">
-        <v>15</v>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J264" s="2" t="inlineStr"/>
       <c r="K264" s="2" t="inlineStr"/>
@@ -15652,16 +15668,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B265" s="2" t="n">
-        <v>321</v>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
           <t>O ViiLão</t>
         </is>
       </c>
-      <c r="D265" s="2" t="n">
-        <v>48</v>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
@@ -15678,11 +15698,15 @@
           <t>Freljord|Shadow Isles</t>
         </is>
       </c>
-      <c r="H265" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I265" s="2" t="n">
-        <v>17</v>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="J265" s="2" t="inlineStr"/>
       <c r="K265" s="2" t="inlineStr"/>
@@ -15700,16 +15724,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B266" s="2" t="n">
-        <v>322</v>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
           <t>AltarOfHate</t>
         </is>
       </c>
-      <c r="D266" s="2" t="n">
-        <v>47</v>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -15726,11 +15754,15 @@
           <t>Freljord|Piltover &amp; Zaun|Shadow Isles|Shurima</t>
         </is>
       </c>
-      <c r="H266" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I266" s="2" t="n">
-        <v>18</v>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J266" s="2" t="inlineStr"/>
       <c r="K266" s="2" t="inlineStr"/>
@@ -15748,16 +15780,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B267" s="2" t="n">
-        <v>323</v>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
           <t>themeatlo4f</t>
         </is>
       </c>
-      <c r="D267" s="2" t="n">
-        <v>46</v>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -15774,29 +15810,231 @@
           <t>Bilgewater|Shurima</t>
         </is>
       </c>
-      <c r="H267" s="2" t="n">
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>aggro</t>
+        </is>
+      </c>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"04BW001","n":3},{"c":"04BW003","n":3},{"c":"04BW005","n":3},{"c":"04BW015","n":3},{"c":"04SH019","n":3},{"c":"04SH068","n":3},{"c":"04SH074","n":3},{"c":"04SH080","n":3},{"c":"06BW045","n":2},{"c":"04BW002","n":2},{"c":"04BW004","n":2},{"c":"04BW007","n":2},{"c":"04SH022","n":2},{"c":"04SH059","n":2},{"c":"04SH065","n":2},{"c":"04SH083","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>CaptainAmericano</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>9AIzKgYjU_clQy6IBUjdxSiosCqltUdHYmWJ46Ok9segKFx9wPVlmq3cgzE6z5caZVKPyP5_Csc0xA</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAIEGQAQGAQUAEBQICYBBACASAIJAI5AEBYCBMKAGAIBAIUQEBIEDETAEBYCCEJQOAICAICQCBICAYAQMARAAEDQEBYBBABAUAQBAISTCAQGAQJBK</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Ionia|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="I268" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="inlineStr"/>
+      <c r="M268" s="2" t="inlineStr"/>
+      <c r="N268" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01PZ052","n":3},{"c":"03IO020","n":3},{"c":"03PZ011","n":3},{"c":"08PZ009","n":3},{"c":"09IO058","n":3},{"c":"07IO011","n":3},{"c":"07IO020","n":3},{"c":"01IO041","n":2},{"c":"05PZ025","n":2},{"c":"05PZ038","n":2},{"c":"07IO017","n":2},{"c":"07IO019","n":2},{"c":"01IO002","n":1},{"c":"05FR005","n":1},{"c":"02BW001","n":1},{"c":"06IO032","n":1},{"c":"01SH002","n":1},{"c":"07FR008","n":1},{"c":"02BC002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>cloite</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>S5FeQ_9nYTSQwyzmssTeHjZtfnkDOY3-IkDlNjCoY-lrZ1-TX6gxgYaqnpjF5OIyCnEyB_-uuFMDVg</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>CMBQEAICAYVAKBACAQCQQCIOAUCAOAY2GNOXEAIBBEDQSAQBAEBAWAIGAIBQ</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia|Shurima</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="I267" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J267" s="2" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="K267" s="2" t="n">
+      <c r="I269" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J269" s="2" t="inlineStr"/>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr"/>
+      <c r="M269" s="2" t="inlineStr"/>
+      <c r="N269" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO006","n":3},{"c":"01IO042","n":3},{"c":"04IO004","n":3},{"c":"04IO005","n":3},{"c":"04IO008","n":3},{"c":"04IO009","n":3},{"c":"04IO014","n":3},{"c":"04SH003","n":3},{"c":"04SH026","n":3},{"c":"04SH051","n":3},{"c":"04SH093","n":3},{"c":"04SH114","n":3},{"c":"09SH009","n":2},{"c":"01FR002","n":1},{"c":"11FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>yummyfridchicken</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>PUsNURJe2VxdHbUpClnEirFULa8D5oRJ0Lw4JUkQuci-AAcn6c5q-1_0rUDp_9C-DrY2dLf3FYamGQ</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>CQAQCCAEBEBQCAICFEBAMBASCUBAOAQLCQHACAICGEAQEAQFAEBAIBQBAMBBIAIDAQFQCBICAYAQOBAJAEEAUBQBBACBUAQGAIQCIAQHAIIRGAYBAQASCNAFAYCASIBIFMXAMBIEBIIRQGI3EY</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|F11|F36|Freljord|Ionia|Noxus|Piltover &amp; Zaun|Shadow Isles|Shurima</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="I270" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="L267" s="2" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="M267" s="2" t="inlineStr">
-        <is>
-          <t>aggro</t>
-        </is>
-      </c>
-      <c r="N267" s="2" t="inlineStr">
-        <is>
-          <t>[{"c":"04BW001","n":3},{"c":"04BW003","n":3},{"c":"04BW005","n":3},{"c":"04BW015","n":3},{"c":"04SH019","n":3},{"c":"04SH068","n":3},{"c":"04SH074","n":3},{"c":"04SH080","n":3},{"c":"06BW045","n":2},{"c":"04BW002","n":2},{"c":"04BW004","n":2},{"c":"04BW007","n":2},{"c":"04SH022","n":2},{"c":"04SH059","n":2},{"c":"04SH065","n":2},{"c":"04SH083","n":2}]</t>
+      <c r="J270" s="2" t="inlineStr"/>
+      <c r="K270" s="2" t="inlineStr"/>
+      <c r="L270" s="2" t="inlineStr"/>
+      <c r="M270" s="2" t="inlineStr"/>
+      <c r="N270" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"08PZ009","n":3},{"c":"01IO041","n":2},{"c":"06PZ018","n":2},{"c":"06PZ021","n":2},{"c":"07IO011","n":2},{"c":"07IO020","n":2},{"c":"01FR002","n":1},{"c":"49FR002","n":1},{"c":"02SI001","n":1},{"c":"02PZ006","n":1},{"c":"01NX002","n":1},{"c":"20FR003","n":1},{"c":"04F11001","n":1},{"c":"05IO006","n":1},{"c":"01SH004","n":1},{"c":"09FR008","n":1},{"c":"10BW001","n":1},{"c":"08PZ026","n":1},{"c":"02BW002","n":1},{"c":"32F36002","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>n1cOw1</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>gWLGE1M0AyBdaHFejf6iBykXCU7SQgHtfGRuQcL5YJIjvxZWrh9j4s1r3aauIrDFBf3dDSfh-91png</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAICFEAQKAQGAEEAEDQCAEAROKQCAYASIKIDA4BAWEIUAQAQCAIUAEAQEMIBAYASMAQGAISCYAA</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I271" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr"/>
+      <c r="M271" s="2" t="inlineStr"/>
+      <c r="N271" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO041","n":3},{"c":"05IO006","n":3},{"c":"08IO014","n":3},{"c":"01FR023","n":3},{"c":"01FR042","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"07IO011","n":3},{"c":"07IO017","n":3},{"c":"07IO020","n":3},{"c":"01FR020","n":2},{"c":"01IO049","n":2},{"c":"06FR038","n":2},{"c":"06IO036","n":2},{"c":"06IO044","n":2}]</t>
         </is>
       </c>
     </row>

--- a/lor_dataset.xlsx
+++ b/lor_dataset.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N271"/>
+  <dimension ref="A1:N289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -15852,16 +15852,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B268" s="2" t="n">
-        <v>326</v>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
           <t>CaptainAmericano</t>
         </is>
       </c>
-      <c r="D268" s="2" t="n">
-        <v>44</v>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15878,11 +15882,15 @@
           <t>Bandle City|Bilgewater|Freljord|Ionia|Piltover &amp; Zaun|Shurima</t>
         </is>
       </c>
-      <c r="H268" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="I268" s="2" t="n">
-        <v>19</v>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="J268" s="2" t="inlineStr"/>
       <c r="K268" s="2" t="inlineStr"/>
@@ -15900,16 +15908,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B269" s="2" t="n">
-        <v>330</v>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
           <t>cloite</t>
         </is>
       </c>
-      <c r="D269" s="2" t="n">
-        <v>41</v>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
@@ -15926,11 +15938,15 @@
           <t>Freljord|Ionia|Shurima</t>
         </is>
       </c>
-      <c r="H269" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I269" s="2" t="n">
-        <v>15</v>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J269" s="2" t="inlineStr"/>
       <c r="K269" s="2" t="inlineStr"/>
@@ -15948,16 +15964,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B270" s="2" t="n">
-        <v>332</v>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
           <t>yummyfridchicken</t>
         </is>
       </c>
-      <c r="D270" s="2" t="n">
-        <v>39</v>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
@@ -15974,11 +15994,15 @@
           <t>Bilgewater|F11|F36|Freljord|Ionia|Noxus|Piltover &amp; Zaun|Shadow Isles|Shurima</t>
         </is>
       </c>
-      <c r="H270" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="I270" s="2" t="n">
-        <v>20</v>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="J270" s="2" t="inlineStr"/>
       <c r="K270" s="2" t="inlineStr"/>
@@ -15996,16 +16020,20 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B271" s="2" t="n">
-        <v>337</v>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
           <t>n1cOw1</t>
         </is>
       </c>
-      <c r="D271" s="2" t="n">
-        <v>33</v>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -16022,11 +16050,15 @@
           <t>Freljord|Ionia</t>
         </is>
       </c>
-      <c r="H271" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I271" s="2" t="n">
-        <v>15</v>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="J271" s="2" t="inlineStr"/>
       <c r="K271" s="2" t="inlineStr"/>
@@ -16038,6 +16070,1002 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>zstacks</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>xCbtgFA1YJQrtWRSNqIBB_baxYXZ66BcsBQbAO7etA2BfFCZ987Qsw5255i7DZuwYWIoDYzag-wMPg</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>CEDQCAYBAIAQIAYEAEDAGGQBBABQSAQBAMNB6AQIAEJRQBABAECBMJRQAIAQCAZBAECAGCAA</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="inlineStr"/>
+      <c r="M272" s="2" t="inlineStr"/>
+      <c r="N272" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"03FR002","n":3},{"c":"04NX004","n":3},{"c":"06NX026","n":3},{"c":"08NX009","n":3},{"c":"01NX026","n":3},{"c":"01NX031","n":3},{"c":"08FR019","n":3},{"c":"08FR024","n":3},{"c":"01FR004","n":3},{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01FR048","n":3},{"c":"01NX033","n":2},{"c":"04NX008","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>Wolfstocs</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>-M26hvluB9ZYDHpEv8BjleefydV21zzm2QSdI0mNwXnlvMyFNXLt07NFAgW2BGCGksvQ0-vqMu_Fyw</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>CECACAIBAEAQKBACAEEAIGACAECAQGIGAEBACAQBAICAUAIDAQCQCCABCMBACBBUHICACAIEBMPCUAYBAUCA4AIGAQVQGAIBA4KCM</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>F43|Freljord|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr"/>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr"/>
+      <c r="M273" s="2" t="inlineStr"/>
+      <c r="N273" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR001","n":3},{"c":"05PZ002","n":3},{"c":"08PZ024","n":3},{"c":"01PZ008","n":3},{"c":"01PZ025","n":3},{"c":"02FR002","n":2},{"c":"02PZ010","n":2},{"c":"03PZ005","n":2},{"c":"08FR019","n":2},{"c":"01PZ052","n":2},{"c":"01PZ058","n":2},{"c":"01FR004","n":2},{"c":"01FR011","n":2},{"c":"01FR030","n":2},{"c":"01FR042","n":2},{"c":"01SI004","n":1},{"c":"14FR006","n":1},{"c":"04F43003","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>TN Chema</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>QvhkiAwTVxA02NsMxspvn1dY47fm0KrT49HdQecvwZLBtx8mJpph-_vmVSbICA-ExG1JclQzoPYiOA</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>CEBQCAIDEEAQIAYEAUAQCCYWEYUTABIBAEBR6AIGAEJACBQDDMAQOAIIAMAQCAI6FICACAIBAQAQIAIKAEDAABQCAQBQQDY</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Noxus</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="inlineStr"/>
+      <c r="M274" s="2" t="inlineStr"/>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01NX033","n":3},{"c":"04NX004","n":3},{"c":"01FR011","n":3},{"c":"01FR022","n":3},{"c":"01FR038","n":3},{"c":"01FR041","n":3},{"c":"01FR048","n":3},{"c":"01NX031","n":2},{"c":"06FR018","n":2},{"c":"06NX027","n":2},{"c":"07FR008","n":2},{"c":"01FR001","n":2},{"c":"01FR030","n":2},{"c":"01FR042","n":2},{"c":"01FR001","n":1},{"c":"04FR004","n":1},{"c":"01BC001","n":1},{"c":"06DE006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>DOUBLE A BATTERY</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Zi0ooeaPDWtw0B9w-RjKJY0dQYd5HBm2tsJ7A8KZ8jzmtH8-2iKuFqgrLFsAhewrnQoFgRutqAx-zA</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>CUDQCAIBCYAQMCQ2AEDASHIBAYGACAIIAADACCABCMBAMAIVDQDACAIBFEAQEAICAEDAULABAYES6AIIAEMAEBQBDAQAEAICAEDQCBABBI</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord|Ionia|Mount Targon|Runeterra</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr"/>
+      <c r="K275" s="2" t="inlineStr"/>
+      <c r="L275" s="2" t="inlineStr"/>
+      <c r="M275" s="2" t="inlineStr"/>
+      <c r="N275" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR022","n":3},{"c":"06BC026","n":3},{"c":"06MT029","n":3},{"c":"06RU001","n":3},{"c":"08DE006","n":3},{"c":"08FR019","n":3},{"c":"06FR021","n":3},{"c":"06FR028","n":3},{"c":"01FR041","n":2},{"c":"02FR002","n":2},{"c":"06BC044","n":2},{"c":"06MT047","n":2},{"c":"08FR024","n":2},{"c":"06FR024","n":2},{"c":"06FR032","n":2},{"c":"01IO001","n":1},{"c":"07FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Keldog</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>1CKHt5W262OqVUahdjh11tOI_iLOClJy8SS9v3HT9RIEWsSJ40CQAUPI_xtuajXdOFC7cdvA3xsd3A</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>CUDQCBIKDUAQMCJPAEDAYAIBA4FBIAIIAUKQCCIKCQBAMCQLCUCACBIKAEAQMCI5AIDAUHZPAIEAUAQGAIAQMCRLAMCQUEYUWEAQ</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Mount Targon|Noxus|Runeterra|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr"/>
+      <c r="K276" s="2" t="inlineStr"/>
+      <c r="L276" s="2" t="inlineStr"/>
+      <c r="M276" s="2" t="inlineStr"/>
+      <c r="N276" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC029","n":3},{"c":"06MT047","n":3},{"c":"06RU001","n":3},{"c":"07BC020","n":3},{"c":"08SI021","n":3},{"c":"09BC020","n":3},{"c":"06BC011","n":3},{"c":"06BC021","n":3},{"c":"05BC001","n":2},{"c":"06MT029","n":2},{"c":"06BC031","n":2},{"c":"06BC047","n":2},{"c":"08BC002","n":2},{"c":"08BC006","n":2},{"c":"01BW010","n":1},{"c":"43NX005","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>ChelseyBabyCake</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>HlUxWPl1cN_YiDzlRJy6Ky-5zy-4WFSXO2iVvx_b_LhmtbQY7xGra3gzPYnhOTqRX_l0c05RQ9HCaw</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>CQCACBQEFIAQQCQGAEEAECQBBACASBQBAIBAKAIDAIKAEAICFEYQEAYEAQFQEBIEDATAEBYCCQVQOAIBAQ4ACAYEAMAQMARAAEDAICIBA4BAOAIJAI5AEAICAISQ</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Ionia|Noxus|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr"/>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="inlineStr"/>
+      <c r="M277" s="2" t="inlineStr"/>
+      <c r="N277" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06PZ042","n":3},{"c":"08BC006","n":3},{"c":"08IO010","n":3},{"c":"08PZ009","n":3},{"c":"02IO005","n":2},{"c":"03IO020","n":2},{"c":"01IO041","n":2},{"c":"01IO049","n":2},{"c":"03PZ004","n":2},{"c":"03PZ011","n":2},{"c":"05PZ024","n":2},{"c":"05PZ038","n":2},{"c":"07IO020","n":2},{"c":"07IO043","n":2},{"c":"01FR004","n":1},{"c":"56FR003","n":1},{"c":"04NX001","n":1},{"c":"06IO032","n":1},{"c":"01BW004","n":1},{"c":"09FR007","n":1},{"c":"02SH001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>batmankv</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>U1AcADci3fc4Uk79Z4RBMnxKSSrOC4PTqUPUwRP-y95hzOWONA9Yujz3yQIK8iJqDS2vvguC-oes9w</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>CMCACBQGFUAQMBYFAQCAMAIDAUHQMBAHCMLECRCKKAAQCBAGAQBACBAGAIAQIBZ3</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr"/>
+      <c r="K278" s="2" t="inlineStr"/>
+      <c r="L278" s="2" t="inlineStr"/>
+      <c r="M278" s="2" t="inlineStr"/>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BW045","n":3},{"c":"06SH005","n":3},{"c":"04BW001","n":3},{"c":"04BW003","n":3},{"c":"04BW005","n":3},{"c":"04BW015","n":3},{"c":"04SH019","n":3},{"c":"04SH022","n":3},{"c":"04SH065","n":3},{"c":"04SH068","n":3},{"c":"04SH074","n":3},{"c":"04SH080","n":3},{"c":"04BW004","n":2},{"c":"01PZ006","n":1},{"c":"02FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>Edgy Dank Memer</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>F74AKcKMmPGOnYg66v1j86wCa8V6a1aGJrZDLcyWZ85FJLfiGjvMJR1wC_Nzsz-vWuaUikoWp-d0eg</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>CEDACAIFAEAQGAIWAEEACAICAYASIKIDAQCTKNZYAQAQCDAXFI2AEAIBAUOQCBYFAEAA</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr"/>
+      <c r="K279" s="2" t="inlineStr"/>
+      <c r="L279" s="2" t="inlineStr"/>
+      <c r="M279" s="2" t="inlineStr"/>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI001","n":3},{"c":"03FR022","n":3},{"c":"08FR001","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"04SI053","n":3},{"c":"04SI055","n":3},{"c":"04SI056","n":3},{"c":"01FR012","n":3},{"c":"01FR023","n":3},{"c":"01FR042","n":3},{"c":"01FR052","n":3},{"c":"01SI029","n":2},{"c":"07SI001","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>The Condor Hero</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>cLreYqCgVsM-tdtswOoteDVHRuhSGY5uRv2QIM9DRlHpzvUtaJKwhsuJYOSsJAXdB4wNeH9DRX0Jpw</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>CQCQCBIKP4AQMAAGAEDQUCIBBAEQGBIJBIAQGDANCQCACAIADIAQEAABAECQADABBEFAIBABAUFACAIHBIHQCCIAFUBASCQLCI</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|F15|Freljord|Mount Targon|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr"/>
+      <c r="K280" s="2" t="inlineStr"/>
+      <c r="L280" s="2" t="inlineStr"/>
+      <c r="M280" s="2" t="inlineStr"/>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC127","n":3},{"c":"06DE006","n":3},{"c":"07BC009","n":3},{"c":"08MT003","n":3},{"c":"09BC001","n":3},{"c":"09BC003","n":3},{"c":"09BC012","n":3},{"c":"09BC013","n":3},{"c":"09BC020","n":3},{"c":"01DE026","n":2},{"c":"02DE001","n":2},{"c":"05DE012","n":2},{"c":"09BC004","n":2},{"c":"01SI010","n":1},{"c":"01FR007","n":1},{"c":"10F15001","n":1},{"c":"09DE045","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>ANG3L</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>64T_QJuxrjgymcgVU_WRi83XMzxl5n3CFbhCLnEpra1r8axDA_rRCCP2Lvk2rIRx-TL7jn-FAfdNqQ</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>CIDACBYJBEAQQAI6AIDACJBJAIEASAY7AMAQCDBBFICAGCIOCVLWIAABAEBQCFQ</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Mount Targon|Noxus</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr"/>
+      <c r="K281" s="2" t="inlineStr"/>
+      <c r="L281" s="2" t="inlineStr"/>
+      <c r="M281" s="2" t="inlineStr"/>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"07MT009","n":3},{"c":"08FR030","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"08MT003","n":3},{"c":"08MT031","n":3},{"c":"01FR012","n":3},{"c":"01FR033","n":3},{"c":"01FR042","n":3},{"c":"03MT014","n":3},{"c":"03MT021","n":3},{"c":"03MT087","n":3},{"c":"03MT100","n":3},{"c":"01NX001","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Fathermitch</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>u9P21YdI4OIKc24Y0pF-80wnRRaEBUDTLOJ0i0GI8KLbG_AFSLJkG97OBNPX-I4XWtnnhjdRtGPZtg</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>CEAAAAICAAAAMJY</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>Demacia</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr"/>
+      <c r="K282" s="2" t="inlineStr"/>
+      <c r="L282" s="2" t="inlineStr"/>
+      <c r="M282" s="2" t="inlineStr"/>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02DE000","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>Street Saint</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>E7smQaEa-hHpUuWQqVn-mefaJrXHeFLEoMWV-L32PyWbHALmGjQ3ddKMC9eUIgCOIYgT5g7IyJBAwQ</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>CQDQCAIFBQAQMBJKAEEAMHABBACAQAIJBIAQCCIFBUBAQBI2FACACAIEGQBACBIWGEBAIBAHBMBAMBI3FABACAIFAEAQMBJN</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Bilgewater|Freljord|Piltover &amp; Zaun|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr"/>
+      <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr"/>
+      <c r="M283" s="2" t="inlineStr"/>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01SI012","n":3},{"c":"06SI042","n":3},{"c":"08BW028","n":3},{"c":"08PZ008","n":3},{"c":"09BC001","n":3},{"c":"09SI013","n":3},{"c":"08SI026","n":3},{"c":"08SI040","n":3},{"c":"01PZ052","n":2},{"c":"01SI022","n":2},{"c":"01SI049","n":2},{"c":"04PZ007","n":2},{"c":"04PZ011","n":2},{"c":"06SI027","n":2},{"c":"06SI040","n":2},{"c":"01FR005","n":1},{"c":"01FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Eksirf</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>suoMpWzGhtjvF_YYo5Yz40FMKQk5OdgLb3OF_JE5690sWdr1F5HzX1HoRMd2zOvlW2IdzkrNq7UuOw</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>CMCACBQGFUAQMBYFAQCAOE2EJJIAMBAGAEBAGBAFB4AQCBAHIEBACBAGA4AQIBYW</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Freljord|Piltover &amp; Zaun|Shurima</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr"/>
+      <c r="K284" s="2" t="inlineStr"/>
+      <c r="L284" s="2" t="inlineStr"/>
+      <c r="M284" s="2" t="inlineStr"/>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"06BW045","n":3},{"c":"06SH005","n":3},{"c":"04SH019","n":3},{"c":"04SH068","n":3},{"c":"04SH074","n":3},{"c":"04SH080","n":3},{"c":"04BW001","n":3},{"c":"04BW002","n":3},{"c":"04BW003","n":3},{"c":"04BW004","n":3},{"c":"04BW005","n":3},{"c":"04BW015","n":3},{"c":"04SH065","n":2},{"c":"01PZ006","n":1},{"c":"07FR004","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>MrPapichurris</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>k5Mo2wzvsv69wr-ICakBXkpwPqxDhYBp9bOHGBRzFkYUpEMe6ORsHPlEf_A5xI8kguB54rx9M-WHHQ</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>CEBQCAICFEAQGAIWAIDQECYUBEAQCARRAEBAEBIBAMBBGAIFAIDACBQCFQAQOAQRAEEACEYDAYASIJRJAQAQCDAUC4VAA</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr"/>
+      <c r="K285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr"/>
+      <c r="M285" s="2" t="inlineStr"/>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01IO041","n":3},{"c":"03FR022","n":3},{"c":"07IO011","n":3},{"c":"07IO020","n":3},{"c":"01IO049","n":2},{"c":"02IO005","n":2},{"c":"03IO019","n":2},{"c":"05IO006","n":2},{"c":"06IO044","n":2},{"c":"07IO017","n":2},{"c":"08FR019","n":2},{"c":"06FR036","n":2},{"c":"06FR038","n":2},{"c":"06FR041","n":2},{"c":"01FR012","n":2},{"c":"01FR020","n":2},{"c":"01FR023","n":2},{"c":"01FR042","n":2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Caramelo07</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>8q_A3W2j4zqkUseWjKlJEqlWYhy0I9CKKvlF6U-n6z1PItnbfN-8HLBEDKBcrABCgGRGf4Y59KLuRg</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>CQBAKCIADYPSEJBHAYEQUAIDAQDAWFADAEDAUKABBEFBAAIJAAVQCAIFBIFA</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I286" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J286" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="K286" s="2" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="L286" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M286" s="2" t="inlineStr">
+        <is>
+          <t>midrange</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"09DE030","n":3},{"c":"09DE031","n":3},{"c":"09DE034","n":3},{"c":"09DE036","n":3},{"c":"09DE039","n":3},{"c":"09BC001","n":3},{"c":"09BC003","n":3},{"c":"09BC004","n":3},{"c":"09BC006","n":3},{"c":"09BC011","n":3},{"c":"09BC020","n":3},{"c":"06BC040","n":2},{"c":"09BC016","n":2},{"c":"09DE043","n":2},{"c":"01SI010","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>VICEREME</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>0dOWqKCbYXD-5wmCrgaSwfICOpIbHqvGMZDNw-U50Xbf-OOjPJxG97aGKvpXz5701cWy3A_mK6PFxg</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>CQBQCBIK4AAQICIADYPSEJYHBEFACAQDAQFQYFABAEEQAJACAEAQAGQBBEFBE</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>Bandle City|Demacia|Freljord</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I287" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J287" s="2" t="inlineStr"/>
+      <c r="K287" s="2" t="inlineStr"/>
+      <c r="L287" s="2" t="inlineStr"/>
+      <c r="M287" s="2" t="inlineStr"/>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"05BC224","n":3},{"c":"09DE030","n":3},{"c":"09DE031","n":3},{"c":"09DE034","n":3},{"c":"09DE039","n":3},{"c":"09BC001","n":3},{"c":"09BC002","n":3},{"c":"09BC003","n":3},{"c":"09BC004","n":3},{"c":"09BC011","n":3},{"c":"09BC012","n":3},{"c":"09BC020","n":3},{"c":"09DE036","n":2},{"c":"01FR000","n":1},{"c":"26FR009","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>aminnoo</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>mSzd_6ozuhJSYsCq5H7lSpPcuo3wHccXTpeW9RfdDjqJbOUN7zc6IRJx4fwcnnAvswgBrMqec3NX7A</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>CECQCAIBBQAQGAIWAIAQEKJRAIDACJBJAIDQECYRAYAQCAJKAEBQEFABAUBAMAIGAETACBYCCQBAEAQFBEBACAICAEAQMARM</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>Freljord|Ionia</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I288" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J288" s="2" t="inlineStr"/>
+      <c r="K288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr"/>
+      <c r="M288" s="2" t="inlineStr"/>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"01FR012","n":3},{"c":"03FR022","n":3},{"c":"01IO041","n":3},{"c":"01IO049","n":3},{"c":"06FR036","n":3},{"c":"06FR041","n":3},{"c":"07IO011","n":3},{"c":"07IO017","n":3},{"c":"01FR042","n":2},{"c":"03IO020","n":2},{"c":"05IO006","n":2},{"c":"06FR038","n":2},{"c":"07IO020","n":2},{"c":"02IO005","n":2},{"c":"02IO009","n":2},{"c":"01FR002","n":1},{"c":"01FR006","n":1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>Arfilion</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>w5T0Juwqz8aUwHcRj5-fehs9dULlHagJG9j561E4xl9-xHA2rI0-dBNq-JoOIVyCNOtgVQxCNIGf4Q</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>CICQCAQFBAAQGBQBAECAKDYBAYCSWBQCAYLR2LBPGU4AGAIGAYTAEAQGDYSQEAQFA4FAA</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>Bilgewater|Shadow Isles</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I289" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J289" s="2" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K289" s="2" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="L289" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="M289" s="2" t="inlineStr">
+        <is>
+          <t>midrange</t>
+        </is>
+      </c>
+      <c r="N289" s="2" t="inlineStr">
+        <is>
+          <t>[{"c":"02SI008","n":3},{"c":"03BW001","n":3},{"c":"04SI015","n":3},{"c":"06SI043","n":3},{"c":"02BW023","n":3},{"c":"02BW029","n":3},{"c":"02BW044","n":3},{"c":"02BW047","n":3},{"c":"02BW053","n":3},{"c":"02BW056","n":3},{"c":"06BW038","n":2},{"c":"02BW030","n":2},{"c":"02BW037","n":2},{"c":"02SI007","n":2},{"c":"02SI010","n":2}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
